--- a/notes/langnote.xlsx
+++ b/notes/langnote.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23628"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\langnote\notes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\gitlab\langnote\notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D40CB575-A74B-49B1-860A-D481D0141AC8}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5205" yWindow="1110" windowWidth="22485" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5205" yWindow="1110" windowWidth="22485" windowHeight="11295" firstSheet="3" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="2014" sheetId="9" r:id="rId1"/>
@@ -22,6 +21,7 @@
     <sheet name="上证50" sheetId="5" r:id="rId7"/>
     <sheet name="2018年JavaEE课程大纲" sheetId="3" r:id="rId8"/>
     <sheet name="CVS repo" sheetId="6" r:id="rId9"/>
+    <sheet name="CVS repo github" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -5480,10 +5480,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>git@gitee.com:edidada/testjava11.git</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>git@gitee.com:edidada/testjuc.git</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -6924,13 +6920,17 @@
   </si>
   <si>
     <t>2月7日除夕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>git@gitee.com:edidada/testjava11.git</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="21">
     <font>
       <sz val="11"/>
@@ -7434,6 +7434,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7472,9 +7475,6 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -7756,158 +7756,158 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4E33173-997F-4553-8EFA-63F55CE6EBBA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B42"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>1833</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>1831</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>1830</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>1808</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="B30" t="s">
         <v>921</v>
@@ -7915,80 +7915,80 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="B31" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="B33" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="B36" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="B38" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="B40" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="B42" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
     </row>
   </sheetData>
@@ -7998,8 +7998,177 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A26"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="26" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="26" t="s">
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="26" t="s">
+        <v>1516</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="26" t="s">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="26" t="s">
+        <v>1521</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="26" t="s">
+        <v>1522</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="26" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="26" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="26" t="s">
+        <v>1525</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="26" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="26" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="26" t="s">
+        <v>1528</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="26" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="26" t="s">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="26" t="s">
+        <v>1530</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="26" t="s">
+        <v>1531</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="26" t="s">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="26" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="26" t="s">
+        <v>1534</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="26" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="26" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="26" t="s">
+        <v>1537</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="26" t="s">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="26" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="26" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="26" t="s">
+        <v>1541</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A1" r:id="rId1"/>
+    <hyperlink ref="A26" r:id="rId2"/>
+    <hyperlink ref="A25" r:id="rId3"/>
+    <hyperlink ref="A7" r:id="rId4"/>
+    <hyperlink ref="A2" r:id="rId5"/>
+    <hyperlink ref="A3" r:id="rId6"/>
+    <hyperlink ref="A4" r:id="rId7"/>
+    <hyperlink ref="A5" r:id="rId8"/>
+    <hyperlink ref="A6" r:id="rId9"/>
+    <hyperlink ref="A8" r:id="rId10"/>
+    <hyperlink ref="A9" r:id="rId11"/>
+    <hyperlink ref="A10" r:id="rId12"/>
+    <hyperlink ref="A11" r:id="rId13"/>
+    <hyperlink ref="A12" r:id="rId14"/>
+    <hyperlink ref="A14" r:id="rId15"/>
+    <hyperlink ref="A15" r:id="rId16"/>
+    <hyperlink ref="A16" r:id="rId17"/>
+    <hyperlink ref="A17" r:id="rId18"/>
+    <hyperlink ref="A18" r:id="rId19"/>
+    <hyperlink ref="A19" r:id="rId20"/>
+    <hyperlink ref="A20" r:id="rId21"/>
+    <hyperlink ref="A21" r:id="rId22"/>
+    <hyperlink ref="A22" r:id="rId23"/>
+    <hyperlink ref="A23" r:id="rId24"/>
+    <hyperlink ref="A24" r:id="rId25"/>
+    <hyperlink ref="A13" r:id="rId26"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8298A7F1-C2F5-49AA-98EA-50390782F5B3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -8008,92 +8177,92 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="B1" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="B2" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="B3" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="B4" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="B5" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="40.5">
       <c r="A6" s="1" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="27">
       <c r="A8" s="1" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="C8" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="B10" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="C10" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
     </row>
   </sheetData>
@@ -8103,7 +8272,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C5250C6-1281-4939-80EE-E0EAA9B95551}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -8112,74 +8281,74 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="B2" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="B4" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="B10" t="s">
+        <v>1888</v>
+      </c>
+      <c r="C10" t="s">
         <v>1889</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1890</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
   </sheetData>
@@ -8189,7 +8358,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G366"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -8322,10 +8491,10 @@
         <v>1039</v>
       </c>
       <c r="D20" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="E20" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -8358,7 +8527,7 @@
         <v>1044</v>
       </c>
       <c r="C23" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -8372,7 +8541,7 @@
         <v>1046</v>
       </c>
       <c r="D24" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -8394,8 +8563,8 @@
       <c r="A28" s="1" t="s">
         <v>1029</v>
       </c>
-      <c r="B28" s="40" t="s">
-        <v>1903</v>
+      <c r="B28" s="27" t="s">
+        <v>1902</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="11.45" customHeight="1">
@@ -8403,7 +8572,7 @@
         <v>1030</v>
       </c>
       <c r="B29" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="11.45" customHeight="1">
@@ -8426,7 +8595,7 @@
         <v>997</v>
       </c>
       <c r="B33" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -8462,7 +8631,7 @@
         <v>3</v>
       </c>
       <c r="D39" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -8476,10 +8645,10 @@
         <v>5</v>
       </c>
       <c r="D40" t="s">
+        <v>1645</v>
+      </c>
+      <c r="E40" t="s">
         <v>1646</v>
-      </c>
-      <c r="E40" t="s">
-        <v>1647</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -8532,13 +8701,13 @@
         <v>13</v>
       </c>
       <c r="B47" t="s">
+        <v>1647</v>
+      </c>
+      <c r="C47" t="s">
         <v>1648</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>1649</v>
-      </c>
-      <c r="D47" t="s">
-        <v>1650</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -8549,7 +8718,7 @@
         <v>16</v>
       </c>
       <c r="C48" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -8566,7 +8735,7 @@
         <v>21</v>
       </c>
       <c r="E49" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -8593,7 +8762,7 @@
         <v>32</v>
       </c>
       <c r="D52" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -8601,7 +8770,7 @@
         <v>27</v>
       </c>
       <c r="B53" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -8692,10 +8861,10 @@
         <v>49</v>
       </c>
       <c r="C64" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="D64" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -8733,7 +8902,7 @@
         <v>59</v>
       </c>
       <c r="B68" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="C68" t="s">
         <v>60</v>
@@ -8805,7 +8974,7 @@
         <v>78</v>
       </c>
       <c r="B74" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -8844,7 +9013,7 @@
         <v>88</v>
       </c>
       <c r="B77" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="C77" t="s">
         <v>93</v>
@@ -8872,7 +9041,7 @@
         <v>94</v>
       </c>
       <c r="C79" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -8899,10 +9068,10 @@
         <v>104</v>
       </c>
       <c r="C82" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="D82" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -8925,10 +9094,10 @@
         <v>100</v>
       </c>
       <c r="B86" t="s">
+        <v>1655</v>
+      </c>
+      <c r="C86" t="s">
         <v>1656</v>
-      </c>
-      <c r="C86" t="s">
-        <v>1657</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -9020,7 +9189,7 @@
         <v>123</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="103" spans="1:3">
@@ -9059,7 +9228,7 @@
         <v>129</v>
       </c>
       <c r="B108" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="109" spans="1:3">
@@ -9168,7 +9337,7 @@
         <v>153</v>
       </c>
       <c r="B122" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -9186,7 +9355,7 @@
         <v>156</v>
       </c>
       <c r="B125" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -9204,7 +9373,7 @@
         <v>159</v>
       </c>
       <c r="B128" t="s">
-        <v>1801</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -9217,7 +9386,7 @@
         <v>161</v>
       </c>
       <c r="B130" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -9314,7 +9483,7 @@
         <v>178</v>
       </c>
       <c r="B147" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -9822,765 +9991,765 @@
     </row>
     <row r="245" spans="1:2">
       <c r="A245" s="1" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="246" spans="1:2">
       <c r="A246" s="1" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="247" spans="1:2">
       <c r="A247" s="1" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="248" spans="1:2">
       <c r="A248" s="1" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="249" spans="1:2">
       <c r="A249" s="1" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="250" spans="1:2">
       <c r="A250" s="1" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="251" spans="1:2">
       <c r="A251" s="1" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="252" spans="1:2">
       <c r="A252" s="1" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="B252" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" s="1" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="B253" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="254" spans="1:2">
       <c r="A254" s="1" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="B254" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="255" spans="1:2">
       <c r="A255" s="1" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="B255" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" s="1" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="257" spans="1:2">
       <c r="A257" s="1" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" s="1" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="B258" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="259" spans="1:2">
       <c r="A259" s="1" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="B259" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="260" spans="1:2">
       <c r="A260" s="1" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="261" spans="1:2">
       <c r="A261" s="1" t="s">
-        <v>1675</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="262" spans="1:2">
       <c r="A262" s="1" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="263" spans="1:2">
       <c r="A263" s="1" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="264" spans="1:2">
       <c r="A264" s="1" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="265" spans="1:2">
       <c r="A265" s="1" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="266" spans="1:2">
       <c r="A266" s="1" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="267" spans="1:2">
       <c r="A267" s="1" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="268" spans="1:2">
       <c r="A268" s="1" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="269" spans="1:2">
       <c r="A269" s="1" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="270" spans="1:2">
       <c r="A270" s="1" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="271" spans="1:2">
       <c r="A271" s="1" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="272" spans="1:2">
       <c r="A272" s="1" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="273" spans="1:1">
       <c r="A273" s="1" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="274" spans="1:1">
       <c r="A274" s="1" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="275" spans="1:1">
       <c r="A275" s="1" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="276" spans="1:1">
       <c r="A276" s="1" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="277" spans="1:1">
       <c r="A277" s="1" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="278" spans="1:1">
       <c r="A278" s="1" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="279" spans="1:1">
       <c r="A279" s="1" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="280" spans="1:1">
       <c r="A280" s="1" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="281" spans="1:1">
       <c r="A281" s="1" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="282" spans="1:1">
       <c r="A282" s="1" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="283" spans="1:1">
       <c r="A283" s="1" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="284" spans="1:1">
       <c r="A284" s="1" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="285" spans="1:1">
       <c r="A285" s="1" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="286" spans="1:1">
       <c r="A286" s="1" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="287" spans="1:1">
       <c r="A287" s="1" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="288" spans="1:1">
       <c r="A288" s="1" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" s="1" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="290" spans="1:2">
       <c r="A290" s="1" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="291" spans="1:2">
       <c r="A291" s="1" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="292" spans="1:2">
       <c r="A292" s="1" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="B292" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="293" spans="1:2">
       <c r="A293" s="1" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="294" spans="1:2">
       <c r="A294" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="295" spans="1:2">
       <c r="A295" s="1" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="296" spans="1:2">
       <c r="A296" s="1" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="297" spans="1:2">
       <c r="A297" s="1" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="298" spans="1:2">
       <c r="A298" s="1" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="299" spans="1:2">
       <c r="A299" s="1" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="300" spans="1:2">
       <c r="A300" s="1" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="301" spans="1:2">
       <c r="A301" s="1" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="302" spans="1:2">
       <c r="A302" s="1" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="303" spans="1:2">
       <c r="A303" s="1" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="304" spans="1:2">
       <c r="A304" s="1" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="305" spans="1:1">
       <c r="A305" s="1" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="306" spans="1:1">
       <c r="A306" s="1" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="307" spans="1:1">
       <c r="A307" s="1" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="308" spans="1:1">
       <c r="A308" s="1" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="309" spans="1:1">
       <c r="A309" s="1" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="310" spans="1:1">
       <c r="A310" s="1" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="311" spans="1:1">
       <c r="A311" s="1" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="312" spans="1:1">
       <c r="A312" s="1" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="313" spans="1:1">
       <c r="A313" s="1" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="314" spans="1:1">
       <c r="A314" s="1" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="315" spans="1:1">
       <c r="A315" s="1" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="316" spans="1:1">
       <c r="A316" s="1" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="317" spans="1:1">
       <c r="A317" s="1" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="318" spans="1:1">
       <c r="A318" s="1" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="319" spans="1:1">
       <c r="A319" s="1" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="320" spans="1:1">
       <c r="A320" s="1" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="321" spans="1:4">
       <c r="A321" s="1" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="322" spans="1:4">
       <c r="A322" s="1" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="323" spans="1:4">
       <c r="A323" s="1" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="B323" t="s">
+        <v>1880</v>
+      </c>
+      <c r="C323" t="s">
         <v>1881</v>
       </c>
-      <c r="C323" t="s">
+      <c r="D323" t="s">
         <v>1882</v>
-      </c>
-      <c r="D323" t="s">
-        <v>1883</v>
       </c>
     </row>
     <row r="324" spans="1:4">
       <c r="A324" s="1" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="325" spans="1:4">
       <c r="A325" s="1" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="B325" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="326" spans="1:4">
       <c r="A326" s="1" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="327" spans="1:4">
       <c r="A327" s="1" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="B327" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="328" spans="1:4">
       <c r="A328" s="1" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="B328" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="329" spans="1:4">
       <c r="A329" s="1" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B329" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="330" spans="1:4">
       <c r="A330" s="1" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="B330" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="331" spans="1:4">
       <c r="A331" s="1" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="B331" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="332" spans="1:4">
       <c r="A332" s="1" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="B332" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="333" spans="1:4">
       <c r="A333" s="1" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="B333" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="334" spans="1:4">
       <c r="A334" s="1" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="B334" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="335" spans="1:4">
       <c r="A335" s="1" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="B335" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="336" spans="1:4">
       <c r="A336" s="1" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="B336" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="337" spans="1:2">
       <c r="A337" s="1" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="B337" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="338" spans="1:2">
       <c r="A338" s="1" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="B338" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="339" spans="1:2">
       <c r="A339" s="1" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="B339" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="340" spans="1:2">
       <c r="A340" s="1" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="B340" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="341" spans="1:2">
       <c r="A341" s="1" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="B341" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="342" spans="1:2">
       <c r="A342" s="1" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="B342" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="343" spans="1:2">
       <c r="A343" s="1" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="B343" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="344" spans="1:2">
       <c r="A344" s="1" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="B344" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="345" spans="1:2">
       <c r="A345" s="1" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="B345" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="346" spans="1:2">
       <c r="A346" s="1" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="B346" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="347" spans="1:2">
       <c r="A347" s="1" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="B347" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="348" spans="1:2">
       <c r="A348" s="1" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="B348" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="349" spans="1:2">
       <c r="A349" s="1" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="B349" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="350" spans="1:2">
       <c r="A350" s="1" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="B350" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="351" spans="1:2">
       <c r="A351" s="1" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="B351" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="352" spans="1:2">
       <c r="A352" s="1" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="B352" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="353" spans="1:2">
       <c r="A353" s="1" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="B353" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="354" spans="1:2">
       <c r="A354" s="1" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="B354" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="355" spans="1:2">
       <c r="A355" s="1" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="B355" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="356" spans="1:2">
       <c r="A356" s="1" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="B356" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="357" spans="1:2">
       <c r="A357" s="1" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="B357" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="358" spans="1:2">
       <c r="A358" s="1" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="B358" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="359" spans="1:2">
       <c r="A359" s="1" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="B359" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="360" spans="1:2">
       <c r="A360" s="1" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="B360" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="361" spans="1:2">
       <c r="A361" s="1" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="B361" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="362" spans="1:2">
       <c r="A362" s="1" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="B362" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="363" spans="1:2">
       <c r="A363" s="1" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="B363" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="364" spans="1:2">
       <c r="A364" s="1" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="B364" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="365" spans="1:2">
       <c r="A365" s="1" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="B365" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="366" spans="1:2">
       <c r="A366" s="1" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="B366" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
     </row>
   </sheetData>
@@ -10591,7 +10760,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L368"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -10621,7 +10790,7 @@
         <v>857</v>
       </c>
       <c r="B3" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -10629,7 +10798,7 @@
         <v>858</v>
       </c>
       <c r="B4" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -10637,7 +10806,7 @@
         <v>859</v>
       </c>
       <c r="B5" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -10710,7 +10879,7 @@
         <v>873</v>
       </c>
       <c r="B19" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -10964,7 +11133,7 @@
         <v>686</v>
       </c>
       <c r="B68" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -10972,7 +11141,7 @@
         <v>687</v>
       </c>
       <c r="B69" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -11030,7 +11199,7 @@
         <v>698</v>
       </c>
       <c r="B80" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -11038,7 +11207,7 @@
         <v>699</v>
       </c>
       <c r="B81" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -11092,7 +11261,7 @@
         <v>254</v>
       </c>
       <c r="D90" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -11373,7 +11542,7 @@
         <v>245</v>
       </c>
       <c r="B115" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="94.5">
@@ -11652,7 +11821,7 @@
         <v>298</v>
       </c>
       <c r="B136" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -11727,7 +11896,7 @@
         <v>1113</v>
       </c>
       <c r="D142" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -12295,7 +12464,7 @@
         <v>412</v>
       </c>
       <c r="D192" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="193" spans="1:7" ht="54">
@@ -12354,7 +12523,7 @@
         <v>415</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -12835,7 +13004,7 @@
         <v>1267</v>
       </c>
       <c r="C240" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="D240" t="s">
         <v>1268</v>
@@ -12863,7 +13032,7 @@
         <v>1271</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="D242" t="s">
         <v>1273</v>
@@ -12957,7 +13126,7 @@
         <v>1281</v>
       </c>
       <c r="C253" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="254" spans="1:5">
@@ -13824,7 +13993,7 @@
         <v>785</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>810</v>
@@ -14016,7 +14185,7 @@
         <v>795</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>1351</v>
@@ -14054,7 +14223,7 @@
         <v>797</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>1353</v>
@@ -14083,7 +14252,7 @@
         <v>816</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="F330" s="2"/>
       <c r="G330" s="2"/>
@@ -14306,7 +14475,7 @@
         <v>852</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="E341" s="2"/>
       <c r="F341" s="2"/>
@@ -14331,7 +14500,7 @@
         <v>1375</v>
       </c>
       <c r="E342" s="2" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="F342" s="2"/>
       <c r="G342" s="2"/>
@@ -14370,7 +14539,7 @@
         <v>856</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="E344" s="2"/>
       <c r="F344" s="2"/>
@@ -14386,7 +14555,7 @@
         <v>829</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="C345" s="2"/>
       <c r="D345" s="2"/>
@@ -14422,10 +14591,10 @@
         <v>831</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="D347" s="2"/>
       <c r="E347" s="2"/>
@@ -14448,7 +14617,7 @@
         <v>853</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="E348" s="2" t="s">
         <v>1378</v>
@@ -14931,60 +15100,60 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E130" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
-    <hyperlink ref="C162" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
-    <hyperlink ref="C178" r:id="rId3" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
-    <hyperlink ref="C179" r:id="rId4" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
-    <hyperlink ref="D181" r:id="rId5" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
-    <hyperlink ref="C185" r:id="rId6" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
-    <hyperlink ref="C188" r:id="rId7" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
-    <hyperlink ref="D188" r:id="rId8" xr:uid="{00000000-0004-0000-0100-000007000000}"/>
-    <hyperlink ref="F188" r:id="rId9" xr:uid="{00000000-0004-0000-0100-000008000000}"/>
-    <hyperlink ref="E138" r:id="rId10" location="/info" xr:uid="{00000000-0004-0000-0100-000009000000}"/>
-    <hyperlink ref="C190" r:id="rId11" location="/info" xr:uid="{00000000-0004-0000-0100-00000A000000}"/>
-    <hyperlink ref="D190" r:id="rId12" xr:uid="{00000000-0004-0000-0100-00000B000000}"/>
-    <hyperlink ref="D193" r:id="rId13" xr:uid="{00000000-0004-0000-0100-00000C000000}"/>
-    <hyperlink ref="E193" r:id="rId14" xr:uid="{00000000-0004-0000-0100-00000D000000}"/>
-    <hyperlink ref="F193" r:id="rId15" xr:uid="{00000000-0004-0000-0100-00000E000000}"/>
-    <hyperlink ref="C198" r:id="rId16" xr:uid="{00000000-0004-0000-0100-00000F000000}"/>
-    <hyperlink ref="B200" r:id="rId17" xr:uid="{00000000-0004-0000-0100-000010000000}"/>
-    <hyperlink ref="B201" r:id="rId18" xr:uid="{00000000-0004-0000-0100-000011000000}"/>
-    <hyperlink ref="C201" r:id="rId19" xr:uid="{00000000-0004-0000-0100-000012000000}"/>
-    <hyperlink ref="E202" r:id="rId20" xr:uid="{00000000-0004-0000-0100-000013000000}"/>
-    <hyperlink ref="B209" r:id="rId21" display="https://link.zhihu.com/?target=https%3A//www.mongodb.com/cloud" xr:uid="{00000000-0004-0000-0100-000014000000}"/>
-    <hyperlink ref="B211" r:id="rId22" xr:uid="{00000000-0004-0000-0100-000015000000}"/>
-    <hyperlink ref="C211" r:id="rId23" xr:uid="{00000000-0004-0000-0100-000016000000}"/>
-    <hyperlink ref="C213" r:id="rId24" xr:uid="{00000000-0004-0000-0100-000017000000}"/>
-    <hyperlink ref="C191" r:id="rId25" xr:uid="{00000000-0004-0000-0100-000018000000}"/>
-    <hyperlink ref="D219" r:id="rId26" xr:uid="{00000000-0004-0000-0100-000019000000}"/>
-    <hyperlink ref="B219" r:id="rId27" xr:uid="{00000000-0004-0000-0100-00001A000000}"/>
-    <hyperlink ref="D220" r:id="rId28" xr:uid="{00000000-0004-0000-0100-00001B000000}"/>
-    <hyperlink ref="B232" r:id="rId29" xr:uid="{00000000-0004-0000-0100-00001C000000}"/>
-    <hyperlink ref="D242" r:id="rId30" display="https://github.com/360EntSecGroup-Skylar/ElasticHD" xr:uid="{00000000-0004-0000-0100-00001D000000}"/>
-    <hyperlink ref="C286" r:id="rId31" xr:uid="{00000000-0004-0000-0100-00001E000000}"/>
-    <hyperlink ref="D286" r:id="rId32" xr:uid="{00000000-0004-0000-0100-00001F000000}"/>
-    <hyperlink ref="E286" r:id="rId33" xr:uid="{00000000-0004-0000-0100-000020000000}"/>
-    <hyperlink ref="B287" r:id="rId34" display="https://github.com/medcl/elasticsearch-migration/" xr:uid="{00000000-0004-0000-0100-000021000000}"/>
-    <hyperlink ref="C287" r:id="rId35" xr:uid="{00000000-0004-0000-0100-000022000000}"/>
-    <hyperlink ref="D291" r:id="rId36" xr:uid="{00000000-0004-0000-0100-000023000000}"/>
-    <hyperlink ref="B292" r:id="rId37" xr:uid="{00000000-0004-0000-0100-000024000000}"/>
-    <hyperlink ref="B312" r:id="rId38" xr:uid="{00000000-0004-0000-0100-000025000000}"/>
-    <hyperlink ref="D317" r:id="rId39" xr:uid="{00000000-0004-0000-0100-000026000000}"/>
-    <hyperlink ref="B330" r:id="rId40" display="https://github.com/youfou/wxpy" xr:uid="{00000000-0004-0000-0100-000027000000}"/>
-    <hyperlink ref="F348" r:id="rId41" xr:uid="{00000000-0004-0000-0100-000028000000}"/>
-    <hyperlink ref="D354" r:id="rId42" xr:uid="{00000000-0004-0000-0100-000029000000}"/>
-    <hyperlink ref="C356" r:id="rId43" xr:uid="{00000000-0004-0000-0100-00002A000000}"/>
-    <hyperlink ref="E358" r:id="rId44" xr:uid="{00000000-0004-0000-0100-00002B000000}"/>
-    <hyperlink ref="B359" r:id="rId45" xr:uid="{00000000-0004-0000-0100-00002C000000}"/>
-    <hyperlink ref="D359" r:id="rId46" xr:uid="{00000000-0004-0000-0100-00002D000000}"/>
-    <hyperlink ref="C362" r:id="rId47" xr:uid="{00000000-0004-0000-0100-00002E000000}"/>
-    <hyperlink ref="F362" r:id="rId48" xr:uid="{00000000-0004-0000-0100-00002F000000}"/>
-    <hyperlink ref="G362" r:id="rId49" xr:uid="{00000000-0004-0000-0100-000030000000}"/>
-    <hyperlink ref="G360" r:id="rId50" xr:uid="{00000000-0004-0000-0100-000031000000}"/>
-    <hyperlink ref="B363" r:id="rId51" xr:uid="{00000000-0004-0000-0100-000032000000}"/>
-    <hyperlink ref="C367" r:id="rId52" xr:uid="{00000000-0004-0000-0100-000033000000}"/>
-    <hyperlink ref="D367" r:id="rId53" xr:uid="{00000000-0004-0000-0100-000034000000}"/>
-    <hyperlink ref="G367" r:id="rId54" xr:uid="{00000000-0004-0000-0100-000035000000}"/>
+    <hyperlink ref="E130" r:id="rId1"/>
+    <hyperlink ref="C162" r:id="rId2"/>
+    <hyperlink ref="C178" r:id="rId3"/>
+    <hyperlink ref="C179" r:id="rId4"/>
+    <hyperlink ref="D181" r:id="rId5"/>
+    <hyperlink ref="C185" r:id="rId6"/>
+    <hyperlink ref="C188" r:id="rId7"/>
+    <hyperlink ref="D188" r:id="rId8"/>
+    <hyperlink ref="F188" r:id="rId9"/>
+    <hyperlink ref="E138" r:id="rId10" location="/info"/>
+    <hyperlink ref="C190" r:id="rId11" location="/info"/>
+    <hyperlink ref="D190" r:id="rId12"/>
+    <hyperlink ref="D193" r:id="rId13"/>
+    <hyperlink ref="E193" r:id="rId14"/>
+    <hyperlink ref="F193" r:id="rId15"/>
+    <hyperlink ref="C198" r:id="rId16"/>
+    <hyperlink ref="B200" r:id="rId17"/>
+    <hyperlink ref="B201" r:id="rId18"/>
+    <hyperlink ref="C201" r:id="rId19"/>
+    <hyperlink ref="E202" r:id="rId20"/>
+    <hyperlink ref="B209" r:id="rId21" display="https://link.zhihu.com/?target=https%3A//www.mongodb.com/cloud"/>
+    <hyperlink ref="B211" r:id="rId22"/>
+    <hyperlink ref="C211" r:id="rId23"/>
+    <hyperlink ref="C213" r:id="rId24"/>
+    <hyperlink ref="C191" r:id="rId25"/>
+    <hyperlink ref="D219" r:id="rId26"/>
+    <hyperlink ref="B219" r:id="rId27"/>
+    <hyperlink ref="D220" r:id="rId28"/>
+    <hyperlink ref="B232" r:id="rId29"/>
+    <hyperlink ref="D242" r:id="rId30" display="https://github.com/360EntSecGroup-Skylar/ElasticHD"/>
+    <hyperlink ref="C286" r:id="rId31"/>
+    <hyperlink ref="D286" r:id="rId32"/>
+    <hyperlink ref="E286" r:id="rId33"/>
+    <hyperlink ref="B287" r:id="rId34" display="https://github.com/medcl/elasticsearch-migration/"/>
+    <hyperlink ref="C287" r:id="rId35"/>
+    <hyperlink ref="D291" r:id="rId36"/>
+    <hyperlink ref="B292" r:id="rId37"/>
+    <hyperlink ref="B312" r:id="rId38"/>
+    <hyperlink ref="D317" r:id="rId39"/>
+    <hyperlink ref="B330" r:id="rId40" display="https://github.com/youfou/wxpy"/>
+    <hyperlink ref="F348" r:id="rId41"/>
+    <hyperlink ref="D354" r:id="rId42"/>
+    <hyperlink ref="C356" r:id="rId43"/>
+    <hyperlink ref="E358" r:id="rId44"/>
+    <hyperlink ref="B359" r:id="rId45"/>
+    <hyperlink ref="D359" r:id="rId46"/>
+    <hyperlink ref="C362" r:id="rId47"/>
+    <hyperlink ref="F362" r:id="rId48"/>
+    <hyperlink ref="G362" r:id="rId49"/>
+    <hyperlink ref="G360" r:id="rId50"/>
+    <hyperlink ref="B363" r:id="rId51"/>
+    <hyperlink ref="C367" r:id="rId52"/>
+    <hyperlink ref="D367" r:id="rId53"/>
+    <hyperlink ref="G367" r:id="rId54"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId55"/>
@@ -14992,7 +15161,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G297"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -15007,19 +15176,19 @@
   <sheetData>
     <row r="1" spans="1:7" ht="56.25" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>937</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>938</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>1459</v>
@@ -15030,7 +15199,7 @@
     </row>
     <row r="2" spans="1:7" ht="49.9" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>991</v>
@@ -15053,7 +15222,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="4" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>1456</v>
@@ -15068,13 +15237,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="4" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>1462</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -15083,7 +15252,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="4" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>1462</v>
@@ -15096,7 +15265,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="4" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>1466</v>
@@ -15109,7 +15278,7 @@
     </row>
     <row r="7" spans="1:7" ht="27">
       <c r="A7" s="4" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>1463</v>
@@ -15122,7 +15291,7 @@
     </row>
     <row r="8" spans="1:7" ht="27">
       <c r="A8" s="4" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>1464</v>
@@ -15134,17 +15303,17 @@
         <v>1467</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7" ht="27">
       <c r="A9" s="4" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>1468</v>
@@ -15160,7 +15329,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="4" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>1472</v>
@@ -15175,7 +15344,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="4" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>1471</v>
@@ -15188,7 +15357,7 @@
     </row>
     <row r="12" spans="1:7" ht="27">
       <c r="A12" s="4" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>1474</v>
@@ -15205,7 +15374,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="4" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>1477</v>
@@ -15218,7 +15387,7 @@
     </row>
     <row r="14" spans="1:7" ht="27">
       <c r="A14" s="4" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>1478</v>
@@ -15233,7 +15402,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="4" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>1481</v>
@@ -15246,7 +15415,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="4" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>1480</v>
@@ -15259,7 +15428,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="4" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>1482</v>
@@ -15276,10 +15445,10 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="4" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -15289,13 +15458,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="4" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -15304,13 +15473,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="4" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>1519</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>1520</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -15319,13 +15488,13 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="4" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -15334,10 +15503,10 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="4" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -15347,10 +15516,10 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="4" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -15360,10 +15529,10 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="4" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -15373,10 +15542,10 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="4" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
@@ -15386,10 +15555,10 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="4" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -15399,13 +15568,13 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="4" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>1550</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>1551</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>1552</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -15414,10 +15583,10 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="4" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
@@ -15427,7 +15596,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="4" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -15438,10 +15607,10 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="4" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="C30" s="4"/>
       <c r="D30" s="4"/>
@@ -15451,7 +15620,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="4" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -15462,7 +15631,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="4" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -15473,7 +15642,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="4" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -15484,7 +15653,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="4" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="C34" s="4"/>
       <c r="D34" s="4"/>
@@ -15494,7 +15663,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="4" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>922</v>
@@ -15507,10 +15676,10 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="4" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="C36" s="4"/>
       <c r="D36" s="4"/>
@@ -15520,10 +15689,10 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="4" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -15533,10 +15702,10 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="4" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
@@ -15546,10 +15715,10 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="4" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -15559,7 +15728,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="4" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -15570,7 +15739,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="4" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -15581,10 +15750,10 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="4" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
@@ -15594,7 +15763,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="4" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -15605,10 +15774,10 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="4" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
@@ -15618,10 +15787,10 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="4" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
@@ -15631,7 +15800,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" s="4" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -15642,7 +15811,7 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="4" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -15653,7 +15822,7 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" s="4" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -15664,7 +15833,7 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="4" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -15675,7 +15844,7 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="4" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -15686,7 +15855,7 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" s="4" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -15697,7 +15866,7 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="4" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -15708,7 +15877,7 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="4" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>408</v>
@@ -15721,7 +15890,7 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="4" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -15732,7 +15901,7 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" s="4" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -15743,7 +15912,7 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="4" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -15754,7 +15923,7 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="4" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -15765,7 +15934,7 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="4" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -15776,7 +15945,7 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="4" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -17930,11 +18099,11 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
-    <hyperlink ref="F2" r:id="rId2" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
-    <hyperlink ref="G2" r:id="rId3" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
-    <hyperlink ref="B12" r:id="rId4" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
-    <hyperlink ref="C14" r:id="rId5" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="F2" r:id="rId2"/>
+    <hyperlink ref="G2" r:id="rId3"/>
+    <hyperlink ref="B12" r:id="rId4"/>
+    <hyperlink ref="C14" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
@@ -17942,7 +18111,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -18144,7 +18313,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D89"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
@@ -18154,12 +18323,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="37" t="s">
         <v>420</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="38"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="39"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="16" t="s">
@@ -18176,13 +18345,13 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="28" t="s">
         <v>425</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="31" t="s">
         <v>426</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="C3" s="34" t="s">
         <v>427</v>
       </c>
       <c r="D3" s="18" t="s">
@@ -18190,47 +18359,47 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="28"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="34"/>
+      <c r="A4" s="29"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="35"/>
       <c r="D4" s="19" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="28"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="34"/>
+      <c r="A5" s="29"/>
+      <c r="B5" s="32"/>
+      <c r="C5" s="35"/>
       <c r="D5" s="19" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="28"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="34"/>
+      <c r="A6" s="29"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="35"/>
       <c r="D6" s="19" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="28"/>
-      <c r="B7" s="31"/>
-      <c r="C7" s="34"/>
+      <c r="A7" s="29"/>
+      <c r="B7" s="32"/>
+      <c r="C7" s="35"/>
       <c r="D7" s="19" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="28"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="35"/>
+      <c r="A8" s="29"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="36"/>
       <c r="D8" s="19" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="28"/>
+      <c r="A9" s="29"/>
       <c r="B9" s="11" t="s">
         <v>439</v>
       </c>
@@ -18242,7 +18411,7 @@
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="28"/>
+      <c r="A10" s="29"/>
       <c r="B10" s="11" t="s">
         <v>441</v>
       </c>
@@ -18252,7 +18421,7 @@
       <c r="D10" s="20"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="28"/>
+      <c r="A11" s="29"/>
       <c r="B11" s="11" t="s">
         <v>443</v>
       </c>
@@ -18264,7 +18433,7 @@
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="28"/>
+      <c r="A12" s="29"/>
       <c r="B12" s="11" t="s">
         <v>445</v>
       </c>
@@ -18276,7 +18445,7 @@
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="28"/>
+      <c r="A13" s="29"/>
       <c r="B13" s="11" t="s">
         <v>447</v>
       </c>
@@ -18286,7 +18455,7 @@
       <c r="D13" s="20"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="28"/>
+      <c r="A14" s="29"/>
       <c r="B14" s="11" t="s">
         <v>449</v>
       </c>
@@ -18298,7 +18467,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" ht="24">
-      <c r="A15" s="39"/>
+      <c r="A15" s="40"/>
       <c r="B15" s="11" t="s">
         <v>451</v>
       </c>
@@ -18310,13 +18479,13 @@
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="28" t="s">
         <v>453</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="31" t="s">
         <v>454</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="34" t="s">
         <v>455</v>
       </c>
       <c r="D16" s="18" t="s">
@@ -18324,31 +18493,31 @@
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="28"/>
-      <c r="B17" s="31"/>
-      <c r="C17" s="34"/>
+      <c r="A17" s="29"/>
+      <c r="B17" s="32"/>
+      <c r="C17" s="35"/>
       <c r="D17" s="19" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="24">
-      <c r="A18" s="28"/>
-      <c r="B18" s="31"/>
-      <c r="C18" s="34"/>
+      <c r="A18" s="29"/>
+      <c r="B18" s="32"/>
+      <c r="C18" s="35"/>
       <c r="D18" s="19" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="28"/>
-      <c r="B19" s="32"/>
-      <c r="C19" s="35"/>
+      <c r="A19" s="29"/>
+      <c r="B19" s="33"/>
+      <c r="C19" s="36"/>
       <c r="D19" s="19" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="28"/>
+      <c r="A20" s="29"/>
       <c r="B20" s="11" t="s">
         <v>465</v>
       </c>
@@ -18360,7 +18529,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" ht="24">
-      <c r="A21" s="28"/>
+      <c r="A21" s="29"/>
       <c r="B21" s="11" t="s">
         <v>467</v>
       </c>
@@ -18372,7 +18541,7 @@
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="28"/>
+      <c r="A22" s="29"/>
       <c r="B22" s="11" t="s">
         <v>469</v>
       </c>
@@ -18384,7 +18553,7 @@
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="28"/>
+      <c r="A23" s="29"/>
       <c r="B23" s="11" t="s">
         <v>471</v>
       </c>
@@ -18394,7 +18563,7 @@
       <c r="D23" s="20"/>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="28"/>
+      <c r="A24" s="29"/>
       <c r="B24" s="11" t="s">
         <v>473</v>
       </c>
@@ -18406,7 +18575,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" ht="24">
-      <c r="A25" s="28"/>
+      <c r="A25" s="29"/>
       <c r="B25" s="11" t="s">
         <v>475</v>
       </c>
@@ -18418,7 +18587,7 @@
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="28"/>
+      <c r="A26" s="29"/>
       <c r="B26" s="11" t="s">
         <v>477</v>
       </c>
@@ -18428,7 +18597,7 @@
       <c r="D26" s="20"/>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="28"/>
+      <c r="A27" s="29"/>
       <c r="B27" s="11" t="s">
         <v>479</v>
       </c>
@@ -18440,7 +18609,7 @@
       </c>
     </row>
     <row r="28" spans="1:4" ht="36">
-      <c r="A28" s="39"/>
+      <c r="A28" s="40"/>
       <c r="B28" s="11" t="s">
         <v>481</v>
       </c>
@@ -18452,13 +18621,13 @@
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="27" t="s">
+      <c r="A29" s="28" t="s">
         <v>483</v>
       </c>
-      <c r="B29" s="30" t="s">
+      <c r="B29" s="31" t="s">
         <v>484</v>
       </c>
-      <c r="C29" s="33" t="s">
+      <c r="C29" s="34" t="s">
         <v>485</v>
       </c>
       <c r="D29" s="18" t="s">
@@ -18466,143 +18635,143 @@
       </c>
     </row>
     <row r="30" spans="1:4" ht="24">
-      <c r="A30" s="28"/>
-      <c r="B30" s="31"/>
-      <c r="C30" s="34"/>
+      <c r="A30" s="29"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="35"/>
       <c r="D30" s="19" t="s">
         <v>486</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="28"/>
-      <c r="B31" s="31"/>
-      <c r="C31" s="34"/>
+      <c r="A31" s="29"/>
+      <c r="B31" s="32"/>
+      <c r="C31" s="35"/>
       <c r="D31" s="19" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="28"/>
-      <c r="B32" s="31"/>
-      <c r="C32" s="34"/>
+      <c r="A32" s="29"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="35"/>
       <c r="D32" s="19" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="28"/>
-      <c r="B33" s="31"/>
-      <c r="C33" s="34"/>
+      <c r="A33" s="29"/>
+      <c r="B33" s="32"/>
+      <c r="C33" s="35"/>
       <c r="D33" s="19" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="28"/>
-      <c r="B34" s="31"/>
-      <c r="C34" s="34"/>
+      <c r="A34" s="29"/>
+      <c r="B34" s="32"/>
+      <c r="C34" s="35"/>
       <c r="D34" s="19" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="28"/>
-      <c r="B35" s="31"/>
-      <c r="C35" s="34"/>
+      <c r="A35" s="29"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="35"/>
       <c r="D35" s="19" t="s">
         <v>491</v>
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="28"/>
-      <c r="B36" s="31"/>
-      <c r="C36" s="34"/>
+      <c r="A36" s="29"/>
+      <c r="B36" s="32"/>
+      <c r="C36" s="35"/>
       <c r="D36" s="19" t="s">
         <v>492</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="28"/>
-      <c r="B37" s="31"/>
-      <c r="C37" s="34"/>
+      <c r="A37" s="29"/>
+      <c r="B37" s="32"/>
+      <c r="C37" s="35"/>
       <c r="D37" s="19" t="s">
         <v>493</v>
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="28"/>
-      <c r="B38" s="31"/>
-      <c r="C38" s="34"/>
+      <c r="A38" s="29"/>
+      <c r="B38" s="32"/>
+      <c r="C38" s="35"/>
       <c r="D38" s="19" t="s">
         <v>494</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="28"/>
-      <c r="B39" s="31"/>
-      <c r="C39" s="34"/>
+      <c r="A39" s="29"/>
+      <c r="B39" s="32"/>
+      <c r="C39" s="35"/>
       <c r="D39" s="19" t="s">
         <v>495</v>
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="28"/>
-      <c r="B40" s="31"/>
-      <c r="C40" s="34"/>
+      <c r="A40" s="29"/>
+      <c r="B40" s="32"/>
+      <c r="C40" s="35"/>
       <c r="D40" s="19" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="28"/>
-      <c r="B41" s="31"/>
-      <c r="C41" s="34"/>
+      <c r="A41" s="29"/>
+      <c r="B41" s="32"/>
+      <c r="C41" s="35"/>
       <c r="D41" s="19" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="28"/>
-      <c r="B42" s="31"/>
-      <c r="C42" s="34"/>
+      <c r="A42" s="29"/>
+      <c r="B42" s="32"/>
+      <c r="C42" s="35"/>
       <c r="D42" s="19" t="s">
         <v>498</v>
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="28"/>
-      <c r="B43" s="31"/>
-      <c r="C43" s="34"/>
+      <c r="A43" s="29"/>
+      <c r="B43" s="32"/>
+      <c r="C43" s="35"/>
       <c r="D43" s="19" t="s">
         <v>499</v>
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="28"/>
-      <c r="B44" s="31"/>
-      <c r="C44" s="34"/>
+      <c r="A44" s="29"/>
+      <c r="B44" s="32"/>
+      <c r="C44" s="35"/>
       <c r="D44" s="19" t="s">
         <v>500</v>
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="28"/>
-      <c r="B45" s="31"/>
-      <c r="C45" s="34"/>
+      <c r="A45" s="29"/>
+      <c r="B45" s="32"/>
+      <c r="C45" s="35"/>
       <c r="D45" s="19" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="28"/>
-      <c r="B46" s="32"/>
-      <c r="C46" s="35"/>
+      <c r="A46" s="29"/>
+      <c r="B46" s="33"/>
+      <c r="C46" s="36"/>
       <c r="D46" s="19" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="28"/>
+      <c r="A47" s="29"/>
       <c r="B47" s="11" t="s">
         <v>505</v>
       </c>
@@ -18612,8 +18781,8 @@
       <c r="D47" s="20"/>
     </row>
     <row r="48" spans="1:4">
-      <c r="A48" s="28"/>
-      <c r="B48" s="30" t="s">
+      <c r="A48" s="29"/>
+      <c r="B48" s="31" t="s">
         <v>507</v>
       </c>
       <c r="C48" s="8" t="s">
@@ -18624,8 +18793,8 @@
       </c>
     </row>
     <row r="49" spans="1:4" ht="48">
-      <c r="A49" s="28"/>
-      <c r="B49" s="32"/>
+      <c r="A49" s="29"/>
+      <c r="B49" s="33"/>
       <c r="C49" s="10" t="s">
         <v>509</v>
       </c>
@@ -18634,8 +18803,8 @@
       </c>
     </row>
     <row r="50" spans="1:4">
-      <c r="A50" s="28"/>
-      <c r="B50" s="30" t="s">
+      <c r="A50" s="29"/>
+      <c r="B50" s="31" t="s">
         <v>510</v>
       </c>
       <c r="C50" s="8" t="s">
@@ -18644,8 +18813,8 @@
       <c r="D50" s="20"/>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="28"/>
-      <c r="B51" s="32"/>
+      <c r="A51" s="29"/>
+      <c r="B51" s="33"/>
       <c r="C51" s="10" t="s">
         <v>512</v>
       </c>
@@ -18654,7 +18823,7 @@
       </c>
     </row>
     <row r="52" spans="1:4" ht="24">
-      <c r="A52" s="28"/>
+      <c r="A52" s="29"/>
       <c r="B52" s="11" t="s">
         <v>479</v>
       </c>
@@ -18666,7 +18835,7 @@
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="28"/>
+      <c r="A53" s="29"/>
       <c r="B53" s="11" t="s">
         <v>514</v>
       </c>
@@ -18676,7 +18845,7 @@
       <c r="D53" s="19"/>
     </row>
     <row r="54" spans="1:4">
-      <c r="A54" s="28"/>
+      <c r="A54" s="29"/>
       <c r="B54" s="7" t="s">
         <v>516</v>
       </c>
@@ -18686,7 +18855,7 @@
       <c r="D54" s="19"/>
     </row>
     <row r="55" spans="1:4" ht="72">
-      <c r="A55" s="28"/>
+      <c r="A55" s="29"/>
       <c r="B55" s="13" t="s">
         <v>517</v>
       </c>
@@ -18696,7 +18865,7 @@
       <c r="D55" s="19"/>
     </row>
     <row r="56" spans="1:4">
-      <c r="A56" s="28"/>
+      <c r="A56" s="29"/>
       <c r="B56" s="13" t="s">
         <v>518</v>
       </c>
@@ -18704,7 +18873,7 @@
       <c r="D56" s="19"/>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="28"/>
+      <c r="A57" s="29"/>
       <c r="B57" s="13" t="s">
         <v>519</v>
       </c>
@@ -18712,7 +18881,7 @@
       <c r="D57" s="19"/>
     </row>
     <row r="58" spans="1:4">
-      <c r="A58" s="39"/>
+      <c r="A58" s="40"/>
       <c r="B58" s="14" t="s">
         <v>520</v>
       </c>
@@ -18720,13 +18889,13 @@
       <c r="D58" s="22"/>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59" s="27" t="s">
+      <c r="A59" s="28" t="s">
         <v>523</v>
       </c>
-      <c r="B59" s="30" t="s">
+      <c r="B59" s="31" t="s">
         <v>524</v>
       </c>
-      <c r="C59" s="33" t="s">
+      <c r="C59" s="34" t="s">
         <v>525</v>
       </c>
       <c r="D59" s="18" t="s">
@@ -18734,160 +18903,160 @@
       </c>
     </row>
     <row r="60" spans="1:4">
-      <c r="A60" s="28"/>
-      <c r="B60" s="31"/>
-      <c r="C60" s="34"/>
+      <c r="A60" s="29"/>
+      <c r="B60" s="32"/>
+      <c r="C60" s="35"/>
       <c r="D60" s="19" t="s">
         <v>526</v>
       </c>
     </row>
     <row r="61" spans="1:4">
-      <c r="A61" s="28"/>
-      <c r="B61" s="31"/>
-      <c r="C61" s="34"/>
+      <c r="A61" s="29"/>
+      <c r="B61" s="32"/>
+      <c r="C61" s="35"/>
       <c r="D61" s="19" t="s">
         <v>527</v>
       </c>
     </row>
     <row r="62" spans="1:4">
-      <c r="A62" s="28"/>
-      <c r="B62" s="31"/>
-      <c r="C62" s="34"/>
+      <c r="A62" s="29"/>
+      <c r="B62" s="32"/>
+      <c r="C62" s="35"/>
       <c r="D62" s="19" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="63" spans="1:4">
-      <c r="A63" s="28"/>
-      <c r="B63" s="31"/>
-      <c r="C63" s="34"/>
+      <c r="A63" s="29"/>
+      <c r="B63" s="32"/>
+      <c r="C63" s="35"/>
       <c r="D63" s="19" t="s">
         <v>529</v>
       </c>
     </row>
     <row r="64" spans="1:4">
-      <c r="A64" s="28"/>
-      <c r="B64" s="31"/>
-      <c r="C64" s="34"/>
+      <c r="A64" s="29"/>
+      <c r="B64" s="32"/>
+      <c r="C64" s="35"/>
       <c r="D64" s="19" t="s">
         <v>530</v>
       </c>
     </row>
     <row r="65" spans="1:4">
-      <c r="A65" s="28"/>
-      <c r="B65" s="31"/>
-      <c r="C65" s="34"/>
+      <c r="A65" s="29"/>
+      <c r="B65" s="32"/>
+      <c r="C65" s="35"/>
       <c r="D65" s="19" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="66" spans="1:4">
-      <c r="A66" s="28"/>
-      <c r="B66" s="31"/>
-      <c r="C66" s="34"/>
+      <c r="A66" s="29"/>
+      <c r="B66" s="32"/>
+      <c r="C66" s="35"/>
       <c r="D66" s="19" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="67" spans="1:4">
-      <c r="A67" s="28"/>
-      <c r="B67" s="31"/>
-      <c r="C67" s="34"/>
+      <c r="A67" s="29"/>
+      <c r="B67" s="32"/>
+      <c r="C67" s="35"/>
       <c r="D67" s="19" t="s">
         <v>533</v>
       </c>
     </row>
     <row r="68" spans="1:4">
-      <c r="A68" s="28"/>
-      <c r="B68" s="31"/>
-      <c r="C68" s="34"/>
+      <c r="A68" s="29"/>
+      <c r="B68" s="32"/>
+      <c r="C68" s="35"/>
       <c r="D68" s="19" t="s">
         <v>534</v>
       </c>
     </row>
     <row r="69" spans="1:4">
-      <c r="A69" s="28"/>
-      <c r="B69" s="31"/>
-      <c r="C69" s="34"/>
+      <c r="A69" s="29"/>
+      <c r="B69" s="32"/>
+      <c r="C69" s="35"/>
       <c r="D69" s="19" t="s">
         <v>535</v>
       </c>
     </row>
     <row r="70" spans="1:4">
-      <c r="A70" s="28"/>
-      <c r="B70" s="31"/>
-      <c r="C70" s="34"/>
+      <c r="A70" s="29"/>
+      <c r="B70" s="32"/>
+      <c r="C70" s="35"/>
       <c r="D70" s="19" t="s">
         <v>536</v>
       </c>
     </row>
     <row r="71" spans="1:4">
-      <c r="A71" s="28"/>
-      <c r="B71" s="31"/>
-      <c r="C71" s="34"/>
+      <c r="A71" s="29"/>
+      <c r="B71" s="32"/>
+      <c r="C71" s="35"/>
       <c r="D71" s="19" t="s">
         <v>537</v>
       </c>
     </row>
     <row r="72" spans="1:4">
-      <c r="A72" s="28"/>
-      <c r="B72" s="31"/>
-      <c r="C72" s="34"/>
+      <c r="A72" s="29"/>
+      <c r="B72" s="32"/>
+      <c r="C72" s="35"/>
       <c r="D72" s="19" t="s">
         <v>538</v>
       </c>
     </row>
     <row r="73" spans="1:4">
-      <c r="A73" s="28"/>
-      <c r="B73" s="31"/>
-      <c r="C73" s="34"/>
+      <c r="A73" s="29"/>
+      <c r="B73" s="32"/>
+      <c r="C73" s="35"/>
       <c r="D73" s="19" t="s">
         <v>539</v>
       </c>
     </row>
     <row r="74" spans="1:4">
-      <c r="A74" s="28"/>
-      <c r="B74" s="31"/>
-      <c r="C74" s="34"/>
+      <c r="A74" s="29"/>
+      <c r="B74" s="32"/>
+      <c r="C74" s="35"/>
       <c r="D74" s="19" t="s">
         <v>540</v>
       </c>
     </row>
     <row r="75" spans="1:4">
-      <c r="A75" s="28"/>
-      <c r="B75" s="31"/>
-      <c r="C75" s="34"/>
+      <c r="A75" s="29"/>
+      <c r="B75" s="32"/>
+      <c r="C75" s="35"/>
       <c r="D75" s="19" t="s">
         <v>541</v>
       </c>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76" s="28"/>
-      <c r="B76" s="31"/>
-      <c r="C76" s="34"/>
+      <c r="A76" s="29"/>
+      <c r="B76" s="32"/>
+      <c r="C76" s="35"/>
       <c r="D76" s="19" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="77" spans="1:4">
-      <c r="A77" s="28"/>
-      <c r="B77" s="31"/>
-      <c r="C77" s="34"/>
+      <c r="A77" s="29"/>
+      <c r="B77" s="32"/>
+      <c r="C77" s="35"/>
       <c r="D77" s="19" t="s">
         <v>543</v>
       </c>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="28"/>
-      <c r="B78" s="32"/>
-      <c r="C78" s="35"/>
+      <c r="A78" s="29"/>
+      <c r="B78" s="33"/>
+      <c r="C78" s="36"/>
       <c r="D78" s="19" t="s">
         <v>544</v>
       </c>
     </row>
     <row r="79" spans="1:4">
-      <c r="A79" s="28"/>
-      <c r="B79" s="30" t="s">
+      <c r="A79" s="29"/>
+      <c r="B79" s="31" t="s">
         <v>547</v>
       </c>
       <c r="C79" s="8" t="s">
@@ -18896,8 +19065,8 @@
       <c r="D79" s="20"/>
     </row>
     <row r="80" spans="1:4">
-      <c r="A80" s="28"/>
-      <c r="B80" s="32"/>
+      <c r="A80" s="29"/>
+      <c r="B80" s="33"/>
       <c r="C80" s="10" t="s">
         <v>549</v>
       </c>
@@ -18906,7 +19075,7 @@
       </c>
     </row>
     <row r="81" spans="1:4" ht="36">
-      <c r="A81" s="28"/>
+      <c r="A81" s="29"/>
       <c r="B81" s="11" t="s">
         <v>550</v>
       </c>
@@ -18918,7 +19087,7 @@
       </c>
     </row>
     <row r="82" spans="1:4">
-      <c r="A82" s="28"/>
+      <c r="A82" s="29"/>
       <c r="B82" s="11" t="s">
         <v>552</v>
       </c>
@@ -18928,7 +19097,7 @@
       <c r="D82" s="20"/>
     </row>
     <row r="83" spans="1:4">
-      <c r="A83" s="28"/>
+      <c r="A83" s="29"/>
       <c r="B83" s="11" t="s">
         <v>554</v>
       </c>
@@ -18940,7 +19109,7 @@
       </c>
     </row>
     <row r="84" spans="1:4" ht="24">
-      <c r="A84" s="28"/>
+      <c r="A84" s="29"/>
       <c r="B84" s="11" t="s">
         <v>556</v>
       </c>
@@ -18952,7 +19121,7 @@
       </c>
     </row>
     <row r="85" spans="1:4">
-      <c r="A85" s="28"/>
+      <c r="A85" s="29"/>
       <c r="B85" s="7" t="s">
         <v>558</v>
       </c>
@@ -18960,7 +19129,7 @@
       <c r="D85" s="19"/>
     </row>
     <row r="86" spans="1:4">
-      <c r="A86" s="28"/>
+      <c r="A86" s="29"/>
       <c r="B86" s="13" t="s">
         <v>559</v>
       </c>
@@ -18970,7 +19139,7 @@
       <c r="D86" s="19"/>
     </row>
     <row r="87" spans="1:4" ht="120">
-      <c r="A87" s="28"/>
+      <c r="A87" s="29"/>
       <c r="B87" s="13" t="s">
         <v>813</v>
       </c>
@@ -18980,7 +19149,7 @@
       <c r="D87" s="19"/>
     </row>
     <row r="88" spans="1:4">
-      <c r="A88" s="28"/>
+      <c r="A88" s="29"/>
       <c r="B88" s="13" t="s">
         <v>560</v>
       </c>
@@ -18988,7 +19157,7 @@
       <c r="D88" s="19"/>
     </row>
     <row r="89" spans="1:4">
-      <c r="A89" s="29"/>
+      <c r="A89" s="30"/>
       <c r="B89" s="23" t="s">
         <v>520</v>
       </c>
@@ -19021,8 +19190,8 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:A56"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A31"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="89.75" customWidth="1"/>
@@ -19035,340 +19204,187 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="26" t="s">
-        <v>1486</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="26" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="26" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="26" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="26" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="26" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="26" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="26" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="26" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="26" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="26" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="26" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="26" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="26" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="26" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="26" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="26" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="26" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="26" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="26" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="26" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="26" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="26" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="26" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="26" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="26" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="26" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="26" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="26" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="26" t="s">
-        <v>1515</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="26" t="s">
-        <v>1516</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="26" t="s">
-        <v>1517</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="26" t="s">
-        <v>1521</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="26" t="s">
-        <v>1522</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="26" t="s">
-        <v>1523</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="26" t="s">
-        <v>1524</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" s="26" t="s">
-        <v>1525</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="26" t="s">
-        <v>1526</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
-      <c r="A40" s="26" t="s">
-        <v>1527</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="26" t="s">
-        <v>1528</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="26" t="s">
-        <v>1529</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="26" t="s">
-        <v>1543</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" s="26" t="s">
-        <v>1530</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="26" t="s">
-        <v>1531</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="26" t="s">
-        <v>1532</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" s="26" t="s">
-        <v>1533</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="26" t="s">
-        <v>1534</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="26" t="s">
-        <v>1535</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="26" t="s">
-        <v>1536</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" s="26" t="s">
-        <v>1537</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="26" t="s">
-        <v>1538</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="26" t="s">
-        <v>1539</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" s="26" t="s">
-        <v>1540</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="26" t="s">
-        <v>1541</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" s="26" t="s">
-        <v>1542</v>
-      </c>
+      <c r="A31" s="26"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
-    <hyperlink ref="A2" r:id="rId2" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
-    <hyperlink ref="A3" r:id="rId3" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
-    <hyperlink ref="A4" r:id="rId4" xr:uid="{00000000-0004-0000-0500-000003000000}"/>
-    <hyperlink ref="A5" r:id="rId5" xr:uid="{00000000-0004-0000-0500-000004000000}"/>
-    <hyperlink ref="A6" r:id="rId6" xr:uid="{00000000-0004-0000-0500-000005000000}"/>
-    <hyperlink ref="A7" r:id="rId7" xr:uid="{00000000-0004-0000-0500-000006000000}"/>
-    <hyperlink ref="A8" r:id="rId8" xr:uid="{00000000-0004-0000-0500-000007000000}"/>
-    <hyperlink ref="A9" r:id="rId9" xr:uid="{00000000-0004-0000-0500-000008000000}"/>
-    <hyperlink ref="A10" r:id="rId10" xr:uid="{00000000-0004-0000-0500-000009000000}"/>
-    <hyperlink ref="A11" r:id="rId11" xr:uid="{00000000-0004-0000-0500-00000A000000}"/>
-    <hyperlink ref="A12" r:id="rId12" xr:uid="{00000000-0004-0000-0500-00000B000000}"/>
-    <hyperlink ref="A13" r:id="rId13" xr:uid="{00000000-0004-0000-0500-00000C000000}"/>
-    <hyperlink ref="A14" r:id="rId14" xr:uid="{00000000-0004-0000-0500-00000D000000}"/>
-    <hyperlink ref="A15" r:id="rId15" xr:uid="{00000000-0004-0000-0500-00000E000000}"/>
-    <hyperlink ref="A16" r:id="rId16" xr:uid="{00000000-0004-0000-0500-00000F000000}"/>
-    <hyperlink ref="A17" r:id="rId17" xr:uid="{00000000-0004-0000-0500-000010000000}"/>
-    <hyperlink ref="A18" r:id="rId18" xr:uid="{00000000-0004-0000-0500-000011000000}"/>
-    <hyperlink ref="A19" r:id="rId19" xr:uid="{00000000-0004-0000-0500-000012000000}"/>
-    <hyperlink ref="A20" r:id="rId20" xr:uid="{00000000-0004-0000-0500-000013000000}"/>
-    <hyperlink ref="A21" r:id="rId21" xr:uid="{00000000-0004-0000-0500-000014000000}"/>
-    <hyperlink ref="A22" r:id="rId22" xr:uid="{00000000-0004-0000-0500-000015000000}"/>
-    <hyperlink ref="A23" r:id="rId23" xr:uid="{00000000-0004-0000-0500-000016000000}"/>
-    <hyperlink ref="A24" r:id="rId24" xr:uid="{00000000-0004-0000-0500-000017000000}"/>
-    <hyperlink ref="A25" r:id="rId25" xr:uid="{00000000-0004-0000-0500-000018000000}"/>
-    <hyperlink ref="A26" r:id="rId26" xr:uid="{00000000-0004-0000-0500-000019000000}"/>
-    <hyperlink ref="A27" r:id="rId27" xr:uid="{00000000-0004-0000-0500-00001A000000}"/>
-    <hyperlink ref="A28" r:id="rId28" xr:uid="{00000000-0004-0000-0500-00001B000000}"/>
-    <hyperlink ref="A29" r:id="rId29" xr:uid="{00000000-0004-0000-0500-00001C000000}"/>
-    <hyperlink ref="A30" r:id="rId30" xr:uid="{00000000-0004-0000-0500-00001D000000}"/>
-    <hyperlink ref="A31" r:id="rId31" xr:uid="{00000000-0004-0000-0500-00001E000000}"/>
-    <hyperlink ref="A56" r:id="rId32" xr:uid="{00000000-0004-0000-0500-00001F000000}"/>
-    <hyperlink ref="A55" r:id="rId33" xr:uid="{00000000-0004-0000-0500-000020000000}"/>
-    <hyperlink ref="A37" r:id="rId34" xr:uid="{00000000-0004-0000-0500-000021000000}"/>
-    <hyperlink ref="A32" r:id="rId35" xr:uid="{00000000-0004-0000-0500-000022000000}"/>
-    <hyperlink ref="A33" r:id="rId36" xr:uid="{00000000-0004-0000-0500-000023000000}"/>
-    <hyperlink ref="A34" r:id="rId37" xr:uid="{00000000-0004-0000-0500-000024000000}"/>
-    <hyperlink ref="A35" r:id="rId38" xr:uid="{00000000-0004-0000-0500-000025000000}"/>
-    <hyperlink ref="A36" r:id="rId39" xr:uid="{00000000-0004-0000-0500-000026000000}"/>
-    <hyperlink ref="A38" r:id="rId40" xr:uid="{00000000-0004-0000-0500-000027000000}"/>
-    <hyperlink ref="A39" r:id="rId41" xr:uid="{00000000-0004-0000-0500-000028000000}"/>
-    <hyperlink ref="A40" r:id="rId42" xr:uid="{00000000-0004-0000-0500-000029000000}"/>
-    <hyperlink ref="A41" r:id="rId43" xr:uid="{00000000-0004-0000-0500-00002A000000}"/>
-    <hyperlink ref="A42" r:id="rId44" xr:uid="{00000000-0004-0000-0500-00002B000000}"/>
-    <hyperlink ref="A44" r:id="rId45" xr:uid="{00000000-0004-0000-0500-00002C000000}"/>
-    <hyperlink ref="A45" r:id="rId46" xr:uid="{00000000-0004-0000-0500-00002D000000}"/>
-    <hyperlink ref="A46" r:id="rId47" xr:uid="{00000000-0004-0000-0500-00002E000000}"/>
-    <hyperlink ref="A47" r:id="rId48" xr:uid="{00000000-0004-0000-0500-00002F000000}"/>
-    <hyperlink ref="A48" r:id="rId49" xr:uid="{00000000-0004-0000-0500-000030000000}"/>
-    <hyperlink ref="A49" r:id="rId50" xr:uid="{00000000-0004-0000-0500-000031000000}"/>
-    <hyperlink ref="A50" r:id="rId51" xr:uid="{00000000-0004-0000-0500-000032000000}"/>
-    <hyperlink ref="A51" r:id="rId52" xr:uid="{00000000-0004-0000-0500-000033000000}"/>
-    <hyperlink ref="A52" r:id="rId53" xr:uid="{00000000-0004-0000-0500-000034000000}"/>
-    <hyperlink ref="A53" r:id="rId54" xr:uid="{00000000-0004-0000-0500-000035000000}"/>
-    <hyperlink ref="A54" r:id="rId55" xr:uid="{00000000-0004-0000-0500-000036000000}"/>
-    <hyperlink ref="A43" r:id="rId56" xr:uid="{00000000-0004-0000-0500-000037000000}"/>
+    <hyperlink ref="A1" r:id="rId1"/>
+    <hyperlink ref="A2" r:id="rId2"/>
+    <hyperlink ref="A3" r:id="rId3"/>
+    <hyperlink ref="A4" r:id="rId4"/>
+    <hyperlink ref="A5" r:id="rId5"/>
+    <hyperlink ref="A6" r:id="rId6"/>
+    <hyperlink ref="A7" r:id="rId7"/>
+    <hyperlink ref="A8" r:id="rId8"/>
+    <hyperlink ref="A9" r:id="rId9"/>
+    <hyperlink ref="A10" r:id="rId10"/>
+    <hyperlink ref="A11" r:id="rId11"/>
+    <hyperlink ref="A12" r:id="rId12"/>
+    <hyperlink ref="A13" r:id="rId13"/>
+    <hyperlink ref="A14" r:id="rId14"/>
+    <hyperlink ref="A15" r:id="rId15"/>
+    <hyperlink ref="A16" r:id="rId16"/>
+    <hyperlink ref="A17" r:id="rId17"/>
+    <hyperlink ref="A18" r:id="rId18"/>
+    <hyperlink ref="A19" r:id="rId19"/>
+    <hyperlink ref="A20" r:id="rId20"/>
+    <hyperlink ref="A21" r:id="rId21"/>
+    <hyperlink ref="A22" r:id="rId22"/>
+    <hyperlink ref="A23" r:id="rId23"/>
+    <hyperlink ref="A24" r:id="rId24"/>
+    <hyperlink ref="A25" r:id="rId25"/>
+    <hyperlink ref="A26" r:id="rId26"/>
+    <hyperlink ref="A27" r:id="rId27"/>
+    <hyperlink ref="A28" r:id="rId28"/>
+    <hyperlink ref="A29" r:id="rId29"/>
+    <hyperlink ref="A30" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId57"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId31"/>
 </worksheet>
 </file>
--- a/notes/langnote.xlsx
+++ b/notes/langnote.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10414"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\gitlab\langnote\notes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ibqo/Develop/git/github/LangNote/notes/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D3C61F1-74A3-6C44-8B17-B70DEDA5E297}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5205" yWindow="1110" windowWidth="22485" windowHeight="11295" firstSheet="3" activeTab="9"/>
+    <workbookView xWindow="5200" yWindow="1120" windowWidth="22480" windowHeight="11300" firstSheet="2" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2014" sheetId="9" r:id="rId1"/>
@@ -22,6 +23,7 @@
     <sheet name="2018年JavaEE课程大纲" sheetId="3" r:id="rId8"/>
     <sheet name="CVS repo" sheetId="6" r:id="rId9"/>
     <sheet name="CVS repo github" sheetId="10" r:id="rId10"/>
+    <sheet name="2021计划" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1984" uniqueCount="1905">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2082" uniqueCount="2003">
   <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -6926,11 +6928,319 @@
     <t>git@gitee.com:edidada/testjava11.git</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>20210101</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20210102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20210103</t>
+  </si>
+  <si>
+    <t>20210104</t>
+  </si>
+  <si>
+    <t>20210105</t>
+  </si>
+  <si>
+    <t>20210106</t>
+  </si>
+  <si>
+    <t>20210107</t>
+  </si>
+  <si>
+    <t>20210108</t>
+  </si>
+  <si>
+    <t>20210109</t>
+  </si>
+  <si>
+    <t>20210110</t>
+  </si>
+  <si>
+    <t>20210111</t>
+  </si>
+  <si>
+    <t>20210112</t>
+  </si>
+  <si>
+    <t>20210113</t>
+  </si>
+  <si>
+    <t>20210114</t>
+  </si>
+  <si>
+    <t>20210115</t>
+  </si>
+  <si>
+    <t>20210116</t>
+  </si>
+  <si>
+    <t>20210117</t>
+  </si>
+  <si>
+    <t>20210118</t>
+  </si>
+  <si>
+    <t>20210119</t>
+  </si>
+  <si>
+    <t>20210120</t>
+  </si>
+  <si>
+    <t>20210121</t>
+  </si>
+  <si>
+    <t>20210122</t>
+  </si>
+  <si>
+    <t>20210123</t>
+  </si>
+  <si>
+    <t>20210124</t>
+  </si>
+  <si>
+    <t>20210125</t>
+  </si>
+  <si>
+    <t>20210126</t>
+  </si>
+  <si>
+    <t>20210127</t>
+  </si>
+  <si>
+    <t>20210128</t>
+  </si>
+  <si>
+    <t>20210129</t>
+  </si>
+  <si>
+    <t>20210130</t>
+  </si>
+  <si>
+    <t>20210131</t>
+  </si>
+  <si>
+    <t>20210201</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20210202</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20210203</t>
+  </si>
+  <si>
+    <t>20210204</t>
+  </si>
+  <si>
+    <t>20210205</t>
+  </si>
+  <si>
+    <t>20210206</t>
+  </si>
+  <si>
+    <t>20210207</t>
+  </si>
+  <si>
+    <t>20210208</t>
+  </si>
+  <si>
+    <t>20210209</t>
+  </si>
+  <si>
+    <t>20210210</t>
+  </si>
+  <si>
+    <t>20210211</t>
+  </si>
+  <si>
+    <t>20210212</t>
+  </si>
+  <si>
+    <t>20210213</t>
+  </si>
+  <si>
+    <t>20210214</t>
+  </si>
+  <si>
+    <t>20210215</t>
+  </si>
+  <si>
+    <t>20210216</t>
+  </si>
+  <si>
+    <t>20210217</t>
+  </si>
+  <si>
+    <t>20210218</t>
+  </si>
+  <si>
+    <t>20210219</t>
+  </si>
+  <si>
+    <t>20210220</t>
+  </si>
+  <si>
+    <t>20210221</t>
+  </si>
+  <si>
+    <t>20210222</t>
+  </si>
+  <si>
+    <t>20210223</t>
+  </si>
+  <si>
+    <t>20210224</t>
+  </si>
+  <si>
+    <t>20210225</t>
+  </si>
+  <si>
+    <t>20210226</t>
+  </si>
+  <si>
+    <t>20210227</t>
+  </si>
+  <si>
+    <t>20210228</t>
+  </si>
+  <si>
+    <t>20210301</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20210302</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20210303</t>
+  </si>
+  <si>
+    <t>20210304</t>
+  </si>
+  <si>
+    <t>20210305</t>
+  </si>
+  <si>
+    <t>20210306</t>
+  </si>
+  <si>
+    <t>20210307</t>
+  </si>
+  <si>
+    <t>20210308</t>
+  </si>
+  <si>
+    <t>20210309</t>
+  </si>
+  <si>
+    <t>20210310</t>
+  </si>
+  <si>
+    <t>20210311</t>
+  </si>
+  <si>
+    <t>20210312</t>
+  </si>
+  <si>
+    <t>20210313</t>
+  </si>
+  <si>
+    <t>20210314</t>
+  </si>
+  <si>
+    <t>20210315</t>
+  </si>
+  <si>
+    <t>20210316</t>
+  </si>
+  <si>
+    <t>20210317</t>
+  </si>
+  <si>
+    <t>20210318</t>
+  </si>
+  <si>
+    <t>20210319</t>
+  </si>
+  <si>
+    <t>20210320</t>
+  </si>
+  <si>
+    <t>20210321</t>
+  </si>
+  <si>
+    <t>20210322</t>
+  </si>
+  <si>
+    <t>20210323</t>
+  </si>
+  <si>
+    <t>20210324</t>
+  </si>
+  <si>
+    <t>20210325</t>
+  </si>
+  <si>
+    <t>20210326</t>
+  </si>
+  <si>
+    <t>20210327</t>
+  </si>
+  <si>
+    <t>20210328</t>
+  </si>
+  <si>
+    <t>20210329</t>
+  </si>
+  <si>
+    <t>20210330</t>
+  </si>
+  <si>
+    <t>20210331</t>
+  </si>
+  <si>
+    <t>后端技术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人文修养</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算机技术 OS 编译原理 编程语言 AI 机器学习 音视频</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Java 数据库 架构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金融专业知识</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>从业资格 证券 会计 金融风险管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mysql 回顾 c++ Java API demo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>索引类型 高可用架构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="21">
     <font>
       <sz val="11"/>
@@ -7756,9 +8066,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B42"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
@@ -7999,9 +8309,9 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:A26"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="26" t="s">
@@ -8136,43 +8446,536 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1"/>
-    <hyperlink ref="A26" r:id="rId2"/>
-    <hyperlink ref="A25" r:id="rId3"/>
-    <hyperlink ref="A7" r:id="rId4"/>
-    <hyperlink ref="A2" r:id="rId5"/>
-    <hyperlink ref="A3" r:id="rId6"/>
-    <hyperlink ref="A4" r:id="rId7"/>
-    <hyperlink ref="A5" r:id="rId8"/>
-    <hyperlink ref="A6" r:id="rId9"/>
-    <hyperlink ref="A8" r:id="rId10"/>
-    <hyperlink ref="A9" r:id="rId11"/>
-    <hyperlink ref="A10" r:id="rId12"/>
-    <hyperlink ref="A11" r:id="rId13"/>
-    <hyperlink ref="A12" r:id="rId14"/>
-    <hyperlink ref="A14" r:id="rId15"/>
-    <hyperlink ref="A15" r:id="rId16"/>
-    <hyperlink ref="A16" r:id="rId17"/>
-    <hyperlink ref="A17" r:id="rId18"/>
-    <hyperlink ref="A18" r:id="rId19"/>
-    <hyperlink ref="A19" r:id="rId20"/>
-    <hyperlink ref="A20" r:id="rId21"/>
-    <hyperlink ref="A21" r:id="rId22"/>
-    <hyperlink ref="A22" r:id="rId23"/>
-    <hyperlink ref="A23" r:id="rId24"/>
-    <hyperlink ref="A24" r:id="rId25"/>
-    <hyperlink ref="A13" r:id="rId26"/>
+    <hyperlink ref="A1" r:id="rId1" xr:uid="{00000000-0004-0000-0900-000000000000}"/>
+    <hyperlink ref="A26" r:id="rId2" xr:uid="{00000000-0004-0000-0900-000001000000}"/>
+    <hyperlink ref="A25" r:id="rId3" xr:uid="{00000000-0004-0000-0900-000002000000}"/>
+    <hyperlink ref="A7" r:id="rId4" xr:uid="{00000000-0004-0000-0900-000003000000}"/>
+    <hyperlink ref="A2" r:id="rId5" xr:uid="{00000000-0004-0000-0900-000004000000}"/>
+    <hyperlink ref="A3" r:id="rId6" xr:uid="{00000000-0004-0000-0900-000005000000}"/>
+    <hyperlink ref="A4" r:id="rId7" xr:uid="{00000000-0004-0000-0900-000006000000}"/>
+    <hyperlink ref="A5" r:id="rId8" xr:uid="{00000000-0004-0000-0900-000007000000}"/>
+    <hyperlink ref="A6" r:id="rId9" xr:uid="{00000000-0004-0000-0900-000008000000}"/>
+    <hyperlink ref="A8" r:id="rId10" xr:uid="{00000000-0004-0000-0900-000009000000}"/>
+    <hyperlink ref="A9" r:id="rId11" xr:uid="{00000000-0004-0000-0900-00000A000000}"/>
+    <hyperlink ref="A10" r:id="rId12" xr:uid="{00000000-0004-0000-0900-00000B000000}"/>
+    <hyperlink ref="A11" r:id="rId13" xr:uid="{00000000-0004-0000-0900-00000C000000}"/>
+    <hyperlink ref="A12" r:id="rId14" xr:uid="{00000000-0004-0000-0900-00000D000000}"/>
+    <hyperlink ref="A14" r:id="rId15" xr:uid="{00000000-0004-0000-0900-00000E000000}"/>
+    <hyperlink ref="A15" r:id="rId16" xr:uid="{00000000-0004-0000-0900-00000F000000}"/>
+    <hyperlink ref="A16" r:id="rId17" xr:uid="{00000000-0004-0000-0900-000010000000}"/>
+    <hyperlink ref="A17" r:id="rId18" xr:uid="{00000000-0004-0000-0900-000011000000}"/>
+    <hyperlink ref="A18" r:id="rId19" xr:uid="{00000000-0004-0000-0900-000012000000}"/>
+    <hyperlink ref="A19" r:id="rId20" xr:uid="{00000000-0004-0000-0900-000013000000}"/>
+    <hyperlink ref="A20" r:id="rId21" xr:uid="{00000000-0004-0000-0900-000014000000}"/>
+    <hyperlink ref="A21" r:id="rId22" xr:uid="{00000000-0004-0000-0900-000015000000}"/>
+    <hyperlink ref="A22" r:id="rId23" xr:uid="{00000000-0004-0000-0900-000016000000}"/>
+    <hyperlink ref="A23" r:id="rId24" xr:uid="{00000000-0004-0000-0900-000017000000}"/>
+    <hyperlink ref="A24" r:id="rId25" xr:uid="{00000000-0004-0000-0900-000018000000}"/>
+    <hyperlink ref="A13" r:id="rId26" xr:uid="{00000000-0004-0000-0900-000019000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DC7242D-34A4-514D-94C8-37221C34C339}">
+  <dimension ref="A1:C100"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>1995</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="1" t="s">
+        <v>1905</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="1" t="s">
+        <v>1906</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="1" t="s">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="1" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="1" t="s">
+        <v>1909</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="1" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="s">
+        <v>1912</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="1" t="s">
+        <v>1914</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="1" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="1" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="1" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="1" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="1" t="s">
+        <v>1923</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="1" t="s">
+        <v>1924</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="1" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="1" t="s">
+        <v>1926</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1" t="s">
+        <v>1927</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="1" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>1929</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="1" t="s">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="1" t="s">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="1" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="1" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="1" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="1" t="s">
+        <v>1940</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="1" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="1" t="s">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="1" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="1" t="s">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="1" t="s">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="1" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="1" t="s">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="1" t="s">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="1" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="1" t="s">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="1" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="1" t="s">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="1" t="s">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="1" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="1" t="s">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="1" t="s">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="1" t="s">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" s="1" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="1" t="s">
+        <v>1960</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="1" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" s="1" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" s="1" t="s">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" s="1" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" s="1" t="s">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" s="1" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" s="1" t="s">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" s="1" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="1" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="1" t="s">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" s="1" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" s="1" t="s">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" s="1" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="1" t="s">
+        <v>1974</v>
+      </c>
+      <c r="B80" t="s">
+        <v>2001</v>
+      </c>
+      <c r="C80" t="s">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="1" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="1" t="s">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="1" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="1" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="1" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="1" t="s">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="1" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="1" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="1" t="s">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="1" t="s">
+        <v>1984</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="1" t="s">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="1" t="s">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="1" t="s">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="1" t="s">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="1" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="1" t="s">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="1" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="1" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="1" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="1" t="s">
+        <v>1994</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="24.75" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8215,7 +9018,7 @@
         <v>1876</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="40.5">
+    <row r="6" spans="1:3" ht="45">
       <c r="A6" s="1" t="s">
         <v>1852</v>
       </c>
@@ -8228,7 +9031,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="27">
+    <row r="8" spans="1:3" ht="30">
       <c r="A8" s="1" t="s">
         <v>1854</v>
       </c>
@@ -8272,11 +9075,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="21.75" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8358,16 +9161,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G366"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="54.875" customWidth="1"/>
-    <col min="3" max="3" width="30.75" customWidth="1"/>
-    <col min="4" max="4" width="40.375" customWidth="1"/>
-    <col min="5" max="5" width="31.375" customWidth="1"/>
-    <col min="6" max="6" width="21.125" customWidth="1"/>
+    <col min="2" max="2" width="54.83203125" customWidth="1"/>
+    <col min="3" max="3" width="30.6640625" customWidth="1"/>
+    <col min="4" max="4" width="40.33203125" customWidth="1"/>
+    <col min="5" max="5" width="31.33203125" customWidth="1"/>
+    <col min="6" max="6" width="21.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -8378,7 +9181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="24.6" customHeight="1">
+    <row r="2" spans="1:2" ht="24.5" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1003</v>
       </c>
@@ -8463,7 +9266,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="27">
+    <row r="19" spans="1:5" ht="30">
       <c r="A19" s="1" t="s">
         <v>1020</v>
       </c>
@@ -8554,12 +9357,12 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="11.45" customHeight="1">
+    <row r="27" spans="1:5" ht="11.5" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>1028</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="11.45" customHeight="1">
+    <row r="28" spans="1:5" ht="11.5" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>1029</v>
       </c>
@@ -8567,7 +9370,7 @@
         <v>1902</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="11.45" customHeight="1">
+    <row r="29" spans="1:5" ht="11.5" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>1030</v>
       </c>
@@ -8575,17 +9378,17 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="11.45" customHeight="1">
+    <row r="30" spans="1:5" ht="11.5" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>1031</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="11.45" customHeight="1">
+    <row r="31" spans="1:5" ht="11.5" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>1032</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="11.45" customHeight="1">
+    <row r="32" spans="1:5" ht="11.5" customHeight="1">
       <c r="A32" s="1" t="s">
         <v>1033</v>
       </c>
@@ -8671,7 +9474,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="35.450000000000003" customHeight="1">
+    <row r="45" spans="1:6" ht="35.5" customHeight="1">
       <c r="A45" s="1" t="s">
         <v>10</v>
       </c>
@@ -8799,7 +9602,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="40.5">
+    <row r="58" spans="1:5" ht="45">
       <c r="A58" s="1" t="s">
         <v>34</v>
       </c>
@@ -8818,7 +9621,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="27">
+    <row r="60" spans="1:5" ht="30">
       <c r="A60" s="1" t="s">
         <v>39</v>
       </c>
@@ -8867,7 +9670,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" ht="15">
       <c r="A65" s="1" t="s">
         <v>57</v>
       </c>
@@ -8875,7 +9678,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" ht="15">
       <c r="A66" s="1" t="s">
         <v>58</v>
       </c>
@@ -8947,7 +9750,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" ht="15">
       <c r="A72" s="1" t="s">
         <v>67</v>
       </c>
@@ -8988,7 +9791,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" ht="15">
       <c r="A76" s="1" t="s">
         <v>92</v>
       </c>
@@ -9181,7 +9984,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="40.5">
+    <row r="102" spans="1:3" ht="45">
       <c r="A102" s="1" t="s">
         <v>121</v>
       </c>
@@ -9312,7 +10115,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:6" ht="15">
       <c r="A121" s="1" t="s">
         <v>149</v>
       </c>
@@ -10760,19 +11563,19 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L368"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="28.25" customWidth="1"/>
+    <col min="1" max="1" width="28.1640625" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
-    <col min="3" max="3" width="31.375" customWidth="1"/>
-    <col min="4" max="4" width="55.125" customWidth="1"/>
-    <col min="5" max="5" width="33.375" customWidth="1"/>
+    <col min="3" max="3" width="31.33203125" customWidth="1"/>
+    <col min="4" max="4" width="55.1640625" customWidth="1"/>
+    <col min="5" max="5" width="33.33203125" customWidth="1"/>
     <col min="6" max="6" width="18.5" customWidth="1"/>
     <col min="7" max="7" width="25.5" customWidth="1"/>
-    <col min="8" max="8" width="17.25" customWidth="1"/>
-    <col min="9" max="9" width="18.375" customWidth="1"/>
+    <col min="8" max="8" width="17.1640625" customWidth="1"/>
+    <col min="9" max="9" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -11389,7 +12192,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="40.5">
+    <row r="104" spans="1:9" ht="45">
       <c r="A104" s="1" t="s">
         <v>237</v>
       </c>
@@ -11423,7 +12226,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="40.5">
+    <row r="106" spans="1:9" ht="45">
       <c r="A106" s="1" t="s">
         <v>239</v>
       </c>
@@ -11482,7 +12285,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="27">
+    <row r="110" spans="1:9" ht="30">
       <c r="A110" s="1" t="s">
         <v>241</v>
       </c>
@@ -11545,7 +12348,7 @@
         <v>1793</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="94.5">
+    <row r="116" spans="1:9" ht="105">
       <c r="A116" s="1" t="s">
         <v>246</v>
       </c>
@@ -11574,7 +12377,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="27">
+    <row r="117" spans="1:9" ht="30">
       <c r="A117" s="1" t="s">
         <v>247</v>
       </c>
@@ -11613,7 +12416,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="27">
+    <row r="120" spans="1:9" ht="30">
       <c r="A120" s="1" t="s">
         <v>250</v>
       </c>
@@ -11635,7 +12438,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="27">
+    <row r="122" spans="1:9" ht="30">
       <c r="A122" s="1" t="s">
         <v>252</v>
       </c>
@@ -11646,7 +12449,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="27">
+    <row r="123" spans="1:9" ht="30">
       <c r="A123" s="1" t="s">
         <v>253</v>
       </c>
@@ -11654,7 +12457,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="54">
+    <row r="124" spans="1:9" ht="60">
       <c r="A124" s="1" t="s">
         <v>286</v>
       </c>
@@ -11735,7 +12538,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="130" spans="1:6" ht="27">
+    <row r="130" spans="1:6" ht="30">
       <c r="A130" s="1" t="s">
         <v>292</v>
       </c>
@@ -11808,7 +12611,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="135" spans="1:6" ht="27">
+    <row r="135" spans="1:6" ht="30">
       <c r="A135" s="1" t="s">
         <v>297</v>
       </c>
@@ -11838,7 +12641,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="138" spans="1:6" ht="27">
+    <row r="138" spans="1:6" ht="30">
       <c r="A138" s="1" t="s">
         <v>300</v>
       </c>
@@ -11940,7 +12743,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="15">
+    <row r="147" spans="1:5" ht="16">
       <c r="A147" s="1" t="s">
         <v>309</v>
       </c>
@@ -11957,7 +12760,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="27">
+    <row r="148" spans="1:5" ht="30">
       <c r="A148" s="1" t="s">
         <v>310</v>
       </c>
@@ -11971,7 +12774,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="27">
+    <row r="149" spans="1:5" ht="30">
       <c r="A149" s="1" t="s">
         <v>311</v>
       </c>
@@ -11993,7 +12796,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="40.5">
+    <row r="151" spans="1:5" ht="45">
       <c r="A151" s="1" t="s">
         <v>313</v>
       </c>
@@ -12015,7 +12818,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="27">
+    <row r="153" spans="1:5" ht="30">
       <c r="A153" s="1" t="s">
         <v>315</v>
       </c>
@@ -12060,7 +12863,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="27">
+    <row r="159" spans="1:5" ht="30">
       <c r="A159" s="1" t="s">
         <v>335</v>
       </c>
@@ -12087,7 +12890,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="27">
+    <row r="162" spans="1:8" ht="30">
       <c r="A162" s="1" t="s">
         <v>338</v>
       </c>
@@ -12120,7 +12923,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="27">
+    <row r="165" spans="1:8" ht="30">
       <c r="A165" s="1" t="s">
         <v>341</v>
       </c>
@@ -12140,7 +12943,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="54">
+    <row r="166" spans="1:8" ht="60">
       <c r="A166" s="1" t="s">
         <v>342</v>
       </c>
@@ -12203,7 +13006,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="40.5">
+    <row r="172" spans="1:8" ht="45">
       <c r="A172" s="1" t="s">
         <v>348</v>
       </c>
@@ -12248,7 +13051,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="27">
+    <row r="175" spans="1:8" ht="30">
       <c r="A175" s="1" t="s">
         <v>351</v>
       </c>
@@ -12267,7 +13070,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="27">
+    <row r="177" spans="1:6" ht="30">
       <c r="A177" s="1" t="s">
         <v>353</v>
       </c>
@@ -12278,7 +13081,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="178" spans="1:6" ht="27">
+    <row r="178" spans="1:6" ht="30">
       <c r="A178" s="1" t="s">
         <v>354</v>
       </c>
@@ -12289,7 +13092,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="179" spans="1:6">
+    <row r="179" spans="1:6" ht="15">
       <c r="A179" s="1" t="s">
         <v>355</v>
       </c>
@@ -12428,7 +13231,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="190" spans="1:6" ht="40.5">
+    <row r="190" spans="1:6" ht="45">
       <c r="A190" s="1" t="s">
         <v>383</v>
       </c>
@@ -12442,7 +13245,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="27">
+    <row r="191" spans="1:6" ht="30">
       <c r="A191" s="1" t="s">
         <v>384</v>
       </c>
@@ -12467,7 +13270,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="193" spans="1:7" ht="54">
+    <row r="193" spans="1:7" ht="60">
       <c r="A193" s="1" t="s">
         <v>386</v>
       </c>
@@ -12509,7 +13312,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="196" spans="1:7" ht="27">
+    <row r="196" spans="1:7" ht="30">
       <c r="A196" s="1" t="s">
         <v>389</v>
       </c>
@@ -12534,7 +13337,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="198" spans="1:7" ht="27">
+    <row r="198" spans="1:7" ht="30">
       <c r="A198" s="1" t="s">
         <v>391</v>
       </c>
@@ -12559,7 +13362,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="200" spans="1:7" ht="27">
+    <row r="200" spans="1:7" ht="30">
       <c r="A200" s="1" t="s">
         <v>393</v>
       </c>
@@ -12570,7 +13373,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="201" spans="1:7" ht="67.5">
+    <row r="201" spans="1:7" ht="75">
       <c r="A201" s="1" t="s">
         <v>394</v>
       </c>
@@ -12581,7 +13384,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="202" spans="1:7" ht="27">
+    <row r="202" spans="1:7" ht="30">
       <c r="A202" s="1" t="s">
         <v>395</v>
       </c>
@@ -12628,7 +13431,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="206" spans="1:7">
+    <row r="206" spans="1:7" ht="15">
       <c r="A206" s="1" t="s">
         <v>399</v>
       </c>
@@ -12667,7 +13470,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="209" spans="1:6" ht="27">
+    <row r="209" spans="1:6" ht="30">
       <c r="A209" s="1" t="s">
         <v>402</v>
       </c>
@@ -12689,7 +13492,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="211" spans="1:6" ht="27">
+    <row r="211" spans="1:6" ht="30">
       <c r="A211" s="1" t="s">
         <v>404</v>
       </c>
@@ -12700,7 +13503,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="212" spans="1:6" ht="27">
+    <row r="212" spans="1:6" ht="15">
       <c r="A212" s="1" t="s">
         <v>405</v>
       </c>
@@ -12711,7 +13514,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="213" spans="1:6" ht="27">
+    <row r="213" spans="1:6" ht="30">
       <c r="A213" s="1" t="s">
         <v>406</v>
       </c>
@@ -12736,7 +13539,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="215" spans="1:6" ht="27">
+    <row r="215" spans="1:6" ht="30">
       <c r="A215" s="1" t="s">
         <v>566</v>
       </c>
@@ -12744,7 +13547,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="216" spans="1:6">
+    <row r="216" spans="1:6" ht="15">
       <c r="A216" s="1" t="s">
         <v>567</v>
       </c>
@@ -12752,7 +13555,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="217" spans="1:6">
+    <row r="217" spans="1:6" ht="15">
       <c r="A217" s="1" t="s">
         <v>568</v>
       </c>
@@ -12763,7 +13566,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="218" spans="1:6">
+    <row r="218" spans="1:6" ht="15">
       <c r="A218" s="1" t="s">
         <v>569</v>
       </c>
@@ -12771,7 +13574,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="219" spans="1:6" ht="27">
+    <row r="219" spans="1:6" ht="30">
       <c r="A219" s="1" t="s">
         <v>570</v>
       </c>
@@ -12785,7 +13588,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="220" spans="1:6">
+    <row r="220" spans="1:6" ht="15">
       <c r="A220" s="1" t="s">
         <v>571</v>
       </c>
@@ -12807,7 +13610,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="222" spans="1:6">
+    <row r="222" spans="1:6" ht="15">
       <c r="A222" s="1" t="s">
         <v>573</v>
       </c>
@@ -12926,7 +13729,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="232" spans="1:6" ht="27">
+    <row r="232" spans="1:6" ht="30">
       <c r="A232" s="1" t="s">
         <v>583</v>
       </c>
@@ -12985,7 +13788,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="239" spans="1:6" ht="27">
+    <row r="239" spans="1:6" ht="30">
       <c r="A239" s="1" t="s">
         <v>590</v>
       </c>
@@ -13024,7 +13827,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="242" spans="1:5" ht="27">
+    <row r="242" spans="1:5" ht="30">
       <c r="A242" s="1" t="s">
         <v>593</v>
       </c>
@@ -13326,7 +14129,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="285" spans="1:12">
+    <row r="285" spans="1:12" ht="15">
       <c r="A285" s="1" t="s">
         <v>646</v>
       </c>
@@ -13348,7 +14151,7 @@
       <c r="K285" s="2"/>
       <c r="L285" s="2"/>
     </row>
-    <row r="286" spans="1:12" ht="27">
+    <row r="286" spans="1:12" ht="30">
       <c r="A286" s="1" t="s">
         <v>647</v>
       </c>
@@ -13372,7 +14175,7 @@
       <c r="K286" s="2"/>
       <c r="L286" s="2"/>
     </row>
-    <row r="287" spans="1:12" ht="67.5">
+    <row r="287" spans="1:12" ht="75">
       <c r="A287" s="1" t="s">
         <v>648</v>
       </c>
@@ -13398,7 +14201,7 @@
       <c r="K287" s="2"/>
       <c r="L287" s="2"/>
     </row>
-    <row r="288" spans="1:12">
+    <row r="288" spans="1:12" ht="15">
       <c r="A288" s="1" t="s">
         <v>649</v>
       </c>
@@ -13422,7 +14225,7 @@
       <c r="K288" s="2"/>
       <c r="L288" s="2"/>
     </row>
-    <row r="289" spans="1:12" ht="27">
+    <row r="289" spans="1:12" ht="30">
       <c r="A289" s="1" t="s">
         <v>650</v>
       </c>
@@ -13444,7 +14247,7 @@
       <c r="K289" s="2"/>
       <c r="L289" s="2"/>
     </row>
-    <row r="290" spans="1:12" ht="27">
+    <row r="290" spans="1:12" ht="30">
       <c r="A290" s="1" t="s">
         <v>651</v>
       </c>
@@ -13462,7 +14265,7 @@
       <c r="K290" s="2"/>
       <c r="L290" s="2"/>
     </row>
-    <row r="291" spans="1:12" ht="40.5">
+    <row r="291" spans="1:12" ht="45">
       <c r="A291" s="1" t="s">
         <v>652</v>
       </c>
@@ -13486,7 +14289,7 @@
       <c r="K291" s="2"/>
       <c r="L291" s="2"/>
     </row>
-    <row r="292" spans="1:12" ht="27">
+    <row r="292" spans="1:12" ht="30">
       <c r="A292" s="1" t="s">
         <v>653</v>
       </c>
@@ -13526,7 +14329,7 @@
       <c r="K293" s="2"/>
       <c r="L293" s="2"/>
     </row>
-    <row r="294" spans="1:12">
+    <row r="294" spans="1:12" ht="15">
       <c r="A294" s="1" t="s">
         <v>655</v>
       </c>
@@ -13544,7 +14347,7 @@
       <c r="K294" s="2"/>
       <c r="L294" s="2"/>
     </row>
-    <row r="295" spans="1:12">
+    <row r="295" spans="1:12" ht="15">
       <c r="A295" s="1" t="s">
         <v>656</v>
       </c>
@@ -13562,7 +14365,7 @@
       <c r="K295" s="2"/>
       <c r="L295" s="2"/>
     </row>
-    <row r="296" spans="1:12">
+    <row r="296" spans="1:12" ht="15">
       <c r="A296" s="1" t="s">
         <v>657</v>
       </c>
@@ -13580,7 +14383,7 @@
       <c r="K296" s="2"/>
       <c r="L296" s="2"/>
     </row>
-    <row r="297" spans="1:12">
+    <row r="297" spans="1:12" ht="15">
       <c r="A297" s="1" t="s">
         <v>658</v>
       </c>
@@ -13614,7 +14417,7 @@
       <c r="K298" s="2"/>
       <c r="L298" s="2"/>
     </row>
-    <row r="299" spans="1:12">
+    <row r="299" spans="1:12" ht="15">
       <c r="A299" s="1" t="s">
         <v>660</v>
       </c>
@@ -13634,7 +14437,7 @@
       <c r="K299" s="2"/>
       <c r="L299" s="2"/>
     </row>
-    <row r="300" spans="1:12" ht="27">
+    <row r="300" spans="1:12" ht="30">
       <c r="A300" s="1" t="s">
         <v>661</v>
       </c>
@@ -13658,7 +14461,7 @@
       <c r="K300" s="2"/>
       <c r="L300" s="2"/>
     </row>
-    <row r="301" spans="1:12">
+    <row r="301" spans="1:12" ht="15">
       <c r="A301" s="1" t="s">
         <v>662</v>
       </c>
@@ -13682,7 +14485,7 @@
       <c r="K301" s="2"/>
       <c r="L301" s="2"/>
     </row>
-    <row r="302" spans="1:12">
+    <row r="302" spans="1:12" ht="15">
       <c r="A302" s="1" t="s">
         <v>663</v>
       </c>
@@ -13700,7 +14503,7 @@
       <c r="K302" s="2"/>
       <c r="L302" s="2"/>
     </row>
-    <row r="303" spans="1:12">
+    <row r="303" spans="1:12" ht="15">
       <c r="A303" s="1" t="s">
         <v>664</v>
       </c>
@@ -13718,7 +14521,7 @@
       <c r="K303" s="2"/>
       <c r="L303" s="2"/>
     </row>
-    <row r="304" spans="1:12">
+    <row r="304" spans="1:12" ht="15">
       <c r="A304" s="1" t="s">
         <v>665</v>
       </c>
@@ -13738,7 +14541,7 @@
       <c r="K304" s="2"/>
       <c r="L304" s="2"/>
     </row>
-    <row r="305" spans="1:12">
+    <row r="305" spans="1:12" ht="15">
       <c r="A305" s="1" t="s">
         <v>666</v>
       </c>
@@ -13758,7 +14561,7 @@
       <c r="K305" s="2"/>
       <c r="L305" s="2"/>
     </row>
-    <row r="306" spans="1:12">
+    <row r="306" spans="1:12" ht="15">
       <c r="A306" s="1" t="s">
         <v>667</v>
       </c>
@@ -13776,7 +14579,7 @@
       <c r="K306" s="2"/>
       <c r="L306" s="2"/>
     </row>
-    <row r="307" spans="1:12">
+    <row r="307" spans="1:12" ht="15">
       <c r="A307" s="1" t="s">
         <v>668</v>
       </c>
@@ -13798,7 +14601,7 @@
       <c r="K307" s="2"/>
       <c r="L307" s="2"/>
     </row>
-    <row r="308" spans="1:12">
+    <row r="308" spans="1:12" ht="15">
       <c r="A308" s="1" t="s">
         <v>776</v>
       </c>
@@ -13816,7 +14619,7 @@
       <c r="K308" s="2"/>
       <c r="L308" s="2"/>
     </row>
-    <row r="309" spans="1:12">
+    <row r="309" spans="1:12" ht="15">
       <c r="A309" s="1" t="s">
         <v>777</v>
       </c>
@@ -13840,7 +14643,7 @@
       <c r="K309" s="2"/>
       <c r="L309" s="2"/>
     </row>
-    <row r="310" spans="1:12">
+    <row r="310" spans="1:12" ht="15">
       <c r="A310" s="1" t="s">
         <v>778</v>
       </c>
@@ -13862,7 +14665,7 @@
       <c r="K310" s="2"/>
       <c r="L310" s="2"/>
     </row>
-    <row r="311" spans="1:12">
+    <row r="311" spans="1:12" ht="15">
       <c r="A311" s="1" t="s">
         <v>779</v>
       </c>
@@ -13882,7 +14685,7 @@
       <c r="K311" s="2"/>
       <c r="L311" s="2"/>
     </row>
-    <row r="312" spans="1:12" ht="27">
+    <row r="312" spans="1:12" ht="30">
       <c r="A312" s="1" t="s">
         <v>780</v>
       </c>
@@ -13902,7 +14705,7 @@
       <c r="K312" s="2"/>
       <c r="L312" s="2"/>
     </row>
-    <row r="313" spans="1:12">
+    <row r="313" spans="1:12" ht="15">
       <c r="A313" s="1" t="s">
         <v>781</v>
       </c>
@@ -13926,7 +14729,7 @@
       <c r="K313" s="2"/>
       <c r="L313" s="2"/>
     </row>
-    <row r="314" spans="1:12">
+    <row r="314" spans="1:12" ht="15">
       <c r="A314" s="1" t="s">
         <v>782</v>
       </c>
@@ -13946,7 +14749,7 @@
       <c r="K314" s="2"/>
       <c r="L314" s="2"/>
     </row>
-    <row r="315" spans="1:12" ht="27">
+    <row r="315" spans="1:12" ht="30">
       <c r="A315" s="1" t="s">
         <v>783</v>
       </c>
@@ -13966,7 +14769,7 @@
       <c r="K315" s="2"/>
       <c r="L315" s="2"/>
     </row>
-    <row r="316" spans="1:12">
+    <row r="316" spans="1:12" ht="15">
       <c r="A316" s="1" t="s">
         <v>784</v>
       </c>
@@ -13988,7 +14791,7 @@
       <c r="K316" s="2"/>
       <c r="L316" s="2"/>
     </row>
-    <row r="317" spans="1:12" ht="27">
+    <row r="317" spans="1:12" ht="30">
       <c r="A317" s="1" t="s">
         <v>785</v>
       </c>
@@ -14012,7 +14815,7 @@
       <c r="K317" s="2"/>
       <c r="L317" s="2"/>
     </row>
-    <row r="318" spans="1:12">
+    <row r="318" spans="1:12" ht="15">
       <c r="A318" s="1" t="s">
         <v>786</v>
       </c>
@@ -14030,7 +14833,7 @@
       <c r="K318" s="2"/>
       <c r="L318" s="2"/>
     </row>
-    <row r="319" spans="1:12">
+    <row r="319" spans="1:12" ht="15">
       <c r="A319" s="1" t="s">
         <v>787</v>
       </c>
@@ -14048,7 +14851,7 @@
       <c r="K319" s="2"/>
       <c r="L319" s="2"/>
     </row>
-    <row r="320" spans="1:12" ht="27">
+    <row r="320" spans="1:12" ht="30">
       <c r="A320" s="1" t="s">
         <v>788</v>
       </c>
@@ -14070,7 +14873,7 @@
       <c r="K320" s="2"/>
       <c r="L320" s="2"/>
     </row>
-    <row r="321" spans="1:12" ht="27">
+    <row r="321" spans="1:12" ht="30">
       <c r="A321" s="1" t="s">
         <v>789</v>
       </c>
@@ -14088,7 +14891,7 @@
       <c r="K321" s="2"/>
       <c r="L321" s="2"/>
     </row>
-    <row r="322" spans="1:12">
+    <row r="322" spans="1:12" ht="15">
       <c r="A322" s="1" t="s">
         <v>790</v>
       </c>
@@ -14108,7 +14911,7 @@
       <c r="K322" s="2"/>
       <c r="L322" s="2"/>
     </row>
-    <row r="323" spans="1:12">
+    <row r="323" spans="1:12" ht="15">
       <c r="A323" s="1" t="s">
         <v>791</v>
       </c>
@@ -14144,7 +14947,7 @@
       <c r="K324" s="2"/>
       <c r="L324" s="2"/>
     </row>
-    <row r="325" spans="1:12">
+    <row r="325" spans="1:12" ht="15">
       <c r="A325" s="1" t="s">
         <v>793</v>
       </c>
@@ -14162,7 +14965,7 @@
       <c r="K325" s="2"/>
       <c r="L325" s="2"/>
     </row>
-    <row r="326" spans="1:12">
+    <row r="326" spans="1:12" ht="15">
       <c r="A326" s="1" t="s">
         <v>794</v>
       </c>
@@ -14180,7 +14983,7 @@
       <c r="K326" s="2"/>
       <c r="L326" s="2"/>
     </row>
-    <row r="327" spans="1:12">
+    <row r="327" spans="1:12" ht="15">
       <c r="A327" s="1" t="s">
         <v>795</v>
       </c>
@@ -14200,7 +15003,7 @@
       <c r="K327" s="2"/>
       <c r="L327" s="2"/>
     </row>
-    <row r="328" spans="1:12">
+    <row r="328" spans="1:12" ht="15">
       <c r="A328" s="1" t="s">
         <v>796</v>
       </c>
@@ -14218,7 +15021,7 @@
       <c r="K328" s="2"/>
       <c r="L328" s="2"/>
     </row>
-    <row r="329" spans="1:12">
+    <row r="329" spans="1:12" ht="15">
       <c r="A329" s="1" t="s">
         <v>797</v>
       </c>
@@ -14238,7 +15041,7 @@
       <c r="K329" s="2"/>
       <c r="L329" s="2"/>
     </row>
-    <row r="330" spans="1:12" ht="27">
+    <row r="330" spans="1:12" ht="30">
       <c r="A330" s="1" t="s">
         <v>798</v>
       </c>
@@ -14262,7 +15065,7 @@
       <c r="K330" s="2"/>
       <c r="L330" s="2"/>
     </row>
-    <row r="331" spans="1:12">
+    <row r="331" spans="1:12" ht="15">
       <c r="A331" s="1" t="s">
         <v>799</v>
       </c>
@@ -14280,7 +15083,7 @@
       <c r="K331" s="2"/>
       <c r="L331" s="2"/>
     </row>
-    <row r="332" spans="1:12">
+    <row r="332" spans="1:12" ht="15">
       <c r="A332" s="1" t="s">
         <v>800</v>
       </c>
@@ -14300,7 +15103,7 @@
       <c r="K332" s="2"/>
       <c r="L332" s="2"/>
     </row>
-    <row r="333" spans="1:12">
+    <row r="333" spans="1:12" ht="15">
       <c r="A333" s="1" t="s">
         <v>801</v>
       </c>
@@ -14324,7 +15127,7 @@
       <c r="K333" s="2"/>
       <c r="L333" s="2"/>
     </row>
-    <row r="334" spans="1:12">
+    <row r="334" spans="1:12" ht="15">
       <c r="A334" s="1" t="s">
         <v>802</v>
       </c>
@@ -14342,7 +15145,7 @@
       <c r="K334" s="2"/>
       <c r="L334" s="2"/>
     </row>
-    <row r="335" spans="1:12">
+    <row r="335" spans="1:12" ht="15">
       <c r="A335" s="1" t="s">
         <v>803</v>
       </c>
@@ -14366,7 +15169,7 @@
       <c r="K335" s="2"/>
       <c r="L335" s="2"/>
     </row>
-    <row r="336" spans="1:12">
+    <row r="336" spans="1:12" ht="15">
       <c r="A336" s="1" t="s">
         <v>820</v>
       </c>
@@ -14386,7 +15189,7 @@
       <c r="K336" s="2"/>
       <c r="L336" s="2"/>
     </row>
-    <row r="337" spans="1:12">
+    <row r="337" spans="1:12" ht="15">
       <c r="A337" s="1" t="s">
         <v>821</v>
       </c>
@@ -14404,7 +15207,7 @@
       <c r="K337" s="2"/>
       <c r="L337" s="2"/>
     </row>
-    <row r="338" spans="1:12" ht="27">
+    <row r="338" spans="1:12" ht="30">
       <c r="A338" s="1" t="s">
         <v>822</v>
       </c>
@@ -14424,7 +15227,7 @@
       <c r="K338" s="2"/>
       <c r="L338" s="2"/>
     </row>
-    <row r="339" spans="1:12">
+    <row r="339" spans="1:12" ht="15">
       <c r="A339" s="1" t="s">
         <v>823</v>
       </c>
@@ -14444,7 +15247,7 @@
       <c r="K339" s="2"/>
       <c r="L339" s="2"/>
     </row>
-    <row r="340" spans="1:12">
+    <row r="340" spans="1:12" ht="15">
       <c r="A340" s="1" t="s">
         <v>824</v>
       </c>
@@ -14464,7 +15267,7 @@
       <c r="K340" s="2"/>
       <c r="L340" s="2"/>
     </row>
-    <row r="341" spans="1:12">
+    <row r="341" spans="1:12" ht="15">
       <c r="A341" s="1" t="s">
         <v>825</v>
       </c>
@@ -14486,7 +15289,7 @@
       <c r="K341" s="2"/>
       <c r="L341" s="2"/>
     </row>
-    <row r="342" spans="1:12">
+    <row r="342" spans="1:12" ht="15">
       <c r="A342" s="1" t="s">
         <v>826</v>
       </c>
@@ -14510,7 +15313,7 @@
       <c r="K342" s="2"/>
       <c r="L342" s="2"/>
     </row>
-    <row r="343" spans="1:12">
+    <row r="343" spans="1:12" ht="15">
       <c r="A343" s="1" t="s">
         <v>827</v>
       </c>
@@ -14528,7 +15331,7 @@
       <c r="K343" s="2"/>
       <c r="L343" s="2"/>
     </row>
-    <row r="344" spans="1:12">
+    <row r="344" spans="1:12" ht="15">
       <c r="A344" s="1" t="s">
         <v>828</v>
       </c>
@@ -14550,7 +15353,7 @@
       <c r="K344" s="2"/>
       <c r="L344" s="2"/>
     </row>
-    <row r="345" spans="1:12">
+    <row r="345" spans="1:12" ht="15">
       <c r="A345" s="1" t="s">
         <v>829</v>
       </c>
@@ -14568,7 +15371,7 @@
       <c r="K345" s="2"/>
       <c r="L345" s="2"/>
     </row>
-    <row r="346" spans="1:12">
+    <row r="346" spans="1:12" ht="15">
       <c r="A346" s="1" t="s">
         <v>830</v>
       </c>
@@ -14586,7 +15389,7 @@
       <c r="K346" s="2"/>
       <c r="L346" s="2"/>
     </row>
-    <row r="347" spans="1:12">
+    <row r="347" spans="1:12" ht="15">
       <c r="A347" s="1" t="s">
         <v>831</v>
       </c>
@@ -14606,7 +15409,7 @@
       <c r="K347" s="2"/>
       <c r="L347" s="2"/>
     </row>
-    <row r="348" spans="1:12" ht="54">
+    <row r="348" spans="1:12" ht="60">
       <c r="A348" s="1" t="s">
         <v>832</v>
       </c>
@@ -14632,7 +15435,7 @@
       <c r="K348" s="2"/>
       <c r="L348" s="2"/>
     </row>
-    <row r="349" spans="1:12">
+    <row r="349" spans="1:12" ht="15">
       <c r="A349" s="1" t="s">
         <v>833</v>
       </c>
@@ -14652,7 +15455,7 @@
       <c r="K349" s="2"/>
       <c r="L349" s="2"/>
     </row>
-    <row r="350" spans="1:12">
+    <row r="350" spans="1:12" ht="15">
       <c r="A350" s="1" t="s">
         <v>834</v>
       </c>
@@ -14678,7 +15481,7 @@
       <c r="K350" s="2"/>
       <c r="L350" s="2"/>
     </row>
-    <row r="351" spans="1:12">
+    <row r="351" spans="1:12" ht="15">
       <c r="A351" s="1" t="s">
         <v>835</v>
       </c>
@@ -14696,7 +15499,7 @@
       <c r="K351" s="2"/>
       <c r="L351" s="2"/>
     </row>
-    <row r="352" spans="1:12">
+    <row r="352" spans="1:12" ht="15">
       <c r="A352" s="1" t="s">
         <v>836</v>
       </c>
@@ -14718,7 +15521,7 @@
       <c r="K352" s="2"/>
       <c r="L352" s="2"/>
     </row>
-    <row r="353" spans="1:12">
+    <row r="353" spans="1:12" ht="15">
       <c r="A353" s="1" t="s">
         <v>837</v>
       </c>
@@ -14740,7 +15543,7 @@
       </c>
       <c r="L353" s="2"/>
     </row>
-    <row r="354" spans="1:12" ht="27">
+    <row r="354" spans="1:12" ht="30">
       <c r="A354" s="1" t="s">
         <v>915</v>
       </c>
@@ -14774,7 +15577,7 @@
       <c r="K354" s="2"/>
       <c r="L354" s="2"/>
     </row>
-    <row r="355" spans="1:12">
+    <row r="355" spans="1:12" ht="15">
       <c r="A355" s="1" t="s">
         <v>838</v>
       </c>
@@ -14798,7 +15601,7 @@
       <c r="K355" s="2"/>
       <c r="L355" s="2"/>
     </row>
-    <row r="356" spans="1:12" ht="27">
+    <row r="356" spans="1:12" ht="32">
       <c r="A356" s="1" t="s">
         <v>839</v>
       </c>
@@ -14822,7 +15625,7 @@
       <c r="K356" s="2"/>
       <c r="L356" s="2"/>
     </row>
-    <row r="357" spans="1:12">
+    <row r="357" spans="1:12" ht="15">
       <c r="A357" s="1" t="s">
         <v>840</v>
       </c>
@@ -14840,7 +15643,7 @@
       <c r="K357" s="2"/>
       <c r="L357" s="2"/>
     </row>
-    <row r="358" spans="1:12" ht="27">
+    <row r="358" spans="1:12" ht="30">
       <c r="A358" s="1" t="s">
         <v>841</v>
       </c>
@@ -14864,7 +15667,7 @@
       <c r="K358" s="2"/>
       <c r="L358" s="2"/>
     </row>
-    <row r="359" spans="1:12" ht="27">
+    <row r="359" spans="1:12" ht="30">
       <c r="A359" s="1" t="s">
         <v>842</v>
       </c>
@@ -14888,7 +15691,7 @@
       <c r="K359" s="2"/>
       <c r="L359" s="2"/>
     </row>
-    <row r="360" spans="1:12" ht="27">
+    <row r="360" spans="1:12" ht="30">
       <c r="A360" s="1" t="s">
         <v>843</v>
       </c>
@@ -14916,7 +15719,7 @@
       <c r="K360" s="2"/>
       <c r="L360" s="2"/>
     </row>
-    <row r="361" spans="1:12">
+    <row r="361" spans="1:12" ht="15">
       <c r="A361" s="1" t="s">
         <v>844</v>
       </c>
@@ -14946,7 +15749,7 @@
       <c r="K361" s="2"/>
       <c r="L361" s="2"/>
     </row>
-    <row r="362" spans="1:12" ht="40.5">
+    <row r="362" spans="1:12" ht="45">
       <c r="A362" s="1" t="s">
         <v>845</v>
       </c>
@@ -14974,7 +15777,7 @@
       <c r="K362" s="2"/>
       <c r="L362" s="2"/>
     </row>
-    <row r="363" spans="1:12" ht="27">
+    <row r="363" spans="1:12" ht="30">
       <c r="A363" s="1" t="s">
         <v>846</v>
       </c>
@@ -15010,7 +15813,7 @@
       <c r="K364" s="2"/>
       <c r="L364" s="2"/>
     </row>
-    <row r="365" spans="1:12">
+    <row r="365" spans="1:12" ht="15">
       <c r="A365" s="1" t="s">
         <v>848</v>
       </c>
@@ -15028,7 +15831,7 @@
       <c r="K365" s="2"/>
       <c r="L365" s="2"/>
     </row>
-    <row r="366" spans="1:12" ht="27">
+    <row r="366" spans="1:12" ht="30">
       <c r="A366" s="1" t="s">
         <v>849</v>
       </c>
@@ -15052,7 +15855,7 @@
       <c r="K366" s="2"/>
       <c r="L366" s="2"/>
     </row>
-    <row r="367" spans="1:12" ht="54">
+    <row r="367" spans="1:12" ht="60">
       <c r="A367" s="1" t="s">
         <v>850</v>
       </c>
@@ -15100,60 +15903,60 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E130" r:id="rId1"/>
-    <hyperlink ref="C162" r:id="rId2"/>
-    <hyperlink ref="C178" r:id="rId3"/>
-    <hyperlink ref="C179" r:id="rId4"/>
-    <hyperlink ref="D181" r:id="rId5"/>
-    <hyperlink ref="C185" r:id="rId6"/>
-    <hyperlink ref="C188" r:id="rId7"/>
-    <hyperlink ref="D188" r:id="rId8"/>
-    <hyperlink ref="F188" r:id="rId9"/>
-    <hyperlink ref="E138" r:id="rId10" location="/info"/>
-    <hyperlink ref="C190" r:id="rId11" location="/info"/>
-    <hyperlink ref="D190" r:id="rId12"/>
-    <hyperlink ref="D193" r:id="rId13"/>
-    <hyperlink ref="E193" r:id="rId14"/>
-    <hyperlink ref="F193" r:id="rId15"/>
-    <hyperlink ref="C198" r:id="rId16"/>
-    <hyperlink ref="B200" r:id="rId17"/>
-    <hyperlink ref="B201" r:id="rId18"/>
-    <hyperlink ref="C201" r:id="rId19"/>
-    <hyperlink ref="E202" r:id="rId20"/>
-    <hyperlink ref="B209" r:id="rId21" display="https://link.zhihu.com/?target=https%3A//www.mongodb.com/cloud"/>
-    <hyperlink ref="B211" r:id="rId22"/>
-    <hyperlink ref="C211" r:id="rId23"/>
-    <hyperlink ref="C213" r:id="rId24"/>
-    <hyperlink ref="C191" r:id="rId25"/>
-    <hyperlink ref="D219" r:id="rId26"/>
-    <hyperlink ref="B219" r:id="rId27"/>
-    <hyperlink ref="D220" r:id="rId28"/>
-    <hyperlink ref="B232" r:id="rId29"/>
-    <hyperlink ref="D242" r:id="rId30" display="https://github.com/360EntSecGroup-Skylar/ElasticHD"/>
-    <hyperlink ref="C286" r:id="rId31"/>
-    <hyperlink ref="D286" r:id="rId32"/>
-    <hyperlink ref="E286" r:id="rId33"/>
-    <hyperlink ref="B287" r:id="rId34" display="https://github.com/medcl/elasticsearch-migration/"/>
-    <hyperlink ref="C287" r:id="rId35"/>
-    <hyperlink ref="D291" r:id="rId36"/>
-    <hyperlink ref="B292" r:id="rId37"/>
-    <hyperlink ref="B312" r:id="rId38"/>
-    <hyperlink ref="D317" r:id="rId39"/>
-    <hyperlink ref="B330" r:id="rId40" display="https://github.com/youfou/wxpy"/>
-    <hyperlink ref="F348" r:id="rId41"/>
-    <hyperlink ref="D354" r:id="rId42"/>
-    <hyperlink ref="C356" r:id="rId43"/>
-    <hyperlink ref="E358" r:id="rId44"/>
-    <hyperlink ref="B359" r:id="rId45"/>
-    <hyperlink ref="D359" r:id="rId46"/>
-    <hyperlink ref="C362" r:id="rId47"/>
-    <hyperlink ref="F362" r:id="rId48"/>
-    <hyperlink ref="G362" r:id="rId49"/>
-    <hyperlink ref="G360" r:id="rId50"/>
-    <hyperlink ref="B363" r:id="rId51"/>
-    <hyperlink ref="C367" r:id="rId52"/>
-    <hyperlink ref="D367" r:id="rId53"/>
-    <hyperlink ref="G367" r:id="rId54"/>
+    <hyperlink ref="E130" r:id="rId1" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
+    <hyperlink ref="C162" r:id="rId2" xr:uid="{00000000-0004-0000-0400-000001000000}"/>
+    <hyperlink ref="C178" r:id="rId3" xr:uid="{00000000-0004-0000-0400-000002000000}"/>
+    <hyperlink ref="C179" r:id="rId4" xr:uid="{00000000-0004-0000-0400-000003000000}"/>
+    <hyperlink ref="D181" r:id="rId5" xr:uid="{00000000-0004-0000-0400-000004000000}"/>
+    <hyperlink ref="C185" r:id="rId6" xr:uid="{00000000-0004-0000-0400-000005000000}"/>
+    <hyperlink ref="C188" r:id="rId7" xr:uid="{00000000-0004-0000-0400-000006000000}"/>
+    <hyperlink ref="D188" r:id="rId8" xr:uid="{00000000-0004-0000-0400-000007000000}"/>
+    <hyperlink ref="F188" r:id="rId9" xr:uid="{00000000-0004-0000-0400-000008000000}"/>
+    <hyperlink ref="E138" r:id="rId10" location="/info" xr:uid="{00000000-0004-0000-0400-000009000000}"/>
+    <hyperlink ref="C190" r:id="rId11" location="/info" xr:uid="{00000000-0004-0000-0400-00000A000000}"/>
+    <hyperlink ref="D190" r:id="rId12" xr:uid="{00000000-0004-0000-0400-00000B000000}"/>
+    <hyperlink ref="D193" r:id="rId13" xr:uid="{00000000-0004-0000-0400-00000C000000}"/>
+    <hyperlink ref="E193" r:id="rId14" xr:uid="{00000000-0004-0000-0400-00000D000000}"/>
+    <hyperlink ref="F193" r:id="rId15" xr:uid="{00000000-0004-0000-0400-00000E000000}"/>
+    <hyperlink ref="C198" r:id="rId16" xr:uid="{00000000-0004-0000-0400-00000F000000}"/>
+    <hyperlink ref="B200" r:id="rId17" xr:uid="{00000000-0004-0000-0400-000010000000}"/>
+    <hyperlink ref="B201" r:id="rId18" xr:uid="{00000000-0004-0000-0400-000011000000}"/>
+    <hyperlink ref="C201" r:id="rId19" xr:uid="{00000000-0004-0000-0400-000012000000}"/>
+    <hyperlink ref="E202" r:id="rId20" xr:uid="{00000000-0004-0000-0400-000013000000}"/>
+    <hyperlink ref="B209" r:id="rId21" display="https://link.zhihu.com/?target=https%3A//www.mongodb.com/cloud" xr:uid="{00000000-0004-0000-0400-000014000000}"/>
+    <hyperlink ref="B211" r:id="rId22" xr:uid="{00000000-0004-0000-0400-000015000000}"/>
+    <hyperlink ref="C211" r:id="rId23" xr:uid="{00000000-0004-0000-0400-000016000000}"/>
+    <hyperlink ref="C213" r:id="rId24" xr:uid="{00000000-0004-0000-0400-000017000000}"/>
+    <hyperlink ref="C191" r:id="rId25" xr:uid="{00000000-0004-0000-0400-000018000000}"/>
+    <hyperlink ref="D219" r:id="rId26" xr:uid="{00000000-0004-0000-0400-000019000000}"/>
+    <hyperlink ref="B219" r:id="rId27" xr:uid="{00000000-0004-0000-0400-00001A000000}"/>
+    <hyperlink ref="D220" r:id="rId28" xr:uid="{00000000-0004-0000-0400-00001B000000}"/>
+    <hyperlink ref="B232" r:id="rId29" xr:uid="{00000000-0004-0000-0400-00001C000000}"/>
+    <hyperlink ref="D242" r:id="rId30" display="https://github.com/360EntSecGroup-Skylar/ElasticHD" xr:uid="{00000000-0004-0000-0400-00001D000000}"/>
+    <hyperlink ref="C286" r:id="rId31" xr:uid="{00000000-0004-0000-0400-00001E000000}"/>
+    <hyperlink ref="D286" r:id="rId32" xr:uid="{00000000-0004-0000-0400-00001F000000}"/>
+    <hyperlink ref="E286" r:id="rId33" xr:uid="{00000000-0004-0000-0400-000020000000}"/>
+    <hyperlink ref="B287" r:id="rId34" display="https://github.com/medcl/elasticsearch-migration/" xr:uid="{00000000-0004-0000-0400-000021000000}"/>
+    <hyperlink ref="C287" r:id="rId35" xr:uid="{00000000-0004-0000-0400-000022000000}"/>
+    <hyperlink ref="D291" r:id="rId36" xr:uid="{00000000-0004-0000-0400-000023000000}"/>
+    <hyperlink ref="B292" r:id="rId37" xr:uid="{00000000-0004-0000-0400-000024000000}"/>
+    <hyperlink ref="B312" r:id="rId38" xr:uid="{00000000-0004-0000-0400-000025000000}"/>
+    <hyperlink ref="D317" r:id="rId39" xr:uid="{00000000-0004-0000-0400-000026000000}"/>
+    <hyperlink ref="B330" r:id="rId40" display="https://github.com/youfou/wxpy" xr:uid="{00000000-0004-0000-0400-000027000000}"/>
+    <hyperlink ref="F348" r:id="rId41" xr:uid="{00000000-0004-0000-0400-000028000000}"/>
+    <hyperlink ref="D354" r:id="rId42" xr:uid="{00000000-0004-0000-0400-000029000000}"/>
+    <hyperlink ref="C356" r:id="rId43" xr:uid="{00000000-0004-0000-0400-00002A000000}"/>
+    <hyperlink ref="E358" r:id="rId44" xr:uid="{00000000-0004-0000-0400-00002B000000}"/>
+    <hyperlink ref="B359" r:id="rId45" xr:uid="{00000000-0004-0000-0400-00002C000000}"/>
+    <hyperlink ref="D359" r:id="rId46" xr:uid="{00000000-0004-0000-0400-00002D000000}"/>
+    <hyperlink ref="C362" r:id="rId47" xr:uid="{00000000-0004-0000-0400-00002E000000}"/>
+    <hyperlink ref="F362" r:id="rId48" xr:uid="{00000000-0004-0000-0400-00002F000000}"/>
+    <hyperlink ref="G362" r:id="rId49" xr:uid="{00000000-0004-0000-0400-000030000000}"/>
+    <hyperlink ref="G360" r:id="rId50" xr:uid="{00000000-0004-0000-0400-000031000000}"/>
+    <hyperlink ref="B363" r:id="rId51" xr:uid="{00000000-0004-0000-0400-000032000000}"/>
+    <hyperlink ref="C367" r:id="rId52" xr:uid="{00000000-0004-0000-0400-000033000000}"/>
+    <hyperlink ref="D367" r:id="rId53" xr:uid="{00000000-0004-0000-0400-000034000000}"/>
+    <hyperlink ref="G367" r:id="rId54" xr:uid="{00000000-0004-0000-0400-000035000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId55"/>
@@ -15161,17 +15964,17 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G297"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="14.125" customWidth="1"/>
-    <col min="2" max="2" width="32.875" customWidth="1"/>
-    <col min="3" max="3" width="35.125" customWidth="1"/>
-    <col min="4" max="4" width="21.875" customWidth="1"/>
-    <col min="5" max="5" width="44.625" customWidth="1"/>
+    <col min="1" max="1" width="14.1640625" customWidth="1"/>
+    <col min="2" max="2" width="32.83203125" customWidth="1"/>
+    <col min="3" max="3" width="35.1640625" customWidth="1"/>
+    <col min="4" max="4" width="21.83203125" customWidth="1"/>
+    <col min="5" max="5" width="44.6640625" customWidth="1"/>
     <col min="6" max="6" width="36.5" customWidth="1"/>
-    <col min="7" max="7" width="45.25" customWidth="1"/>
+    <col min="7" max="7" width="45.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="56.25" customHeight="1">
@@ -15197,7 +16000,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="49.9" customHeight="1">
+    <row r="2" spans="1:7" ht="50" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>1554</v>
       </c>
@@ -15220,7 +16023,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" ht="15">
       <c r="A3" s="4" t="s">
         <v>1555</v>
       </c>
@@ -15235,7 +16038,7 @@
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" ht="15">
       <c r="A4" s="4" t="s">
         <v>1556</v>
       </c>
@@ -15250,7 +16053,7 @@
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" ht="15">
       <c r="A5" s="4" t="s">
         <v>1557</v>
       </c>
@@ -15263,7 +16066,7 @@
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" ht="15">
       <c r="A6" s="4" t="s">
         <v>1558</v>
       </c>
@@ -15276,7 +16079,7 @@
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:7" ht="27">
+    <row r="7" spans="1:7" ht="30">
       <c r="A7" s="4" t="s">
         <v>1559</v>
       </c>
@@ -15289,7 +16092,7 @@
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7" ht="27">
+    <row r="8" spans="1:7" ht="30">
       <c r="A8" s="4" t="s">
         <v>1560</v>
       </c>
@@ -15308,7 +16111,7 @@
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7" ht="27">
+    <row r="9" spans="1:7" ht="15">
       <c r="A9" s="4" t="s">
         <v>1561</v>
       </c>
@@ -15327,7 +16130,7 @@
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" ht="15">
       <c r="A10" s="4" t="s">
         <v>1562</v>
       </c>
@@ -15342,7 +16145,7 @@
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" ht="15">
       <c r="A11" s="4" t="s">
         <v>1563</v>
       </c>
@@ -15355,7 +16158,7 @@
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
     </row>
-    <row r="12" spans="1:7" ht="27">
+    <row r="12" spans="1:7" ht="30">
       <c r="A12" s="4" t="s">
         <v>1564</v>
       </c>
@@ -15372,7 +16175,7 @@
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" ht="15">
       <c r="A13" s="4" t="s">
         <v>1565</v>
       </c>
@@ -15385,7 +16188,7 @@
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
     </row>
-    <row r="14" spans="1:7" ht="27">
+    <row r="14" spans="1:7" ht="30">
       <c r="A14" s="4" t="s">
         <v>1566</v>
       </c>
@@ -15400,7 +16203,7 @@
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" ht="15">
       <c r="A15" s="4" t="s">
         <v>1567</v>
       </c>
@@ -15413,7 +16216,7 @@
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" ht="15">
       <c r="A16" s="4" t="s">
         <v>1568</v>
       </c>
@@ -15426,7 +16229,7 @@
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" ht="15">
       <c r="A17" s="4" t="s">
         <v>1569</v>
       </c>
@@ -15443,7 +16246,7 @@
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" ht="15">
       <c r="A18" s="4" t="s">
         <v>1570</v>
       </c>
@@ -15456,7 +16259,7 @@
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" ht="15">
       <c r="A19" s="4" t="s">
         <v>1571</v>
       </c>
@@ -15471,7 +16274,7 @@
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" ht="15">
       <c r="A20" s="4" t="s">
         <v>1572</v>
       </c>
@@ -15486,7 +16289,7 @@
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" ht="15">
       <c r="A21" s="4" t="s">
         <v>1573</v>
       </c>
@@ -15501,7 +16304,7 @@
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" ht="15">
       <c r="A22" s="4" t="s">
         <v>1574</v>
       </c>
@@ -15514,7 +16317,7 @@
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" ht="15">
       <c r="A23" s="4" t="s">
         <v>1575</v>
       </c>
@@ -15527,7 +16330,7 @@
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" ht="15">
       <c r="A24" s="4" t="s">
         <v>1576</v>
       </c>
@@ -15540,7 +16343,7 @@
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" ht="15">
       <c r="A25" s="4" t="s">
         <v>1577</v>
       </c>
@@ -15553,7 +16356,7 @@
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" ht="15">
       <c r="A26" s="4" t="s">
         <v>1578</v>
       </c>
@@ -15566,7 +16369,7 @@
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" ht="15">
       <c r="A27" s="4" t="s">
         <v>1579</v>
       </c>
@@ -15581,7 +16384,7 @@
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" ht="15">
       <c r="A28" s="4" t="s">
         <v>1580</v>
       </c>
@@ -15594,7 +16397,7 @@
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" ht="15">
       <c r="A29" s="4" t="s">
         <v>1581</v>
       </c>
@@ -15605,7 +16408,7 @@
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" ht="15">
       <c r="A30" s="4" t="s">
         <v>1582</v>
       </c>
@@ -15618,7 +16421,7 @@
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" ht="15">
       <c r="A31" s="4" t="s">
         <v>1583</v>
       </c>
@@ -15629,7 +16432,7 @@
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" ht="15">
       <c r="A32" s="4" t="s">
         <v>1584</v>
       </c>
@@ -15640,7 +16443,7 @@
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" ht="15">
       <c r="A33" s="4" t="s">
         <v>1585</v>
       </c>
@@ -15651,7 +16454,7 @@
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" ht="15">
       <c r="A34" s="4" t="s">
         <v>1586</v>
       </c>
@@ -15661,7 +16464,7 @@
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" ht="15">
       <c r="A35" s="4" t="s">
         <v>1587</v>
       </c>
@@ -15674,7 +16477,7 @@
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" ht="15">
       <c r="A36" s="4" t="s">
         <v>1588</v>
       </c>
@@ -15687,7 +16490,7 @@
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" ht="15">
       <c r="A37" s="4" t="s">
         <v>1589</v>
       </c>
@@ -15700,7 +16503,7 @@
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" ht="15">
       <c r="A38" s="4" t="s">
         <v>1590</v>
       </c>
@@ -15713,7 +16516,7 @@
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" ht="15">
       <c r="A39" s="4" t="s">
         <v>1591</v>
       </c>
@@ -15726,7 +16529,7 @@
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" ht="15">
       <c r="A40" s="4" t="s">
         <v>1592</v>
       </c>
@@ -15737,7 +16540,7 @@
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" ht="15">
       <c r="A41" s="4" t="s">
         <v>1593</v>
       </c>
@@ -15748,7 +16551,7 @@
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" ht="15">
       <c r="A42" s="4" t="s">
         <v>1594</v>
       </c>
@@ -15761,7 +16564,7 @@
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" ht="15">
       <c r="A43" s="4" t="s">
         <v>1595</v>
       </c>
@@ -15772,7 +16575,7 @@
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" ht="15">
       <c r="A44" s="4" t="s">
         <v>1596</v>
       </c>
@@ -15785,7 +16588,7 @@
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" ht="15">
       <c r="A45" s="4" t="s">
         <v>1597</v>
       </c>
@@ -15798,7 +16601,7 @@
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" ht="15">
       <c r="A46" s="4" t="s">
         <v>1598</v>
       </c>
@@ -15809,7 +16612,7 @@
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" ht="15">
       <c r="A47" s="4" t="s">
         <v>1599</v>
       </c>
@@ -15820,7 +16623,7 @@
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" ht="15">
       <c r="A48" s="4" t="s">
         <v>1600</v>
       </c>
@@ -15831,7 +16634,7 @@
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" ht="15">
       <c r="A49" s="4" t="s">
         <v>1601</v>
       </c>
@@ -15842,7 +16645,7 @@
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" ht="15">
       <c r="A50" s="4" t="s">
         <v>1602</v>
       </c>
@@ -15853,7 +16656,7 @@
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" ht="15">
       <c r="A51" s="4" t="s">
         <v>1603</v>
       </c>
@@ -15864,7 +16667,7 @@
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" ht="15">
       <c r="A52" s="4" t="s">
         <v>1604</v>
       </c>
@@ -15875,7 +16678,7 @@
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" ht="15">
       <c r="A53" s="4" t="s">
         <v>1605</v>
       </c>
@@ -15888,7 +16691,7 @@
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" ht="15">
       <c r="A54" s="4" t="s">
         <v>1606</v>
       </c>
@@ -15899,7 +16702,7 @@
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" ht="15">
       <c r="A55" s="4" t="s">
         <v>1607</v>
       </c>
@@ -15910,7 +16713,7 @@
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" ht="15">
       <c r="A56" s="4" t="s">
         <v>1608</v>
       </c>
@@ -15921,7 +16724,7 @@
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" ht="15">
       <c r="A57" s="4" t="s">
         <v>1609</v>
       </c>
@@ -15932,7 +16735,7 @@
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" ht="15">
       <c r="A58" s="4" t="s">
         <v>1610</v>
       </c>
@@ -15943,7 +16746,7 @@
       <c r="F58" s="4"/>
       <c r="G58" s="4"/>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" ht="15">
       <c r="A59" s="4" t="s">
         <v>1611</v>
       </c>
@@ -18099,11 +18902,11 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="F2" r:id="rId2"/>
-    <hyperlink ref="G2" r:id="rId3"/>
-    <hyperlink ref="B12" r:id="rId4"/>
-    <hyperlink ref="C14" r:id="rId5"/>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
+    <hyperlink ref="F2" r:id="rId2" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
+    <hyperlink ref="G2" r:id="rId3" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
+    <hyperlink ref="B12" r:id="rId4" xr:uid="{00000000-0004-0000-0500-000003000000}"/>
+    <hyperlink ref="C14" r:id="rId5" xr:uid="{00000000-0004-0000-0500-000004000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
@@ -18111,14 +18914,14 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="27.875" customWidth="1"/>
-    <col min="2" max="2" width="24.875" customWidth="1"/>
-    <col min="3" max="3" width="35.625" customWidth="1"/>
-    <col min="4" max="4" width="17.625" customWidth="1"/>
+    <col min="1" max="1" width="27.83203125" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" customWidth="1"/>
+    <col min="3" max="3" width="35.6640625" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -18313,13 +19116,13 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D89"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="31.25" customWidth="1"/>
-    <col min="3" max="3" width="88.375" customWidth="1"/>
-    <col min="4" max="4" width="52.25" customWidth="1"/>
+    <col min="2" max="2" width="31.1640625" customWidth="1"/>
+    <col min="3" max="3" width="88.33203125" customWidth="1"/>
+    <col min="4" max="4" width="52.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -18466,7 +19269,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="24">
+    <row r="15" spans="1:4" ht="26">
       <c r="A15" s="40"/>
       <c r="B15" s="11" t="s">
         <v>451</v>
@@ -18500,7 +19303,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="24">
+    <row r="18" spans="1:4" ht="26">
       <c r="A18" s="29"/>
       <c r="B18" s="32"/>
       <c r="C18" s="35"/>
@@ -18528,7 +19331,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="24">
+    <row r="21" spans="1:4" ht="26">
       <c r="A21" s="29"/>
       <c r="B21" s="11" t="s">
         <v>467</v>
@@ -18574,7 +19377,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="24">
+    <row r="25" spans="1:4" ht="26">
       <c r="A25" s="29"/>
       <c r="B25" s="11" t="s">
         <v>475</v>
@@ -18608,7 +19411,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="36">
+    <row r="28" spans="1:4" ht="39">
       <c r="A28" s="40"/>
       <c r="B28" s="11" t="s">
         <v>481</v>
@@ -18634,7 +19437,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="24">
+    <row r="30" spans="1:4" ht="26">
       <c r="A30" s="29"/>
       <c r="B30" s="32"/>
       <c r="C30" s="35"/>
@@ -18792,7 +19595,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="48">
+    <row r="49" spans="1:4" ht="52">
       <c r="A49" s="29"/>
       <c r="B49" s="33"/>
       <c r="C49" s="10" t="s">
@@ -18822,7 +19625,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="24">
+    <row r="52" spans="1:4" ht="26">
       <c r="A52" s="29"/>
       <c r="B52" s="11" t="s">
         <v>479</v>
@@ -18854,7 +19657,7 @@
       </c>
       <c r="D54" s="19"/>
     </row>
-    <row r="55" spans="1:4" ht="72">
+    <row r="55" spans="1:4" ht="78">
       <c r="A55" s="29"/>
       <c r="B55" s="13" t="s">
         <v>517</v>
@@ -19074,7 +19877,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="36">
+    <row r="81" spans="1:4" ht="39">
       <c r="A81" s="29"/>
       <c r="B81" s="11" t="s">
         <v>550</v>
@@ -19108,7 +19911,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="24">
+    <row r="84" spans="1:4" ht="26">
       <c r="A84" s="29"/>
       <c r="B84" s="11" t="s">
         <v>556</v>
@@ -19138,7 +19941,7 @@
       </c>
       <c r="D86" s="19"/>
     </row>
-    <row r="87" spans="1:4" ht="120">
+    <row r="87" spans="1:4" ht="130">
       <c r="A87" s="29"/>
       <c r="B87" s="13" t="s">
         <v>813</v>
@@ -19190,11 +19993,11 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:A31"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="89.75" customWidth="1"/>
+    <col min="1" max="1" width="89.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
@@ -19353,36 +20156,36 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1"/>
-    <hyperlink ref="A2" r:id="rId2"/>
-    <hyperlink ref="A3" r:id="rId3"/>
-    <hyperlink ref="A4" r:id="rId4"/>
-    <hyperlink ref="A5" r:id="rId5"/>
-    <hyperlink ref="A6" r:id="rId6"/>
-    <hyperlink ref="A7" r:id="rId7"/>
-    <hyperlink ref="A8" r:id="rId8"/>
-    <hyperlink ref="A9" r:id="rId9"/>
-    <hyperlink ref="A10" r:id="rId10"/>
-    <hyperlink ref="A11" r:id="rId11"/>
-    <hyperlink ref="A12" r:id="rId12"/>
-    <hyperlink ref="A13" r:id="rId13"/>
-    <hyperlink ref="A14" r:id="rId14"/>
-    <hyperlink ref="A15" r:id="rId15"/>
-    <hyperlink ref="A16" r:id="rId16"/>
-    <hyperlink ref="A17" r:id="rId17"/>
-    <hyperlink ref="A18" r:id="rId18"/>
-    <hyperlink ref="A19" r:id="rId19"/>
-    <hyperlink ref="A20" r:id="rId20"/>
-    <hyperlink ref="A21" r:id="rId21"/>
-    <hyperlink ref="A22" r:id="rId22"/>
-    <hyperlink ref="A23" r:id="rId23"/>
-    <hyperlink ref="A24" r:id="rId24"/>
-    <hyperlink ref="A25" r:id="rId25"/>
-    <hyperlink ref="A26" r:id="rId26"/>
-    <hyperlink ref="A27" r:id="rId27"/>
-    <hyperlink ref="A28" r:id="rId28"/>
-    <hyperlink ref="A29" r:id="rId29"/>
-    <hyperlink ref="A30" r:id="rId30"/>
+    <hyperlink ref="A1" r:id="rId1" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
+    <hyperlink ref="A2" r:id="rId2" xr:uid="{00000000-0004-0000-0800-000001000000}"/>
+    <hyperlink ref="A3" r:id="rId3" xr:uid="{00000000-0004-0000-0800-000002000000}"/>
+    <hyperlink ref="A4" r:id="rId4" xr:uid="{00000000-0004-0000-0800-000003000000}"/>
+    <hyperlink ref="A5" r:id="rId5" xr:uid="{00000000-0004-0000-0800-000004000000}"/>
+    <hyperlink ref="A6" r:id="rId6" xr:uid="{00000000-0004-0000-0800-000005000000}"/>
+    <hyperlink ref="A7" r:id="rId7" xr:uid="{00000000-0004-0000-0800-000006000000}"/>
+    <hyperlink ref="A8" r:id="rId8" xr:uid="{00000000-0004-0000-0800-000007000000}"/>
+    <hyperlink ref="A9" r:id="rId9" xr:uid="{00000000-0004-0000-0800-000008000000}"/>
+    <hyperlink ref="A10" r:id="rId10" xr:uid="{00000000-0004-0000-0800-000009000000}"/>
+    <hyperlink ref="A11" r:id="rId11" xr:uid="{00000000-0004-0000-0800-00000A000000}"/>
+    <hyperlink ref="A12" r:id="rId12" xr:uid="{00000000-0004-0000-0800-00000B000000}"/>
+    <hyperlink ref="A13" r:id="rId13" xr:uid="{00000000-0004-0000-0800-00000C000000}"/>
+    <hyperlink ref="A14" r:id="rId14" xr:uid="{00000000-0004-0000-0800-00000D000000}"/>
+    <hyperlink ref="A15" r:id="rId15" xr:uid="{00000000-0004-0000-0800-00000E000000}"/>
+    <hyperlink ref="A16" r:id="rId16" xr:uid="{00000000-0004-0000-0800-00000F000000}"/>
+    <hyperlink ref="A17" r:id="rId17" xr:uid="{00000000-0004-0000-0800-000010000000}"/>
+    <hyperlink ref="A18" r:id="rId18" xr:uid="{00000000-0004-0000-0800-000011000000}"/>
+    <hyperlink ref="A19" r:id="rId19" xr:uid="{00000000-0004-0000-0800-000012000000}"/>
+    <hyperlink ref="A20" r:id="rId20" xr:uid="{00000000-0004-0000-0800-000013000000}"/>
+    <hyperlink ref="A21" r:id="rId21" xr:uid="{00000000-0004-0000-0800-000014000000}"/>
+    <hyperlink ref="A22" r:id="rId22" xr:uid="{00000000-0004-0000-0800-000015000000}"/>
+    <hyperlink ref="A23" r:id="rId23" xr:uid="{00000000-0004-0000-0800-000016000000}"/>
+    <hyperlink ref="A24" r:id="rId24" xr:uid="{00000000-0004-0000-0800-000017000000}"/>
+    <hyperlink ref="A25" r:id="rId25" xr:uid="{00000000-0004-0000-0800-000018000000}"/>
+    <hyperlink ref="A26" r:id="rId26" xr:uid="{00000000-0004-0000-0800-000019000000}"/>
+    <hyperlink ref="A27" r:id="rId27" xr:uid="{00000000-0004-0000-0800-00001A000000}"/>
+    <hyperlink ref="A28" r:id="rId28" xr:uid="{00000000-0004-0000-0800-00001B000000}"/>
+    <hyperlink ref="A29" r:id="rId29" xr:uid="{00000000-0004-0000-0800-00001C000000}"/>
+    <hyperlink ref="A30" r:id="rId30" xr:uid="{00000000-0004-0000-0800-00001D000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId31"/>

--- a/notes/langnote.xlsx
+++ b/notes/langnote.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ibqo/Develop/git/github/LangNote/notes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D3C61F1-74A3-6C44-8B17-B70DEDA5E297}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28876BA6-791C-A442-8814-918FEC2661E5}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5200" yWindow="1120" windowWidth="22480" windowHeight="11300" firstSheet="2" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2082" uniqueCount="2003">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2084" uniqueCount="2005">
   <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -7234,6 +7234,14 @@
   </si>
   <si>
     <t>索引类型 高可用架构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基金从业资格证 考取</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MyBatis 用法 三方框架开发 写demo 整理面试题 应用题</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8481,6 +8489,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DC7242D-34A4-514D-94C8-37221C34C339}">
   <dimension ref="A1:C100"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <cols>
+    <col min="2" max="2" width="43.5" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -8864,82 +8875,88 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="81" spans="1:1">
+    <row r="81" spans="1:2">
       <c r="A81" s="1" t="s">
         <v>1975</v>
       </c>
-    </row>
-    <row r="82" spans="1:1">
+      <c r="B81" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
       <c r="A82" s="1" t="s">
         <v>1976</v>
       </c>
-    </row>
-    <row r="83" spans="1:1">
+      <c r="B82" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
       <c r="A83" s="1" t="s">
         <v>1977</v>
       </c>
     </row>
-    <row r="84" spans="1:1">
+    <row r="84" spans="1:2">
       <c r="A84" s="1" t="s">
         <v>1978</v>
       </c>
     </row>
-    <row r="85" spans="1:1">
+    <row r="85" spans="1:2">
       <c r="A85" s="1" t="s">
         <v>1979</v>
       </c>
     </row>
-    <row r="86" spans="1:1">
+    <row r="86" spans="1:2">
       <c r="A86" s="1" t="s">
         <v>1980</v>
       </c>
     </row>
-    <row r="87" spans="1:1">
+    <row r="87" spans="1:2">
       <c r="A87" s="1" t="s">
         <v>1981</v>
       </c>
     </row>
-    <row r="88" spans="1:1">
+    <row r="88" spans="1:2">
       <c r="A88" s="1" t="s">
         <v>1982</v>
       </c>
     </row>
-    <row r="89" spans="1:1">
+    <row r="89" spans="1:2">
       <c r="A89" s="1" t="s">
         <v>1983</v>
       </c>
     </row>
-    <row r="90" spans="1:1">
+    <row r="90" spans="1:2">
       <c r="A90" s="1" t="s">
         <v>1984</v>
       </c>
     </row>
-    <row r="91" spans="1:1">
+    <row r="91" spans="1:2">
       <c r="A91" s="1" t="s">
         <v>1985</v>
       </c>
     </row>
-    <row r="92" spans="1:1">
+    <row r="92" spans="1:2">
       <c r="A92" s="1" t="s">
         <v>1986</v>
       </c>
     </row>
-    <row r="93" spans="1:1">
+    <row r="93" spans="1:2">
       <c r="A93" s="1" t="s">
         <v>1987</v>
       </c>
     </row>
-    <row r="94" spans="1:1">
+    <row r="94" spans="1:2">
       <c r="A94" s="1" t="s">
         <v>1988</v>
       </c>
     </row>
-    <row r="95" spans="1:1">
+    <row r="95" spans="1:2">
       <c r="A95" s="1" t="s">
         <v>1989</v>
       </c>
     </row>
-    <row r="96" spans="1:1">
+    <row r="96" spans="1:2">
       <c r="A96" s="1" t="s">
         <v>1990</v>
       </c>

--- a/notes/langnote.xlsx
+++ b/notes/langnote.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ibqo/Develop/git/github/LangNote/notes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28876BA6-791C-A442-8814-918FEC2661E5}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA14FBB5-9662-BD4E-BF51-F3566374EC34}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5200" yWindow="1120" windowWidth="22480" windowHeight="11300" firstSheet="2" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2084" uniqueCount="2005">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2087" uniqueCount="2008">
   <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -7242,6 +7242,18 @@
   </si>
   <si>
     <t>MyBatis 用法 三方框架开发 写demo 整理面试题 应用题</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>mybatis B站视频 三千万大表 学习</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>国际政治学 B站视频</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>考虑搭建rpm 镜像</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8875,7 +8887,7 @@
         <v>2002</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:3">
       <c r="A81" s="1" t="s">
         <v>1975</v>
       </c>
@@ -8883,7 +8895,7 @@
         <v>2003</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:3">
       <c r="A82" s="1" t="s">
         <v>1976</v>
       </c>
@@ -8891,72 +8903,81 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:3">
       <c r="A83" s="1" t="s">
         <v>1977</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:3">
       <c r="A84" s="1" t="s">
         <v>1978</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:3">
       <c r="A85" s="1" t="s">
         <v>1979</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:3">
       <c r="A86" s="1" t="s">
         <v>1980</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:3">
       <c r="A87" s="1" t="s">
         <v>1981</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:3">
       <c r="A88" s="1" t="s">
         <v>1982</v>
       </c>
-    </row>
-    <row r="89" spans="1:2">
+      <c r="B88" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
       <c r="A89" s="1" t="s">
         <v>1983</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:3">
       <c r="A90" s="1" t="s">
         <v>1984</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" spans="1:3">
       <c r="A91" s="1" t="s">
         <v>1985</v>
       </c>
-    </row>
-    <row r="92" spans="1:2">
+      <c r="B91" t="s">
+        <v>2005</v>
+      </c>
+      <c r="C91" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
       <c r="A92" s="1" t="s">
         <v>1986</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:3">
       <c r="A93" s="1" t="s">
         <v>1987</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:3">
       <c r="A94" s="1" t="s">
         <v>1988</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" spans="1:3">
       <c r="A95" s="1" t="s">
         <v>1989</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" spans="1:3">
       <c r="A96" s="1" t="s">
         <v>1990</v>
       </c>

--- a/notes/langnote.xlsx
+++ b/notes/langnote.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10414"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23801"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ibqo/Develop/git/github/LangNote/notes/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\langnote\notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA14FBB5-9662-BD4E-BF51-F3566374EC34}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D32BBD5-4F55-4E6F-A4B1-1F92C175559B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5200" yWindow="1120" windowWidth="22480" windowHeight="11300" firstSheet="2" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2014" sheetId="9" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2087" uniqueCount="2008">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2093" uniqueCount="2013">
   <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -7254,6 +7254,25 @@
   </si>
   <si>
     <t>考虑搭建rpm 镜像</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>git@github.com:edidada/testoracle.git</t>
+  </si>
+  <si>
+    <t>Oracle入门学习</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>java注解</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>apache commons</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shell</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -8088,7 +8107,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
@@ -8330,137 +8349,162 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:A26"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <dimension ref="A1:C28"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="75.5" customWidth="1"/>
+    <col min="2" max="2" width="45.875" customWidth="1"/>
+    <col min="3" max="3" width="16.125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:3">
       <c r="A1" s="26" t="s">
         <v>1514</v>
       </c>
-    </row>
-    <row r="2" spans="1:1">
+      <c r="C1" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" s="26" t="s">
         <v>1515</v>
       </c>
-    </row>
-    <row r="3" spans="1:1">
+      <c r="C2" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" s="26" t="s">
         <v>1516</v>
       </c>
-    </row>
-    <row r="4" spans="1:1">
+      <c r="C3" t="s">
+        <v>1469</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" s="26" t="s">
         <v>1520</v>
       </c>
-    </row>
-    <row r="5" spans="1:1">
+      <c r="C4" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" s="26" t="s">
         <v>1521</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:3">
       <c r="A6" s="26" t="s">
         <v>1522</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:3">
       <c r="A7" s="26" t="s">
         <v>1523</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:3">
       <c r="A8" s="26" t="s">
         <v>1524</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:3">
       <c r="A9" s="26" t="s">
         <v>1525</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:3">
       <c r="A10" s="26" t="s">
         <v>1526</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:3">
       <c r="A11" s="26" t="s">
         <v>1527</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:3">
       <c r="A12" s="26" t="s">
         <v>1528</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:3">
       <c r="A13" s="26" t="s">
         <v>1542</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:3">
       <c r="A14" s="26" t="s">
         <v>1529</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:3">
       <c r="A15" s="26" t="s">
         <v>1530</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:3">
       <c r="A16" s="26" t="s">
         <v>1531</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:3">
       <c r="A17" s="26" t="s">
         <v>1532</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:3">
       <c r="A18" s="26" t="s">
         <v>1533</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:3">
       <c r="A19" s="26" t="s">
         <v>1534</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:3">
       <c r="A20" s="26" t="s">
         <v>1535</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:3">
       <c r="A21" s="26" t="s">
         <v>1536</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:3">
       <c r="A22" s="26" t="s">
         <v>1537</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:3">
       <c r="A23" s="26" t="s">
         <v>1538</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:3">
       <c r="A24" s="26" t="s">
         <v>1539</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:3">
       <c r="A25" s="26" t="s">
         <v>1540</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:3">
       <c r="A26" s="26" t="s">
         <v>1541</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>2008</v>
+      </c>
+      <c r="C28" t="s">
+        <v>2009</v>
       </c>
     </row>
   </sheetData>
@@ -8500,7 +8544,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DC7242D-34A4-514D-94C8-37221C34C339}">
   <dimension ref="A1:C100"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="43.5" customWidth="1"/>
   </cols>
@@ -9005,15 +9049,16 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="2" max="2" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -9056,7 +9101,7 @@
         <v>1876</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="45">
+    <row r="6" spans="1:3" ht="40.5">
       <c r="A6" s="1" t="s">
         <v>1852</v>
       </c>
@@ -9069,7 +9114,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="30">
+    <row r="8" spans="1:3" ht="27">
       <c r="A8" s="1" t="s">
         <v>1854</v>
       </c>
@@ -9115,9 +9160,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="2" max="2" width="21.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -9201,14 +9246,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G366"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="54.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.6640625" customWidth="1"/>
-    <col min="4" max="4" width="40.33203125" customWidth="1"/>
-    <col min="5" max="5" width="31.33203125" customWidth="1"/>
-    <col min="6" max="6" width="21.1640625" customWidth="1"/>
+    <col min="2" max="2" width="54.875" customWidth="1"/>
+    <col min="3" max="3" width="30.625" customWidth="1"/>
+    <col min="4" max="4" width="40.375" customWidth="1"/>
+    <col min="5" max="5" width="31.375" customWidth="1"/>
+    <col min="6" max="6" width="21.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -9219,7 +9264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="24.5" customHeight="1">
+    <row r="2" spans="1:2" ht="24.6" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1003</v>
       </c>
@@ -9304,7 +9349,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="30">
+    <row r="19" spans="1:5" ht="27">
       <c r="A19" s="1" t="s">
         <v>1020</v>
       </c>
@@ -9395,12 +9440,12 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="11.5" customHeight="1">
+    <row r="27" spans="1:5" ht="11.45" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>1028</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="11.5" customHeight="1">
+    <row r="28" spans="1:5" ht="11.45" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>1029</v>
       </c>
@@ -9408,7 +9453,7 @@
         <v>1902</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="11.5" customHeight="1">
+    <row r="29" spans="1:5" ht="11.45" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>1030</v>
       </c>
@@ -9416,17 +9461,17 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="11.5" customHeight="1">
+    <row r="30" spans="1:5" ht="11.45" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>1031</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="11.5" customHeight="1">
+    <row r="31" spans="1:5" ht="11.45" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>1032</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="11.5" customHeight="1">
+    <row r="32" spans="1:5" ht="11.45" customHeight="1">
       <c r="A32" s="1" t="s">
         <v>1033</v>
       </c>
@@ -9512,7 +9557,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="35.5" customHeight="1">
+    <row r="45" spans="1:6" ht="35.450000000000003" customHeight="1">
       <c r="A45" s="1" t="s">
         <v>10</v>
       </c>
@@ -9640,7 +9685,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="45">
+    <row r="58" spans="1:5" ht="40.5">
       <c r="A58" s="1" t="s">
         <v>34</v>
       </c>
@@ -9659,7 +9704,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="30">
+    <row r="60" spans="1:5" ht="27">
       <c r="A60" s="1" t="s">
         <v>39</v>
       </c>
@@ -9708,7 +9753,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="15">
+    <row r="65" spans="1:7">
       <c r="A65" s="1" t="s">
         <v>57</v>
       </c>
@@ -9716,7 +9761,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="15">
+    <row r="66" spans="1:7">
       <c r="A66" s="1" t="s">
         <v>58</v>
       </c>
@@ -9788,7 +9833,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="15">
+    <row r="72" spans="1:7">
       <c r="A72" s="1" t="s">
         <v>67</v>
       </c>
@@ -9829,7 +9874,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="15">
+    <row r="76" spans="1:7">
       <c r="A76" s="1" t="s">
         <v>92</v>
       </c>
@@ -10022,7 +10067,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="45">
+    <row r="102" spans="1:3" ht="40.5">
       <c r="A102" s="1" t="s">
         <v>121</v>
       </c>
@@ -10153,7 +10198,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="15">
+    <row r="121" spans="1:6">
       <c r="A121" s="1" t="s">
         <v>149</v>
       </c>
@@ -11603,17 +11648,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:L368"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="28.1640625" customWidth="1"/>
+    <col min="1" max="1" width="28.125" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
-    <col min="3" max="3" width="31.33203125" customWidth="1"/>
-    <col min="4" max="4" width="55.1640625" customWidth="1"/>
-    <col min="5" max="5" width="33.33203125" customWidth="1"/>
+    <col min="3" max="3" width="31.375" customWidth="1"/>
+    <col min="4" max="4" width="55.125" customWidth="1"/>
+    <col min="5" max="5" width="33.375" customWidth="1"/>
     <col min="6" max="6" width="18.5" customWidth="1"/>
     <col min="7" max="7" width="25.5" customWidth="1"/>
-    <col min="8" max="8" width="17.1640625" customWidth="1"/>
-    <col min="9" max="9" width="18.33203125" customWidth="1"/>
+    <col min="8" max="8" width="17.125" customWidth="1"/>
+    <col min="9" max="9" width="18.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -12230,7 +12275,7 @@
         <v>1447</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="45">
+    <row r="104" spans="1:9" ht="40.5">
       <c r="A104" s="1" t="s">
         <v>237</v>
       </c>
@@ -12264,7 +12309,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="45">
+    <row r="106" spans="1:9" ht="40.5">
       <c r="A106" s="1" t="s">
         <v>239</v>
       </c>
@@ -12323,7 +12368,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="30">
+    <row r="110" spans="1:9" ht="27">
       <c r="A110" s="1" t="s">
         <v>241</v>
       </c>
@@ -12386,7 +12431,7 @@
         <v>1793</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="105">
+    <row r="116" spans="1:9" ht="94.5">
       <c r="A116" s="1" t="s">
         <v>246</v>
       </c>
@@ -12415,7 +12460,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="30">
+    <row r="117" spans="1:9" ht="27">
       <c r="A117" s="1" t="s">
         <v>247</v>
       </c>
@@ -12454,7 +12499,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="30">
+    <row r="120" spans="1:9" ht="27">
       <c r="A120" s="1" t="s">
         <v>250</v>
       </c>
@@ -12476,7 +12521,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="30">
+    <row r="122" spans="1:9" ht="27">
       <c r="A122" s="1" t="s">
         <v>252</v>
       </c>
@@ -12487,7 +12532,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="30">
+    <row r="123" spans="1:9" ht="27">
       <c r="A123" s="1" t="s">
         <v>253</v>
       </c>
@@ -12495,7 +12540,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="60">
+    <row r="124" spans="1:9" ht="54">
       <c r="A124" s="1" t="s">
         <v>286</v>
       </c>
@@ -12576,7 +12621,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="130" spans="1:6" ht="30">
+    <row r="130" spans="1:6" ht="27">
       <c r="A130" s="1" t="s">
         <v>292</v>
       </c>
@@ -12649,7 +12694,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="135" spans="1:6" ht="30">
+    <row r="135" spans="1:6" ht="27">
       <c r="A135" s="1" t="s">
         <v>297</v>
       </c>
@@ -12679,7 +12724,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="138" spans="1:6" ht="30">
+    <row r="138" spans="1:6" ht="27">
       <c r="A138" s="1" t="s">
         <v>300</v>
       </c>
@@ -12781,7 +12826,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="16">
+    <row r="147" spans="1:5" ht="15">
       <c r="A147" s="1" t="s">
         <v>309</v>
       </c>
@@ -12798,7 +12843,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="30">
+    <row r="148" spans="1:5" ht="27">
       <c r="A148" s="1" t="s">
         <v>310</v>
       </c>
@@ -12812,7 +12857,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="30">
+    <row r="149" spans="1:5" ht="27">
       <c r="A149" s="1" t="s">
         <v>311</v>
       </c>
@@ -12834,7 +12879,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="45">
+    <row r="151" spans="1:5" ht="40.5">
       <c r="A151" s="1" t="s">
         <v>313</v>
       </c>
@@ -12856,7 +12901,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="30">
+    <row r="153" spans="1:5" ht="27">
       <c r="A153" s="1" t="s">
         <v>315</v>
       </c>
@@ -12901,7 +12946,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="30">
+    <row r="159" spans="1:5" ht="27">
       <c r="A159" s="1" t="s">
         <v>335</v>
       </c>
@@ -12928,7 +12973,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="162" spans="1:8" ht="30">
+    <row r="162" spans="1:8" ht="27">
       <c r="A162" s="1" t="s">
         <v>338</v>
       </c>
@@ -12961,7 +13006,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="165" spans="1:8" ht="30">
+    <row r="165" spans="1:8" ht="27">
       <c r="A165" s="1" t="s">
         <v>341</v>
       </c>
@@ -12981,7 +13026,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="166" spans="1:8" ht="60">
+    <row r="166" spans="1:8" ht="54">
       <c r="A166" s="1" t="s">
         <v>342</v>
       </c>
@@ -13044,7 +13089,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="172" spans="1:8" ht="45">
+    <row r="172" spans="1:8" ht="40.5">
       <c r="A172" s="1" t="s">
         <v>348</v>
       </c>
@@ -13089,7 +13134,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="175" spans="1:8" ht="30">
+    <row r="175" spans="1:8" ht="27">
       <c r="A175" s="1" t="s">
         <v>351</v>
       </c>
@@ -13108,7 +13153,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="30">
+    <row r="177" spans="1:6" ht="27">
       <c r="A177" s="1" t="s">
         <v>353</v>
       </c>
@@ -13119,7 +13164,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="178" spans="1:6" ht="30">
+    <row r="178" spans="1:6" ht="27">
       <c r="A178" s="1" t="s">
         <v>354</v>
       </c>
@@ -13130,7 +13175,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="179" spans="1:6" ht="15">
+    <row r="179" spans="1:6">
       <c r="A179" s="1" t="s">
         <v>355</v>
       </c>
@@ -13269,7 +13314,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="190" spans="1:6" ht="45">
+    <row r="190" spans="1:6" ht="40.5">
       <c r="A190" s="1" t="s">
         <v>383</v>
       </c>
@@ -13283,7 +13328,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="30">
+    <row r="191" spans="1:6" ht="27">
       <c r="A191" s="1" t="s">
         <v>384</v>
       </c>
@@ -13308,7 +13353,7 @@
         <v>1796</v>
       </c>
     </row>
-    <row r="193" spans="1:7" ht="60">
+    <row r="193" spans="1:7" ht="54">
       <c r="A193" s="1" t="s">
         <v>386</v>
       </c>
@@ -13350,7 +13395,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="196" spans="1:7" ht="30">
+    <row r="196" spans="1:7" ht="27">
       <c r="A196" s="1" t="s">
         <v>389</v>
       </c>
@@ -13375,7 +13420,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="198" spans="1:7" ht="30">
+    <row r="198" spans="1:7" ht="27">
       <c r="A198" s="1" t="s">
         <v>391</v>
       </c>
@@ -13400,7 +13445,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="200" spans="1:7" ht="30">
+    <row r="200" spans="1:7" ht="27">
       <c r="A200" s="1" t="s">
         <v>393</v>
       </c>
@@ -13411,7 +13456,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="201" spans="1:7" ht="75">
+    <row r="201" spans="1:7" ht="67.5">
       <c r="A201" s="1" t="s">
         <v>394</v>
       </c>
@@ -13422,7 +13467,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="202" spans="1:7" ht="30">
+    <row r="202" spans="1:7" ht="27">
       <c r="A202" s="1" t="s">
         <v>395</v>
       </c>
@@ -13469,7 +13514,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="206" spans="1:7" ht="15">
+    <row r="206" spans="1:7">
       <c r="A206" s="1" t="s">
         <v>399</v>
       </c>
@@ -13508,7 +13553,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="209" spans="1:6" ht="30">
+    <row r="209" spans="1:6" ht="27">
       <c r="A209" s="1" t="s">
         <v>402</v>
       </c>
@@ -13530,7 +13575,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="211" spans="1:6" ht="30">
+    <row r="211" spans="1:6" ht="27">
       <c r="A211" s="1" t="s">
         <v>404</v>
       </c>
@@ -13541,7 +13586,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="212" spans="1:6" ht="15">
+    <row r="212" spans="1:6" ht="27">
       <c r="A212" s="1" t="s">
         <v>405</v>
       </c>
@@ -13552,7 +13597,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="213" spans="1:6" ht="30">
+    <row r="213" spans="1:6" ht="27">
       <c r="A213" s="1" t="s">
         <v>406</v>
       </c>
@@ -13577,7 +13622,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="215" spans="1:6" ht="30">
+    <row r="215" spans="1:6" ht="27">
       <c r="A215" s="1" t="s">
         <v>566</v>
       </c>
@@ -13585,7 +13630,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="216" spans="1:6" ht="15">
+    <row r="216" spans="1:6">
       <c r="A216" s="1" t="s">
         <v>567</v>
       </c>
@@ -13593,7 +13638,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="217" spans="1:6" ht="15">
+    <row r="217" spans="1:6">
       <c r="A217" s="1" t="s">
         <v>568</v>
       </c>
@@ -13604,7 +13649,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="218" spans="1:6" ht="15">
+    <row r="218" spans="1:6">
       <c r="A218" s="1" t="s">
         <v>569</v>
       </c>
@@ -13612,7 +13657,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="219" spans="1:6" ht="30">
+    <row r="219" spans="1:6" ht="27">
       <c r="A219" s="1" t="s">
         <v>570</v>
       </c>
@@ -13626,7 +13671,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="220" spans="1:6" ht="15">
+    <row r="220" spans="1:6">
       <c r="A220" s="1" t="s">
         <v>571</v>
       </c>
@@ -13648,7 +13693,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="222" spans="1:6" ht="15">
+    <row r="222" spans="1:6">
       <c r="A222" s="1" t="s">
         <v>573</v>
       </c>
@@ -13767,7 +13812,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="232" spans="1:6" ht="30">
+    <row r="232" spans="1:6" ht="27">
       <c r="A232" s="1" t="s">
         <v>583</v>
       </c>
@@ -13826,7 +13871,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="239" spans="1:6" ht="30">
+    <row r="239" spans="1:6" ht="27">
       <c r="A239" s="1" t="s">
         <v>590</v>
       </c>
@@ -13865,7 +13910,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="242" spans="1:5" ht="30">
+    <row r="242" spans="1:5" ht="27">
       <c r="A242" s="1" t="s">
         <v>593</v>
       </c>
@@ -14167,7 +14212,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="285" spans="1:12" ht="15">
+    <row r="285" spans="1:12">
       <c r="A285" s="1" t="s">
         <v>646</v>
       </c>
@@ -14189,7 +14234,7 @@
       <c r="K285" s="2"/>
       <c r="L285" s="2"/>
     </row>
-    <row r="286" spans="1:12" ht="30">
+    <row r="286" spans="1:12" ht="27">
       <c r="A286" s="1" t="s">
         <v>647</v>
       </c>
@@ -14213,7 +14258,7 @@
       <c r="K286" s="2"/>
       <c r="L286" s="2"/>
     </row>
-    <row r="287" spans="1:12" ht="75">
+    <row r="287" spans="1:12" ht="67.5">
       <c r="A287" s="1" t="s">
         <v>648</v>
       </c>
@@ -14239,7 +14284,7 @@
       <c r="K287" s="2"/>
       <c r="L287" s="2"/>
     </row>
-    <row r="288" spans="1:12" ht="15">
+    <row r="288" spans="1:12">
       <c r="A288" s="1" t="s">
         <v>649</v>
       </c>
@@ -14263,7 +14308,7 @@
       <c r="K288" s="2"/>
       <c r="L288" s="2"/>
     </row>
-    <row r="289" spans="1:12" ht="30">
+    <row r="289" spans="1:12" ht="27">
       <c r="A289" s="1" t="s">
         <v>650</v>
       </c>
@@ -14285,7 +14330,7 @@
       <c r="K289" s="2"/>
       <c r="L289" s="2"/>
     </row>
-    <row r="290" spans="1:12" ht="30">
+    <row r="290" spans="1:12" ht="27">
       <c r="A290" s="1" t="s">
         <v>651</v>
       </c>
@@ -14303,7 +14348,7 @@
       <c r="K290" s="2"/>
       <c r="L290" s="2"/>
     </row>
-    <row r="291" spans="1:12" ht="45">
+    <row r="291" spans="1:12" ht="40.5">
       <c r="A291" s="1" t="s">
         <v>652</v>
       </c>
@@ -14327,7 +14372,7 @@
       <c r="K291" s="2"/>
       <c r="L291" s="2"/>
     </row>
-    <row r="292" spans="1:12" ht="30">
+    <row r="292" spans="1:12" ht="27">
       <c r="A292" s="1" t="s">
         <v>653</v>
       </c>
@@ -14367,7 +14412,7 @@
       <c r="K293" s="2"/>
       <c r="L293" s="2"/>
     </row>
-    <row r="294" spans="1:12" ht="15">
+    <row r="294" spans="1:12">
       <c r="A294" s="1" t="s">
         <v>655</v>
       </c>
@@ -14385,7 +14430,7 @@
       <c r="K294" s="2"/>
       <c r="L294" s="2"/>
     </row>
-    <row r="295" spans="1:12" ht="15">
+    <row r="295" spans="1:12">
       <c r="A295" s="1" t="s">
         <v>656</v>
       </c>
@@ -14403,7 +14448,7 @@
       <c r="K295" s="2"/>
       <c r="L295" s="2"/>
     </row>
-    <row r="296" spans="1:12" ht="15">
+    <row r="296" spans="1:12">
       <c r="A296" s="1" t="s">
         <v>657</v>
       </c>
@@ -14421,7 +14466,7 @@
       <c r="K296" s="2"/>
       <c r="L296" s="2"/>
     </row>
-    <row r="297" spans="1:12" ht="15">
+    <row r="297" spans="1:12">
       <c r="A297" s="1" t="s">
         <v>658</v>
       </c>
@@ -14455,7 +14500,7 @@
       <c r="K298" s="2"/>
       <c r="L298" s="2"/>
     </row>
-    <row r="299" spans="1:12" ht="15">
+    <row r="299" spans="1:12">
       <c r="A299" s="1" t="s">
         <v>660</v>
       </c>
@@ -14475,7 +14520,7 @@
       <c r="K299" s="2"/>
       <c r="L299" s="2"/>
     </row>
-    <row r="300" spans="1:12" ht="30">
+    <row r="300" spans="1:12" ht="27">
       <c r="A300" s="1" t="s">
         <v>661</v>
       </c>
@@ -14499,7 +14544,7 @@
       <c r="K300" s="2"/>
       <c r="L300" s="2"/>
     </row>
-    <row r="301" spans="1:12" ht="15">
+    <row r="301" spans="1:12">
       <c r="A301" s="1" t="s">
         <v>662</v>
       </c>
@@ -14523,7 +14568,7 @@
       <c r="K301" s="2"/>
       <c r="L301" s="2"/>
     </row>
-    <row r="302" spans="1:12" ht="15">
+    <row r="302" spans="1:12">
       <c r="A302" s="1" t="s">
         <v>663</v>
       </c>
@@ -14541,7 +14586,7 @@
       <c r="K302" s="2"/>
       <c r="L302" s="2"/>
     </row>
-    <row r="303" spans="1:12" ht="15">
+    <row r="303" spans="1:12">
       <c r="A303" s="1" t="s">
         <v>664</v>
       </c>
@@ -14559,7 +14604,7 @@
       <c r="K303" s="2"/>
       <c r="L303" s="2"/>
     </row>
-    <row r="304" spans="1:12" ht="15">
+    <row r="304" spans="1:12">
       <c r="A304" s="1" t="s">
         <v>665</v>
       </c>
@@ -14579,7 +14624,7 @@
       <c r="K304" s="2"/>
       <c r="L304" s="2"/>
     </row>
-    <row r="305" spans="1:12" ht="15">
+    <row r="305" spans="1:12">
       <c r="A305" s="1" t="s">
         <v>666</v>
       </c>
@@ -14599,7 +14644,7 @@
       <c r="K305" s="2"/>
       <c r="L305" s="2"/>
     </row>
-    <row r="306" spans="1:12" ht="15">
+    <row r="306" spans="1:12">
       <c r="A306" s="1" t="s">
         <v>667</v>
       </c>
@@ -14617,7 +14662,7 @@
       <c r="K306" s="2"/>
       <c r="L306" s="2"/>
     </row>
-    <row r="307" spans="1:12" ht="15">
+    <row r="307" spans="1:12">
       <c r="A307" s="1" t="s">
         <v>668</v>
       </c>
@@ -14639,7 +14684,7 @@
       <c r="K307" s="2"/>
       <c r="L307" s="2"/>
     </row>
-    <row r="308" spans="1:12" ht="15">
+    <row r="308" spans="1:12">
       <c r="A308" s="1" t="s">
         <v>776</v>
       </c>
@@ -14657,7 +14702,7 @@
       <c r="K308" s="2"/>
       <c r="L308" s="2"/>
     </row>
-    <row r="309" spans="1:12" ht="15">
+    <row r="309" spans="1:12">
       <c r="A309" s="1" t="s">
         <v>777</v>
       </c>
@@ -14681,7 +14726,7 @@
       <c r="K309" s="2"/>
       <c r="L309" s="2"/>
     </row>
-    <row r="310" spans="1:12" ht="15">
+    <row r="310" spans="1:12">
       <c r="A310" s="1" t="s">
         <v>778</v>
       </c>
@@ -14703,7 +14748,7 @@
       <c r="K310" s="2"/>
       <c r="L310" s="2"/>
     </row>
-    <row r="311" spans="1:12" ht="15">
+    <row r="311" spans="1:12">
       <c r="A311" s="1" t="s">
         <v>779</v>
       </c>
@@ -14723,7 +14768,7 @@
       <c r="K311" s="2"/>
       <c r="L311" s="2"/>
     </row>
-    <row r="312" spans="1:12" ht="30">
+    <row r="312" spans="1:12" ht="27">
       <c r="A312" s="1" t="s">
         <v>780</v>
       </c>
@@ -14743,7 +14788,7 @@
       <c r="K312" s="2"/>
       <c r="L312" s="2"/>
     </row>
-    <row r="313" spans="1:12" ht="15">
+    <row r="313" spans="1:12">
       <c r="A313" s="1" t="s">
         <v>781</v>
       </c>
@@ -14767,7 +14812,7 @@
       <c r="K313" s="2"/>
       <c r="L313" s="2"/>
     </row>
-    <row r="314" spans="1:12" ht="15">
+    <row r="314" spans="1:12">
       <c r="A314" s="1" t="s">
         <v>782</v>
       </c>
@@ -14787,7 +14832,7 @@
       <c r="K314" s="2"/>
       <c r="L314" s="2"/>
     </row>
-    <row r="315" spans="1:12" ht="30">
+    <row r="315" spans="1:12" ht="27">
       <c r="A315" s="1" t="s">
         <v>783</v>
       </c>
@@ -14807,7 +14852,7 @@
       <c r="K315" s="2"/>
       <c r="L315" s="2"/>
     </row>
-    <row r="316" spans="1:12" ht="15">
+    <row r="316" spans="1:12">
       <c r="A316" s="1" t="s">
         <v>784</v>
       </c>
@@ -14829,7 +14874,7 @@
       <c r="K316" s="2"/>
       <c r="L316" s="2"/>
     </row>
-    <row r="317" spans="1:12" ht="30">
+    <row r="317" spans="1:12" ht="27">
       <c r="A317" s="1" t="s">
         <v>785</v>
       </c>
@@ -14853,7 +14898,7 @@
       <c r="K317" s="2"/>
       <c r="L317" s="2"/>
     </row>
-    <row r="318" spans="1:12" ht="15">
+    <row r="318" spans="1:12">
       <c r="A318" s="1" t="s">
         <v>786</v>
       </c>
@@ -14871,7 +14916,7 @@
       <c r="K318" s="2"/>
       <c r="L318" s="2"/>
     </row>
-    <row r="319" spans="1:12" ht="15">
+    <row r="319" spans="1:12">
       <c r="A319" s="1" t="s">
         <v>787</v>
       </c>
@@ -14889,7 +14934,7 @@
       <c r="K319" s="2"/>
       <c r="L319" s="2"/>
     </row>
-    <row r="320" spans="1:12" ht="30">
+    <row r="320" spans="1:12" ht="27">
       <c r="A320" s="1" t="s">
         <v>788</v>
       </c>
@@ -14911,7 +14956,7 @@
       <c r="K320" s="2"/>
       <c r="L320" s="2"/>
     </row>
-    <row r="321" spans="1:12" ht="30">
+    <row r="321" spans="1:12" ht="27">
       <c r="A321" s="1" t="s">
         <v>789</v>
       </c>
@@ -14929,7 +14974,7 @@
       <c r="K321" s="2"/>
       <c r="L321" s="2"/>
     </row>
-    <row r="322" spans="1:12" ht="15">
+    <row r="322" spans="1:12">
       <c r="A322" s="1" t="s">
         <v>790</v>
       </c>
@@ -14949,7 +14994,7 @@
       <c r="K322" s="2"/>
       <c r="L322" s="2"/>
     </row>
-    <row r="323" spans="1:12" ht="15">
+    <row r="323" spans="1:12">
       <c r="A323" s="1" t="s">
         <v>791</v>
       </c>
@@ -14985,7 +15030,7 @@
       <c r="K324" s="2"/>
       <c r="L324" s="2"/>
     </row>
-    <row r="325" spans="1:12" ht="15">
+    <row r="325" spans="1:12">
       <c r="A325" s="1" t="s">
         <v>793</v>
       </c>
@@ -15003,7 +15048,7 @@
       <c r="K325" s="2"/>
       <c r="L325" s="2"/>
     </row>
-    <row r="326" spans="1:12" ht="15">
+    <row r="326" spans="1:12">
       <c r="A326" s="1" t="s">
         <v>794</v>
       </c>
@@ -15021,7 +15066,7 @@
       <c r="K326" s="2"/>
       <c r="L326" s="2"/>
     </row>
-    <row r="327" spans="1:12" ht="15">
+    <row r="327" spans="1:12">
       <c r="A327" s="1" t="s">
         <v>795</v>
       </c>
@@ -15041,7 +15086,7 @@
       <c r="K327" s="2"/>
       <c r="L327" s="2"/>
     </row>
-    <row r="328" spans="1:12" ht="15">
+    <row r="328" spans="1:12">
       <c r="A328" s="1" t="s">
         <v>796</v>
       </c>
@@ -15059,7 +15104,7 @@
       <c r="K328" s="2"/>
       <c r="L328" s="2"/>
     </row>
-    <row r="329" spans="1:12" ht="15">
+    <row r="329" spans="1:12">
       <c r="A329" s="1" t="s">
         <v>797</v>
       </c>
@@ -15079,7 +15124,7 @@
       <c r="K329" s="2"/>
       <c r="L329" s="2"/>
     </row>
-    <row r="330" spans="1:12" ht="30">
+    <row r="330" spans="1:12" ht="27">
       <c r="A330" s="1" t="s">
         <v>798</v>
       </c>
@@ -15103,7 +15148,7 @@
       <c r="K330" s="2"/>
       <c r="L330" s="2"/>
     </row>
-    <row r="331" spans="1:12" ht="15">
+    <row r="331" spans="1:12">
       <c r="A331" s="1" t="s">
         <v>799</v>
       </c>
@@ -15121,7 +15166,7 @@
       <c r="K331" s="2"/>
       <c r="L331" s="2"/>
     </row>
-    <row r="332" spans="1:12" ht="15">
+    <row r="332" spans="1:12">
       <c r="A332" s="1" t="s">
         <v>800</v>
       </c>
@@ -15141,7 +15186,7 @@
       <c r="K332" s="2"/>
       <c r="L332" s="2"/>
     </row>
-    <row r="333" spans="1:12" ht="15">
+    <row r="333" spans="1:12">
       <c r="A333" s="1" t="s">
         <v>801</v>
       </c>
@@ -15165,7 +15210,7 @@
       <c r="K333" s="2"/>
       <c r="L333" s="2"/>
     </row>
-    <row r="334" spans="1:12" ht="15">
+    <row r="334" spans="1:12">
       <c r="A334" s="1" t="s">
         <v>802</v>
       </c>
@@ -15183,7 +15228,7 @@
       <c r="K334" s="2"/>
       <c r="L334" s="2"/>
     </row>
-    <row r="335" spans="1:12" ht="15">
+    <row r="335" spans="1:12">
       <c r="A335" s="1" t="s">
         <v>803</v>
       </c>
@@ -15207,7 +15252,7 @@
       <c r="K335" s="2"/>
       <c r="L335" s="2"/>
     </row>
-    <row r="336" spans="1:12" ht="15">
+    <row r="336" spans="1:12">
       <c r="A336" s="1" t="s">
         <v>820</v>
       </c>
@@ -15227,7 +15272,7 @@
       <c r="K336" s="2"/>
       <c r="L336" s="2"/>
     </row>
-    <row r="337" spans="1:12" ht="15">
+    <row r="337" spans="1:12">
       <c r="A337" s="1" t="s">
         <v>821</v>
       </c>
@@ -15245,7 +15290,7 @@
       <c r="K337" s="2"/>
       <c r="L337" s="2"/>
     </row>
-    <row r="338" spans="1:12" ht="30">
+    <row r="338" spans="1:12" ht="27">
       <c r="A338" s="1" t="s">
         <v>822</v>
       </c>
@@ -15265,7 +15310,7 @@
       <c r="K338" s="2"/>
       <c r="L338" s="2"/>
     </row>
-    <row r="339" spans="1:12" ht="15">
+    <row r="339" spans="1:12">
       <c r="A339" s="1" t="s">
         <v>823</v>
       </c>
@@ -15285,7 +15330,7 @@
       <c r="K339" s="2"/>
       <c r="L339" s="2"/>
     </row>
-    <row r="340" spans="1:12" ht="15">
+    <row r="340" spans="1:12">
       <c r="A340" s="1" t="s">
         <v>824</v>
       </c>
@@ -15305,7 +15350,7 @@
       <c r="K340" s="2"/>
       <c r="L340" s="2"/>
     </row>
-    <row r="341" spans="1:12" ht="15">
+    <row r="341" spans="1:12">
       <c r="A341" s="1" t="s">
         <v>825</v>
       </c>
@@ -15327,7 +15372,7 @@
       <c r="K341" s="2"/>
       <c r="L341" s="2"/>
     </row>
-    <row r="342" spans="1:12" ht="15">
+    <row r="342" spans="1:12">
       <c r="A342" s="1" t="s">
         <v>826</v>
       </c>
@@ -15351,7 +15396,7 @@
       <c r="K342" s="2"/>
       <c r="L342" s="2"/>
     </row>
-    <row r="343" spans="1:12" ht="15">
+    <row r="343" spans="1:12">
       <c r="A343" s="1" t="s">
         <v>827</v>
       </c>
@@ -15369,7 +15414,7 @@
       <c r="K343" s="2"/>
       <c r="L343" s="2"/>
     </row>
-    <row r="344" spans="1:12" ht="15">
+    <row r="344" spans="1:12">
       <c r="A344" s="1" t="s">
         <v>828</v>
       </c>
@@ -15391,7 +15436,7 @@
       <c r="K344" s="2"/>
       <c r="L344" s="2"/>
     </row>
-    <row r="345" spans="1:12" ht="15">
+    <row r="345" spans="1:12">
       <c r="A345" s="1" t="s">
         <v>829</v>
       </c>
@@ -15409,7 +15454,7 @@
       <c r="K345" s="2"/>
       <c r="L345" s="2"/>
     </row>
-    <row r="346" spans="1:12" ht="15">
+    <row r="346" spans="1:12">
       <c r="A346" s="1" t="s">
         <v>830</v>
       </c>
@@ -15427,7 +15472,7 @@
       <c r="K346" s="2"/>
       <c r="L346" s="2"/>
     </row>
-    <row r="347" spans="1:12" ht="15">
+    <row r="347" spans="1:12">
       <c r="A347" s="1" t="s">
         <v>831</v>
       </c>
@@ -15447,7 +15492,7 @@
       <c r="K347" s="2"/>
       <c r="L347" s="2"/>
     </row>
-    <row r="348" spans="1:12" ht="60">
+    <row r="348" spans="1:12" ht="54">
       <c r="A348" s="1" t="s">
         <v>832</v>
       </c>
@@ -15473,7 +15518,7 @@
       <c r="K348" s="2"/>
       <c r="L348" s="2"/>
     </row>
-    <row r="349" spans="1:12" ht="15">
+    <row r="349" spans="1:12">
       <c r="A349" s="1" t="s">
         <v>833</v>
       </c>
@@ -15493,7 +15538,7 @@
       <c r="K349" s="2"/>
       <c r="L349" s="2"/>
     </row>
-    <row r="350" spans="1:12" ht="15">
+    <row r="350" spans="1:12">
       <c r="A350" s="1" t="s">
         <v>834</v>
       </c>
@@ -15519,7 +15564,7 @@
       <c r="K350" s="2"/>
       <c r="L350" s="2"/>
     </row>
-    <row r="351" spans="1:12" ht="15">
+    <row r="351" spans="1:12">
       <c r="A351" s="1" t="s">
         <v>835</v>
       </c>
@@ -15537,7 +15582,7 @@
       <c r="K351" s="2"/>
       <c r="L351" s="2"/>
     </row>
-    <row r="352" spans="1:12" ht="15">
+    <row r="352" spans="1:12">
       <c r="A352" s="1" t="s">
         <v>836</v>
       </c>
@@ -15559,7 +15604,7 @@
       <c r="K352" s="2"/>
       <c r="L352" s="2"/>
     </row>
-    <row r="353" spans="1:12" ht="15">
+    <row r="353" spans="1:12">
       <c r="A353" s="1" t="s">
         <v>837</v>
       </c>
@@ -15581,7 +15626,7 @@
       </c>
       <c r="L353" s="2"/>
     </row>
-    <row r="354" spans="1:12" ht="30">
+    <row r="354" spans="1:12" ht="27">
       <c r="A354" s="1" t="s">
         <v>915</v>
       </c>
@@ -15615,7 +15660,7 @@
       <c r="K354" s="2"/>
       <c r="L354" s="2"/>
     </row>
-    <row r="355" spans="1:12" ht="15">
+    <row r="355" spans="1:12">
       <c r="A355" s="1" t="s">
         <v>838</v>
       </c>
@@ -15639,7 +15684,7 @@
       <c r="K355" s="2"/>
       <c r="L355" s="2"/>
     </row>
-    <row r="356" spans="1:12" ht="32">
+    <row r="356" spans="1:12" ht="27">
       <c r="A356" s="1" t="s">
         <v>839</v>
       </c>
@@ -15663,7 +15708,7 @@
       <c r="K356" s="2"/>
       <c r="L356" s="2"/>
     </row>
-    <row r="357" spans="1:12" ht="15">
+    <row r="357" spans="1:12">
       <c r="A357" s="1" t="s">
         <v>840</v>
       </c>
@@ -15681,7 +15726,7 @@
       <c r="K357" s="2"/>
       <c r="L357" s="2"/>
     </row>
-    <row r="358" spans="1:12" ht="30">
+    <row r="358" spans="1:12" ht="27">
       <c r="A358" s="1" t="s">
         <v>841</v>
       </c>
@@ -15705,7 +15750,7 @@
       <c r="K358" s="2"/>
       <c r="L358" s="2"/>
     </row>
-    <row r="359" spans="1:12" ht="30">
+    <row r="359" spans="1:12" ht="27">
       <c r="A359" s="1" t="s">
         <v>842</v>
       </c>
@@ -15729,7 +15774,7 @@
       <c r="K359" s="2"/>
       <c r="L359" s="2"/>
     </row>
-    <row r="360" spans="1:12" ht="30">
+    <row r="360" spans="1:12" ht="27">
       <c r="A360" s="1" t="s">
         <v>843</v>
       </c>
@@ -15757,7 +15802,7 @@
       <c r="K360" s="2"/>
       <c r="L360" s="2"/>
     </row>
-    <row r="361" spans="1:12" ht="15">
+    <row r="361" spans="1:12">
       <c r="A361" s="1" t="s">
         <v>844</v>
       </c>
@@ -15787,7 +15832,7 @@
       <c r="K361" s="2"/>
       <c r="L361" s="2"/>
     </row>
-    <row r="362" spans="1:12" ht="45">
+    <row r="362" spans="1:12" ht="40.5">
       <c r="A362" s="1" t="s">
         <v>845</v>
       </c>
@@ -15815,7 +15860,7 @@
       <c r="K362" s="2"/>
       <c r="L362" s="2"/>
     </row>
-    <row r="363" spans="1:12" ht="30">
+    <row r="363" spans="1:12" ht="27">
       <c r="A363" s="1" t="s">
         <v>846</v>
       </c>
@@ -15851,7 +15896,7 @@
       <c r="K364" s="2"/>
       <c r="L364" s="2"/>
     </row>
-    <row r="365" spans="1:12" ht="15">
+    <row r="365" spans="1:12">
       <c r="A365" s="1" t="s">
         <v>848</v>
       </c>
@@ -15869,7 +15914,7 @@
       <c r="K365" s="2"/>
       <c r="L365" s="2"/>
     </row>
-    <row r="366" spans="1:12" ht="30">
+    <row r="366" spans="1:12" ht="27">
       <c r="A366" s="1" t="s">
         <v>849</v>
       </c>
@@ -15893,7 +15938,7 @@
       <c r="K366" s="2"/>
       <c r="L366" s="2"/>
     </row>
-    <row r="367" spans="1:12" ht="60">
+    <row r="367" spans="1:12" ht="54">
       <c r="A367" s="1" t="s">
         <v>850</v>
       </c>
@@ -16004,15 +16049,15 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G297"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="14.1640625" customWidth="1"/>
-    <col min="2" max="2" width="32.83203125" customWidth="1"/>
-    <col min="3" max="3" width="35.1640625" customWidth="1"/>
-    <col min="4" max="4" width="21.83203125" customWidth="1"/>
-    <col min="5" max="5" width="44.6640625" customWidth="1"/>
+    <col min="1" max="1" width="14.125" customWidth="1"/>
+    <col min="2" max="2" width="32.875" customWidth="1"/>
+    <col min="3" max="3" width="35.125" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="44.625" customWidth="1"/>
     <col min="6" max="6" width="36.5" customWidth="1"/>
-    <col min="7" max="7" width="45.1640625" customWidth="1"/>
+    <col min="7" max="7" width="45.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="56.25" customHeight="1">
@@ -16038,7 +16083,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="50" customHeight="1">
+    <row r="2" spans="1:7" ht="50.1" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>1554</v>
       </c>
@@ -16061,7 +16106,7 @@
         <v>1461</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15">
+    <row r="3" spans="1:7">
       <c r="A3" s="4" t="s">
         <v>1555</v>
       </c>
@@ -16076,7 +16121,7 @@
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
     </row>
-    <row r="4" spans="1:7" ht="15">
+    <row r="4" spans="1:7">
       <c r="A4" s="4" t="s">
         <v>1556</v>
       </c>
@@ -16091,7 +16136,7 @@
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" spans="1:7" ht="15">
+    <row r="5" spans="1:7">
       <c r="A5" s="4" t="s">
         <v>1557</v>
       </c>
@@ -16104,7 +16149,7 @@
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="1:7" ht="15">
+    <row r="6" spans="1:7">
       <c r="A6" s="4" t="s">
         <v>1558</v>
       </c>
@@ -16117,7 +16162,7 @@
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" spans="1:7" ht="30">
+    <row r="7" spans="1:7" ht="27">
       <c r="A7" s="4" t="s">
         <v>1559</v>
       </c>
@@ -16130,7 +16175,7 @@
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" spans="1:7" ht="30">
+    <row r="8" spans="1:7" ht="27">
       <c r="A8" s="4" t="s">
         <v>1560</v>
       </c>
@@ -16149,7 +16194,7 @@
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" spans="1:7" ht="15">
+    <row r="9" spans="1:7" ht="27">
       <c r="A9" s="4" t="s">
         <v>1561</v>
       </c>
@@ -16168,7 +16213,7 @@
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" spans="1:7" ht="15">
+    <row r="10" spans="1:7">
       <c r="A10" s="4" t="s">
         <v>1562</v>
       </c>
@@ -16183,7 +16228,7 @@
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" spans="1:7" ht="15">
+    <row r="11" spans="1:7">
       <c r="A11" s="4" t="s">
         <v>1563</v>
       </c>
@@ -16196,7 +16241,7 @@
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
     </row>
-    <row r="12" spans="1:7" ht="30">
+    <row r="12" spans="1:7" ht="27">
       <c r="A12" s="4" t="s">
         <v>1564</v>
       </c>
@@ -16213,7 +16258,7 @@
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
     </row>
-    <row r="13" spans="1:7" ht="15">
+    <row r="13" spans="1:7">
       <c r="A13" s="4" t="s">
         <v>1565</v>
       </c>
@@ -16226,7 +16271,7 @@
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
     </row>
-    <row r="14" spans="1:7" ht="30">
+    <row r="14" spans="1:7" ht="27">
       <c r="A14" s="4" t="s">
         <v>1566</v>
       </c>
@@ -16241,7 +16286,7 @@
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
     </row>
-    <row r="15" spans="1:7" ht="15">
+    <row r="15" spans="1:7">
       <c r="A15" s="4" t="s">
         <v>1567</v>
       </c>
@@ -16254,7 +16299,7 @@
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
     </row>
-    <row r="16" spans="1:7" ht="15">
+    <row r="16" spans="1:7">
       <c r="A16" s="4" t="s">
         <v>1568</v>
       </c>
@@ -16267,7 +16312,7 @@
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
     </row>
-    <row r="17" spans="1:7" ht="15">
+    <row r="17" spans="1:7">
       <c r="A17" s="4" t="s">
         <v>1569</v>
       </c>
@@ -16284,7 +16329,7 @@
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
     </row>
-    <row r="18" spans="1:7" ht="15">
+    <row r="18" spans="1:7">
       <c r="A18" s="4" t="s">
         <v>1570</v>
       </c>
@@ -16297,7 +16342,7 @@
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
     </row>
-    <row r="19" spans="1:7" ht="15">
+    <row r="19" spans="1:7">
       <c r="A19" s="4" t="s">
         <v>1571</v>
       </c>
@@ -16312,7 +16357,7 @@
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
     </row>
-    <row r="20" spans="1:7" ht="15">
+    <row r="20" spans="1:7">
       <c r="A20" s="4" t="s">
         <v>1572</v>
       </c>
@@ -16327,7 +16372,7 @@
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
     </row>
-    <row r="21" spans="1:7" ht="15">
+    <row r="21" spans="1:7">
       <c r="A21" s="4" t="s">
         <v>1573</v>
       </c>
@@ -16342,7 +16387,7 @@
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
     </row>
-    <row r="22" spans="1:7" ht="15">
+    <row r="22" spans="1:7">
       <c r="A22" s="4" t="s">
         <v>1574</v>
       </c>
@@ -16355,7 +16400,7 @@
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
     </row>
-    <row r="23" spans="1:7" ht="15">
+    <row r="23" spans="1:7">
       <c r="A23" s="4" t="s">
         <v>1575</v>
       </c>
@@ -16368,7 +16413,7 @@
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
     </row>
-    <row r="24" spans="1:7" ht="15">
+    <row r="24" spans="1:7">
       <c r="A24" s="4" t="s">
         <v>1576</v>
       </c>
@@ -16381,7 +16426,7 @@
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
     </row>
-    <row r="25" spans="1:7" ht="15">
+    <row r="25" spans="1:7">
       <c r="A25" s="4" t="s">
         <v>1577</v>
       </c>
@@ -16394,7 +16439,7 @@
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
     </row>
-    <row r="26" spans="1:7" ht="15">
+    <row r="26" spans="1:7">
       <c r="A26" s="4" t="s">
         <v>1578</v>
       </c>
@@ -16407,7 +16452,7 @@
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
     </row>
-    <row r="27" spans="1:7" ht="15">
+    <row r="27" spans="1:7">
       <c r="A27" s="4" t="s">
         <v>1579</v>
       </c>
@@ -16422,7 +16467,7 @@
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
     </row>
-    <row r="28" spans="1:7" ht="15">
+    <row r="28" spans="1:7">
       <c r="A28" s="4" t="s">
         <v>1580</v>
       </c>
@@ -16435,7 +16480,7 @@
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
     </row>
-    <row r="29" spans="1:7" ht="15">
+    <row r="29" spans="1:7">
       <c r="A29" s="4" t="s">
         <v>1581</v>
       </c>
@@ -16446,7 +16491,7 @@
       <c r="F29" s="4"/>
       <c r="G29" s="4"/>
     </row>
-    <row r="30" spans="1:7" ht="15">
+    <row r="30" spans="1:7">
       <c r="A30" s="4" t="s">
         <v>1582</v>
       </c>
@@ -16459,7 +16504,7 @@
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
     </row>
-    <row r="31" spans="1:7" ht="15">
+    <row r="31" spans="1:7">
       <c r="A31" s="4" t="s">
         <v>1583</v>
       </c>
@@ -16470,7 +16515,7 @@
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
     </row>
-    <row r="32" spans="1:7" ht="15">
+    <row r="32" spans="1:7">
       <c r="A32" s="4" t="s">
         <v>1584</v>
       </c>
@@ -16481,7 +16526,7 @@
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
     </row>
-    <row r="33" spans="1:7" ht="15">
+    <row r="33" spans="1:7">
       <c r="A33" s="4" t="s">
         <v>1585</v>
       </c>
@@ -16492,7 +16537,7 @@
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
     </row>
-    <row r="34" spans="1:7" ht="15">
+    <row r="34" spans="1:7">
       <c r="A34" s="4" t="s">
         <v>1586</v>
       </c>
@@ -16502,7 +16547,7 @@
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
     </row>
-    <row r="35" spans="1:7" ht="15">
+    <row r="35" spans="1:7">
       <c r="A35" s="4" t="s">
         <v>1587</v>
       </c>
@@ -16515,7 +16560,7 @@
       <c r="F35" s="4"/>
       <c r="G35" s="4"/>
     </row>
-    <row r="36" spans="1:7" ht="15">
+    <row r="36" spans="1:7">
       <c r="A36" s="4" t="s">
         <v>1588</v>
       </c>
@@ -16528,7 +16573,7 @@
       <c r="F36" s="4"/>
       <c r="G36" s="4"/>
     </row>
-    <row r="37" spans="1:7" ht="15">
+    <row r="37" spans="1:7">
       <c r="A37" s="4" t="s">
         <v>1589</v>
       </c>
@@ -16541,7 +16586,7 @@
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
     </row>
-    <row r="38" spans="1:7" ht="15">
+    <row r="38" spans="1:7">
       <c r="A38" s="4" t="s">
         <v>1590</v>
       </c>
@@ -16554,7 +16599,7 @@
       <c r="F38" s="4"/>
       <c r="G38" s="4"/>
     </row>
-    <row r="39" spans="1:7" ht="15">
+    <row r="39" spans="1:7">
       <c r="A39" s="4" t="s">
         <v>1591</v>
       </c>
@@ -16567,7 +16612,7 @@
       <c r="F39" s="4"/>
       <c r="G39" s="4"/>
     </row>
-    <row r="40" spans="1:7" ht="15">
+    <row r="40" spans="1:7">
       <c r="A40" s="4" t="s">
         <v>1592</v>
       </c>
@@ -16578,7 +16623,7 @@
       <c r="F40" s="4"/>
       <c r="G40" s="4"/>
     </row>
-    <row r="41" spans="1:7" ht="15">
+    <row r="41" spans="1:7">
       <c r="A41" s="4" t="s">
         <v>1593</v>
       </c>
@@ -16589,7 +16634,7 @@
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
     </row>
-    <row r="42" spans="1:7" ht="15">
+    <row r="42" spans="1:7">
       <c r="A42" s="4" t="s">
         <v>1594</v>
       </c>
@@ -16602,7 +16647,7 @@
       <c r="F42" s="4"/>
       <c r="G42" s="4"/>
     </row>
-    <row r="43" spans="1:7" ht="15">
+    <row r="43" spans="1:7">
       <c r="A43" s="4" t="s">
         <v>1595</v>
       </c>
@@ -16613,7 +16658,7 @@
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
     </row>
-    <row r="44" spans="1:7" ht="15">
+    <row r="44" spans="1:7">
       <c r="A44" s="4" t="s">
         <v>1596</v>
       </c>
@@ -16626,7 +16671,7 @@
       <c r="F44" s="4"/>
       <c r="G44" s="4"/>
     </row>
-    <row r="45" spans="1:7" ht="15">
+    <row r="45" spans="1:7">
       <c r="A45" s="4" t="s">
         <v>1597</v>
       </c>
@@ -16639,7 +16684,7 @@
       <c r="F45" s="4"/>
       <c r="G45" s="4"/>
     </row>
-    <row r="46" spans="1:7" ht="15">
+    <row r="46" spans="1:7">
       <c r="A46" s="4" t="s">
         <v>1598</v>
       </c>
@@ -16650,7 +16695,7 @@
       <c r="F46" s="4"/>
       <c r="G46" s="4"/>
     </row>
-    <row r="47" spans="1:7" ht="15">
+    <row r="47" spans="1:7">
       <c r="A47" s="4" t="s">
         <v>1599</v>
       </c>
@@ -16661,7 +16706,7 @@
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
     </row>
-    <row r="48" spans="1:7" ht="15">
+    <row r="48" spans="1:7">
       <c r="A48" s="4" t="s">
         <v>1600</v>
       </c>
@@ -16672,7 +16717,7 @@
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
     </row>
-    <row r="49" spans="1:7" ht="15">
+    <row r="49" spans="1:7">
       <c r="A49" s="4" t="s">
         <v>1601</v>
       </c>
@@ -16683,7 +16728,7 @@
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
     </row>
-    <row r="50" spans="1:7" ht="15">
+    <row r="50" spans="1:7">
       <c r="A50" s="4" t="s">
         <v>1602</v>
       </c>
@@ -16694,7 +16739,7 @@
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
     </row>
-    <row r="51" spans="1:7" ht="15">
+    <row r="51" spans="1:7">
       <c r="A51" s="4" t="s">
         <v>1603</v>
       </c>
@@ -16705,7 +16750,7 @@
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
     </row>
-    <row r="52" spans="1:7" ht="15">
+    <row r="52" spans="1:7">
       <c r="A52" s="4" t="s">
         <v>1604</v>
       </c>
@@ -16716,7 +16761,7 @@
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
     </row>
-    <row r="53" spans="1:7" ht="15">
+    <row r="53" spans="1:7">
       <c r="A53" s="4" t="s">
         <v>1605</v>
       </c>
@@ -16729,7 +16774,7 @@
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
     </row>
-    <row r="54" spans="1:7" ht="15">
+    <row r="54" spans="1:7">
       <c r="A54" s="4" t="s">
         <v>1606</v>
       </c>
@@ -16740,7 +16785,7 @@
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
     </row>
-    <row r="55" spans="1:7" ht="15">
+    <row r="55" spans="1:7">
       <c r="A55" s="4" t="s">
         <v>1607</v>
       </c>
@@ -16751,7 +16796,7 @@
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
     </row>
-    <row r="56" spans="1:7" ht="15">
+    <row r="56" spans="1:7">
       <c r="A56" s="4" t="s">
         <v>1608</v>
       </c>
@@ -16762,7 +16807,7 @@
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
     </row>
-    <row r="57" spans="1:7" ht="15">
+    <row r="57" spans="1:7">
       <c r="A57" s="4" t="s">
         <v>1609</v>
       </c>
@@ -16773,7 +16818,7 @@
       <c r="F57" s="4"/>
       <c r="G57" s="4"/>
     </row>
-    <row r="58" spans="1:7" ht="15">
+    <row r="58" spans="1:7">
       <c r="A58" s="4" t="s">
         <v>1610</v>
       </c>
@@ -16784,7 +16829,7 @@
       <c r="F58" s="4"/>
       <c r="G58" s="4"/>
     </row>
-    <row r="59" spans="1:7" ht="15">
+    <row r="59" spans="1:7">
       <c r="A59" s="4" t="s">
         <v>1611</v>
       </c>
@@ -18954,12 +18999,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="27.83203125" customWidth="1"/>
-    <col min="2" max="2" width="24.83203125" customWidth="1"/>
-    <col min="3" max="3" width="35.6640625" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" customWidth="1"/>
+    <col min="1" max="1" width="27.875" customWidth="1"/>
+    <col min="2" max="2" width="24.875" customWidth="1"/>
+    <col min="3" max="3" width="35.625" customWidth="1"/>
+    <col min="4" max="4" width="17.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -19156,11 +19201,11 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="31.1640625" customWidth="1"/>
-    <col min="3" max="3" width="88.33203125" customWidth="1"/>
-    <col min="4" max="4" width="52.1640625" customWidth="1"/>
+    <col min="2" max="2" width="31.125" customWidth="1"/>
+    <col min="3" max="3" width="88.375" customWidth="1"/>
+    <col min="4" max="4" width="52.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -19307,7 +19352,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="26">
+    <row r="15" spans="1:4" ht="24">
       <c r="A15" s="40"/>
       <c r="B15" s="11" t="s">
         <v>451</v>
@@ -19341,7 +19386,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="26">
+    <row r="18" spans="1:4" ht="24">
       <c r="A18" s="29"/>
       <c r="B18" s="32"/>
       <c r="C18" s="35"/>
@@ -19369,7 +19414,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="26">
+    <row r="21" spans="1:4" ht="24">
       <c r="A21" s="29"/>
       <c r="B21" s="11" t="s">
         <v>467</v>
@@ -19415,7 +19460,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="26">
+    <row r="25" spans="1:4" ht="24">
       <c r="A25" s="29"/>
       <c r="B25" s="11" t="s">
         <v>475</v>
@@ -19449,7 +19494,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="39">
+    <row r="28" spans="1:4" ht="36">
       <c r="A28" s="40"/>
       <c r="B28" s="11" t="s">
         <v>481</v>
@@ -19475,7 +19520,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="26">
+    <row r="30" spans="1:4" ht="24">
       <c r="A30" s="29"/>
       <c r="B30" s="32"/>
       <c r="C30" s="35"/>
@@ -19633,7 +19678,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="49" spans="1:4" ht="52">
+    <row r="49" spans="1:4" ht="48">
       <c r="A49" s="29"/>
       <c r="B49" s="33"/>
       <c r="C49" s="10" t="s">
@@ -19663,7 +19708,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="52" spans="1:4" ht="26">
+    <row r="52" spans="1:4" ht="24">
       <c r="A52" s="29"/>
       <c r="B52" s="11" t="s">
         <v>479</v>
@@ -19695,7 +19740,7 @@
       </c>
       <c r="D54" s="19"/>
     </row>
-    <row r="55" spans="1:4" ht="78">
+    <row r="55" spans="1:4" ht="72">
       <c r="A55" s="29"/>
       <c r="B55" s="13" t="s">
         <v>517</v>
@@ -19915,7 +19960,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="81" spans="1:4" ht="39">
+    <row r="81" spans="1:4" ht="36">
       <c r="A81" s="29"/>
       <c r="B81" s="11" t="s">
         <v>550</v>
@@ -19949,7 +19994,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="84" spans="1:4" ht="26">
+    <row r="84" spans="1:4" ht="24">
       <c r="A84" s="29"/>
       <c r="B84" s="11" t="s">
         <v>556</v>
@@ -19979,7 +20024,7 @@
       </c>
       <c r="D86" s="19"/>
     </row>
-    <row r="87" spans="1:4" ht="130">
+    <row r="87" spans="1:4" ht="120">
       <c r="A87" s="29"/>
       <c r="B87" s="13" t="s">
         <v>813</v>
@@ -20033,9 +20078,9 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:A31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="89.6640625" customWidth="1"/>
+    <col min="1" max="1" width="89.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">

--- a/notes/langnote.xlsx
+++ b/notes/langnote.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23901"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\langnote\notes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\github\langnote\notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D32BBD5-4F55-4E6F-A4B1-1F92C175559B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E9C4BAC-ED81-4159-934E-172AE58BE30B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2014" sheetId="9" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2093" uniqueCount="2013">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2097" uniqueCount="2017">
   <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -7273,6 +7273,22 @@
   </si>
   <si>
     <t>shell</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Netty源码编译</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpringBoot源码编译</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多米娱乐让画类图</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>考察内容的范围很广泛</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -13865,6 +13881,12 @@
       <c r="A237" s="1" t="s">
         <v>588</v>
       </c>
+      <c r="B237" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C237" t="s">
+        <v>2014</v>
+      </c>
     </row>
     <row r="238" spans="1:6">
       <c r="A238" s="1" t="s">
@@ -14046,6 +14068,9 @@
       <c r="B257" t="s">
         <v>1284</v>
       </c>
+      <c r="C257" t="s">
+        <v>2015</v>
+      </c>
     </row>
     <row r="258" spans="1:4">
       <c r="A258" s="1" t="s">
@@ -14069,6 +14094,9 @@
       </c>
       <c r="B260" t="s">
         <v>1286</v>
+      </c>
+      <c r="C260" t="s">
+        <v>2016</v>
       </c>
     </row>
     <row r="261" spans="1:4">
